--- a/BASE_RECORRIDOS_PRO_JCA.xlsx
+++ b/BASE_RECORRIDOS_PRO_JCA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\INTERVENTORIA VELNEC\Recorridos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C2A09BC-3327-45EB-B8D3-2E2574CCAE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9A81BD-C59B-405A-9957-E01AC8A41196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,8 +30,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId8"/>
-    <pivotCache cacheId="17" r:id="rId9"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4405" uniqueCount="1597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4577" uniqueCount="1671">
   <si>
     <t>ID</t>
   </si>
@@ -4841,6 +4841,228 @@
   </si>
   <si>
     <t>presenta error el GPS</t>
+  </si>
+  <si>
+    <t>574ed8d39c896c02</t>
+  </si>
+  <si>
+    <t>18_09_2026_AO_Diur.gpx</t>
+  </si>
+  <si>
+    <t>574ed8d39c896c0247f665ebcba8d2a772669a22f14ae0070f8da719917542de</t>
+  </si>
+  <si>
+    <t>18/09/2026</t>
+  </si>
+  <si>
+    <t>18/09/2026 08:35:14</t>
+  </si>
+  <si>
+    <t>18/09/2026 16:03:43</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS dentro de la tolerancia del horario programado.; 4 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.225611, -75.599078</t>
+  </si>
+  <si>
+    <t>6.238764, -75.607866</t>
+  </si>
+  <si>
+    <t>db75e5dbfc3c1eec</t>
+  </si>
+  <si>
+    <t>18_09_2026_AR_Diur.gpx</t>
+  </si>
+  <si>
+    <t>db75e5dbfc3c1eecb9afb154e5d6a0d39956d0605060534e537b415b99a07c0a</t>
+  </si>
+  <si>
+    <t>18/09/2026 08:29:36</t>
+  </si>
+  <si>
+    <t>18/09/2026 16:01:24</t>
+  </si>
+  <si>
+    <t>6.225697, -75.599436</t>
+  </si>
+  <si>
+    <t>6.247761, -75.614860</t>
+  </si>
+  <si>
+    <t>28351e32ecc3aab7</t>
+  </si>
+  <si>
+    <t>18_09_2026_DR_Diur.gpx</t>
+  </si>
+  <si>
+    <t>28351e32ecc3aab71e662aabbd511301bdc231f6293fc5ff9d746e362336fe1a</t>
+  </si>
+  <si>
+    <t>18/09/2026 08:37:58</t>
+  </si>
+  <si>
+    <t>18/09/2026 15:42:52</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS anticipado: 00:17:08 antes de las 16:00.; 2 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.230816, -75.601884</t>
+  </si>
+  <si>
+    <t>6.239649, -75.608310</t>
+  </si>
+  <si>
+    <t>760f3e903b5a7381</t>
+  </si>
+  <si>
+    <t>18_09_2026_JA_Diur.gpx</t>
+  </si>
+  <si>
+    <t>760f3e903b5a7381a552db57ff0e37600bba53b1b5771d9f6458bc584420641b</t>
+  </si>
+  <si>
+    <t>18/09/2026 08:43:57</t>
+  </si>
+  <si>
+    <t>18/09/2026 12:05:04</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS anticipado: 03:54:56 antes de las 16:00.</t>
+  </si>
+  <si>
+    <t>6.225685, -75.599091</t>
+  </si>
+  <si>
+    <t>6.237138, -75.558726</t>
+  </si>
+  <si>
+    <t>09ab39dc75e7d94d</t>
+  </si>
+  <si>
+    <t>18_09_2026_JO_Diur.gpx</t>
+  </si>
+  <si>
+    <t>09ab39dc75e7d94d5332ccc0420aa8c018154017de4e948142214b7b19dd0966</t>
+  </si>
+  <si>
+    <t>18/09/2026 08:46:27</t>
+  </si>
+  <si>
+    <t>18/09/2026 16:00:31</t>
+  </si>
+  <si>
+    <t>Inicio GPS tardío: 00:16:28 después de las 08:30.; Fin GPS dentro de la tolerancia del horario programado.; 11 hueco(s) GPS &gt;= 10 min.; 1 permanencia(s) GPS detectada(s); requiere contexto.</t>
+  </si>
+  <si>
+    <t>6.225605, -75.599091</t>
+  </si>
+  <si>
+    <t>6.246771, -75.554138</t>
+  </si>
+  <si>
+    <t>9031de5bb9e7b3c5</t>
+  </si>
+  <si>
+    <t>18_09_2026_JZ_Diur.gpx</t>
+  </si>
+  <si>
+    <t>9031de5bb9e7b3c53e589e5b129dad5824953847aaa15e3f4a325f215adbb8cd</t>
+  </si>
+  <si>
+    <t>18/09/2026 08:10:59</t>
+  </si>
+  <si>
+    <t>18/09/2026 14:48:04</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 00:19:01 antes de las 08:30.; Fin GPS anticipado: 01:11:56 antes de las 16:00.</t>
+  </si>
+  <si>
+    <t>6.226691, -75.599234</t>
+  </si>
+  <si>
+    <t>6.241651, -75.516547</t>
+  </si>
+  <si>
+    <t>d4b7f60cdb6f56d4</t>
+  </si>
+  <si>
+    <t>18_09_2026_SJ_Diur.gpx</t>
+  </si>
+  <si>
+    <t>d4b7f60cdb6f56d4d15ed5e2a9c06189fdbb0bf21191b183fc95e0debaba2af6</t>
+  </si>
+  <si>
+    <t>18/09/2026 08:40:31</t>
+  </si>
+  <si>
+    <t>18/09/2026 15:28:50</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS anticipado: 00:31:10 antes de las 16:00.</t>
+  </si>
+  <si>
+    <t>6.225759, -75.599410</t>
+  </si>
+  <si>
+    <t>6.304929, -75.577502</t>
+  </si>
+  <si>
+    <t>6dd1257b59b28db6</t>
+  </si>
+  <si>
+    <t>18_09_2026_YL_Diur.gpx</t>
+  </si>
+  <si>
+    <t>6dd1257b59b28db66571c1c0235809e4044da3a8f08fe8f8e2c5599b906ad4eb</t>
+  </si>
+  <si>
+    <t>18/09/2026 08:47:14</t>
+  </si>
+  <si>
+    <t>18/09/2026 15:59:49</t>
+  </si>
+  <si>
+    <t>Inicio GPS tardío: 00:17:14 después de las 08:30.; Fin GPS dentro de la tolerancia del horario programado.</t>
+  </si>
+  <si>
+    <t>6.225650, -75.599074</t>
+  </si>
+  <si>
+    <t>6.258732, -75.616245</t>
+  </si>
+  <si>
+    <t>08841ee0ded3204b</t>
+  </si>
+  <si>
+    <t>19_09_2026_DR_Diur.gpx</t>
+  </si>
+  <si>
+    <t>08841ee0ded3204baf0f20b9363ccba0e7e3c445dfce38bd70bfa3a7b5a4ec8c</t>
+  </si>
+  <si>
+    <t>19/09/2026</t>
+  </si>
+  <si>
+    <t>19/09/2026 09:28:26</t>
+  </si>
+  <si>
+    <t>19/09/2026 14:22:55</t>
+  </si>
+  <si>
+    <t>Inicio GPS tardío: 00:58:26 después de las 08:30.; Fin GPS anticipado: 01:37:05 antes de las 16:00.; 1 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.252651, -75.609697</t>
+  </si>
+  <si>
+    <t>6.243433, -75.602993</t>
+  </si>
+  <si>
+    <t>retubieron el vehiculo donde estaba laborando en el corregimineto de Santa Elena</t>
   </si>
 </sst>
 </file>
@@ -5016,7 +5238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5099,318 +5321,16 @@
     <xf numFmtId="21" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" pivotButton="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="128">
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
-    </dxf>
+  <dxfs count="73">
     <dxf>
       <fill>
         <patternFill>
@@ -5507,6 +5427,9 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
     </dxf>
     <dxf>
       <font>
@@ -5628,9 +5551,6 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
     </dxf>
     <dxf>
       <font>
@@ -39226,1385 +39146,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
-  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item h="1" m="1" x="4"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="13"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="10">
-    <format dxfId="70">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="69">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="68">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="67">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="66">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="65">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="64">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="63">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="62">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="61">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="34" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
-  <location ref="A107:D123" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="8"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Suma de Kilómetros" fld="19" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="6">
-    <chartFormat chart="16" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="12"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="12"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B44BF58-179E-4C57-BD89-E6E3367D37B9}" name="TablaDinámica4" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
-  <location ref="K107:M122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item h="1" x="0"/>
-        <item h="1" m="1" x="4"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="17"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="12">
-    <format dxfId="82">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="81">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="80">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="79">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="78">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="17" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="77">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="76">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="75">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="74">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="73">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="72">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="17" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="71">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="28" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="28" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="28" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="28" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E67C1C-2F15-4D2B-A97A-A1B46B6F5B69}" name="TablaDinámica2" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
-  <location ref="A57:E73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item m="1" x="4"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="17"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="8">
-    <chartFormat chart="24" format="13" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="14" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="15" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="16" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="21" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="22" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="23" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="24" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0966AFF-8B15-4A0E-BE48-1F64EB76CB37}" name="TablaDinámica7" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="57">
-  <location ref="AI107:AJ122" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item h="1" x="11"/>
-        <item h="1" x="12"/>
-        <item h="1" x="13"/>
-        <item h="1" x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Turno" fld="8" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="10">
-    <format dxfId="92">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="91">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="90">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="89">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="88">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="87">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="86">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="85">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="84">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="83">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="48" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="53" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="56" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D330A9A-54B8-43DD-8D11-CC5633B99CDA}" name="TablaDinámica1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D330A9A-54B8-43DD-8D11-CC5633B99CDA}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A6:E22" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
     <pivotField showAll="0"/>
@@ -40891,8 +39433,548 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{238AB259-E577-48AC-B3A0-09F752F5685D}" name="TablaDinámica6" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
+  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" m="1" x="4"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="13"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="15">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="34" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
+  <location ref="A107:D123" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="8"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Suma de Kilómetros" fld="19" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="16" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{238AB259-E577-48AC-B3A0-09F752F5685D}" name="TablaDinámica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A169:B185" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="43">
     <pivotField showAll="0"/>
@@ -41690,7 +40772,7 @@
     <dataField name="Suma de Sumatoria de tiempo total sin recorrido" fld="38" baseField="6" baseItem="0" numFmtId="21"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="93">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -41717,42 +40799,880 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B44BF58-179E-4C57-BD89-E6E3367D37B9}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
+  <location ref="K107:M122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item h="1" x="0"/>
+        <item h="1" m="1" x="4"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="17"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="12">
+    <format dxfId="28">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="25">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="17" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="17" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="17">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="28" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="28" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="28" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="28" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E67C1C-2F15-4D2B-A97A-A1B46B6F5B69}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
+  <location ref="A57:E73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item m="1" x="4"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="17"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="8">
+    <chartFormat chart="24" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="15" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="16" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="21" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="22" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="23" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="24" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0966AFF-8B15-4A0E-BE48-1F64EB76CB37}" name="TablaDinámica7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="57">
+  <location ref="AI107:AJ122" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="13"/>
+        <item h="1" x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Turno" fld="8" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="38">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="37">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="35">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="33">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="32">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="31">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="48" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="53" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="56" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{07721E28-36B5-4676-BFC5-097A3B63190A}" name="Tabla1" displayName="Tabla1" ref="A1:AF1048573" totalsRowShown="0" headerRowDxfId="127" dataDxfId="126">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{07721E28-36B5-4676-BFC5-097A3B63190A}" name="Tabla1" displayName="Tabla1" ref="A1:AF1048573" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71">
   <autoFilter ref="A1:AF1048573" xr:uid="{07721E28-36B5-4676-BFC5-097A3B63190A}"/>
   <tableColumns count="32">
-    <tableColumn id="1" xr3:uid="{BFACFB74-E6A6-4648-B0DA-7D6E1FC88A79}" name="ID" dataDxfId="125"/>
-    <tableColumn id="2" xr3:uid="{B67B24E0-3585-47FC-A130-8F37C8640BC4}" name="Archivo" dataDxfId="124"/>
-    <tableColumn id="3" xr3:uid="{FB279346-C755-48B1-8385-D755BC44DB7E}" name="Hash SHA256" dataDxfId="123"/>
-    <tableColumn id="4" xr3:uid="{CF629B59-A100-4AAB-B74C-3B554EAB3BF0}" name="Fecha" dataDxfId="122"/>
-    <tableColumn id="5" xr3:uid="{EE06BA6F-C164-4ECD-A655-515F1957578E}" name="Año-Mes" dataDxfId="121"/>
-    <tableColumn id="6" xr3:uid="{FD8842D0-7E34-4084-9BAA-A564E135D8FF}" name="Día" dataDxfId="120"/>
-    <tableColumn id="7" xr3:uid="{16772661-0D26-4A9C-B574-83DD257F64D2}" name="Técnico" dataDxfId="119"/>
-    <tableColumn id="8" xr3:uid="{DC69C448-58B8-4806-B949-BF996984F186}" name="Iniciales" dataDxfId="118"/>
-    <tableColumn id="9" xr3:uid="{3962F890-58B4-4EE6-ABA8-850EB1190D27}" name="Turno" dataDxfId="117"/>
-    <tableColumn id="10" xr3:uid="{E92FA341-3BD4-4B2B-AC2C-BF72D43C66CC}" name="Puntos GPS" dataDxfId="116"/>
-    <tableColumn id="11" xr3:uid="{72021E2E-2F98-4204-8978-705D7AD09594}" name="Inicio Colombia" dataDxfId="115"/>
-    <tableColumn id="12" xr3:uid="{54D84601-2999-47A1-A65E-57823F56F2ED}" name="Inicio programado" dataDxfId="114"/>
-    <tableColumn id="13" xr3:uid="{640E6A33-50AC-4461-84B0-EB0F59FBE07B}" name="Diferencia inicio" dataDxfId="113"/>
-    <tableColumn id="14" xr3:uid="{DDCE6D58-3D24-45B9-861B-84CCB46683A5}" name="Estado inicio" dataDxfId="112"/>
-    <tableColumn id="15" xr3:uid="{E1697B5C-5781-44C1-8EDA-6F1ACE3F4029}" name="Fin Colombia" dataDxfId="111"/>
-    <tableColumn id="16" xr3:uid="{787745CA-B360-44D9-9446-ECB14730130D}" name="Fin programado" dataDxfId="110"/>
-    <tableColumn id="17" xr3:uid="{46398A77-17CC-4A5A-AC54-FC4D4EE9907E}" name="Diferencia fin" dataDxfId="109"/>
-    <tableColumn id="18" xr3:uid="{4941E755-E9FD-4193-9F96-E53315DB8EBE}" name="Estado fin" dataDxfId="108"/>
-    <tableColumn id="19" xr3:uid="{E263D8E6-044C-4AE9-A18B-8B14B2EAB3DA}" name="Duración" dataDxfId="107"/>
-    <tableColumn id="20" xr3:uid="{BB91D378-A483-49A2-A76B-BD54043F6607}" name="Kilómetros" dataDxfId="106"/>
-    <tableColumn id="21" xr3:uid="{192BB6F7-4294-4FAF-B104-6552C0F61A57}" name="Velocidad promedio (km/h)" dataDxfId="105"/>
-    <tableColumn id="22" xr3:uid="{6F9489E0-14AF-4D91-9AEE-1CE65B9112C6}" name="Tiempo movimiento" dataDxfId="104"/>
-    <tableColumn id="23" xr3:uid="{50092D24-4EA6-441E-B7D6-414B951B9F9F}" name="Movimiento lento" dataDxfId="103"/>
-    <tableColumn id="24" xr3:uid="{CF339310-E34C-43C1-90CE-9F433AAB70F1}" name="Tiempo permanencias" dataDxfId="102"/>
-    <tableColumn id="25" xr3:uid="{6FD925EC-EAEC-45E6-B136-F56F435E59B8}" name="Paradas &gt;=10 min" dataDxfId="101"/>
-    <tableColumn id="26" xr3:uid="{52AB8528-3A79-479D-A997-E53B6084B61F}" name="Paradas &gt;=15 min" dataDxfId="100"/>
-    <tableColumn id="27" xr3:uid="{1BA0A59E-7816-42F2-B5AB-3B78137E0F49}" name="Paradas &gt;=30 min" dataDxfId="99"/>
-    <tableColumn id="28" xr3:uid="{47D5247A-657B-4B5B-9D22-259A6A45A563}" name="Paradas &gt;=40 min" dataDxfId="98"/>
-    <tableColumn id="29" xr3:uid="{4B192CBD-58A3-4F70-BE72-992210A8D8A7}" name="Paradas &gt;=60 min" dataDxfId="97"/>
-    <tableColumn id="30" xr3:uid="{80E38742-5940-41B4-BC40-12884D5F6DF3}" name="Huecos GPS &gt;=10 min" dataDxfId="96"/>
-    <tableColumn id="31" xr3:uid="{A9D280E3-B898-4F0B-AB54-4F5DDCE469DA}" name="Estado recorrido" dataDxfId="95"/>
-    <tableColumn id="32" xr3:uid="{2D572601-C46B-4498-95CD-858FD080879D}" name="Observaciones" dataDxfId="94"/>
+    <tableColumn id="1" xr3:uid="{BFACFB74-E6A6-4648-B0DA-7D6E1FC88A79}" name="ID" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{B67B24E0-3585-47FC-A130-8F37C8640BC4}" name="Archivo" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{FB279346-C755-48B1-8385-D755BC44DB7E}" name="Hash SHA256" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{CF629B59-A100-4AAB-B74C-3B554EAB3BF0}" name="Fecha" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{EE06BA6F-C164-4ECD-A655-515F1957578E}" name="Año-Mes" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{FD8842D0-7E34-4084-9BAA-A564E135D8FF}" name="Día" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{16772661-0D26-4A9C-B574-83DD257F64D2}" name="Técnico" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{DC69C448-58B8-4806-B949-BF996984F186}" name="Iniciales" dataDxfId="63"/>
+    <tableColumn id="9" xr3:uid="{3962F890-58B4-4EE6-ABA8-850EB1190D27}" name="Turno" dataDxfId="62"/>
+    <tableColumn id="10" xr3:uid="{E92FA341-3BD4-4B2B-AC2C-BF72D43C66CC}" name="Puntos GPS" dataDxfId="61"/>
+    <tableColumn id="11" xr3:uid="{72021E2E-2F98-4204-8978-705D7AD09594}" name="Inicio Colombia" dataDxfId="60"/>
+    <tableColumn id="12" xr3:uid="{54D84601-2999-47A1-A65E-57823F56F2ED}" name="Inicio programado" dataDxfId="59"/>
+    <tableColumn id="13" xr3:uid="{640E6A33-50AC-4461-84B0-EB0F59FBE07B}" name="Diferencia inicio" dataDxfId="58"/>
+    <tableColumn id="14" xr3:uid="{DDCE6D58-3D24-45B9-861B-84CCB46683A5}" name="Estado inicio" dataDxfId="57"/>
+    <tableColumn id="15" xr3:uid="{E1697B5C-5781-44C1-8EDA-6F1ACE3F4029}" name="Fin Colombia" dataDxfId="56"/>
+    <tableColumn id="16" xr3:uid="{787745CA-B360-44D9-9446-ECB14730130D}" name="Fin programado" dataDxfId="55"/>
+    <tableColumn id="17" xr3:uid="{46398A77-17CC-4A5A-AC54-FC4D4EE9907E}" name="Diferencia fin" dataDxfId="54"/>
+    <tableColumn id="18" xr3:uid="{4941E755-E9FD-4193-9F96-E53315DB8EBE}" name="Estado fin" dataDxfId="53"/>
+    <tableColumn id="19" xr3:uid="{E263D8E6-044C-4AE9-A18B-8B14B2EAB3DA}" name="Duración" dataDxfId="52"/>
+    <tableColumn id="20" xr3:uid="{BB91D378-A483-49A2-A76B-BD54043F6607}" name="Kilómetros" dataDxfId="51"/>
+    <tableColumn id="21" xr3:uid="{192BB6F7-4294-4FAF-B104-6552C0F61A57}" name="Velocidad promedio (km/h)" dataDxfId="50"/>
+    <tableColumn id="22" xr3:uid="{6F9489E0-14AF-4D91-9AEE-1CE65B9112C6}" name="Tiempo movimiento" dataDxfId="49"/>
+    <tableColumn id="23" xr3:uid="{50092D24-4EA6-441E-B7D6-414B951B9F9F}" name="Movimiento lento" dataDxfId="48"/>
+    <tableColumn id="24" xr3:uid="{CF339310-E34C-43C1-90CE-9F433AAB70F1}" name="Tiempo permanencias" dataDxfId="47"/>
+    <tableColumn id="25" xr3:uid="{6FD925EC-EAEC-45E6-B136-F56F435E59B8}" name="Paradas &gt;=10 min" dataDxfId="46"/>
+    <tableColumn id="26" xr3:uid="{52AB8528-3A79-479D-A997-E53B6084B61F}" name="Paradas &gt;=15 min" dataDxfId="45"/>
+    <tableColumn id="27" xr3:uid="{1BA0A59E-7816-42F2-B5AB-3B78137E0F49}" name="Paradas &gt;=30 min" dataDxfId="44"/>
+    <tableColumn id="28" xr3:uid="{47D5247A-657B-4B5B-9D22-259A6A45A563}" name="Paradas &gt;=40 min" dataDxfId="43"/>
+    <tableColumn id="29" xr3:uid="{4B192CBD-58A3-4F70-BE72-992210A8D8A7}" name="Paradas &gt;=60 min" dataDxfId="42"/>
+    <tableColumn id="30" xr3:uid="{80E38742-5940-41B4-BC40-12884D5F6DF3}" name="Huecos GPS &gt;=10 min" dataDxfId="41"/>
+    <tableColumn id="31" xr3:uid="{A9D280E3-B898-4F0B-AB54-4F5DDCE469DA}" name="Estado recorrido" dataDxfId="40"/>
+    <tableColumn id="32" xr3:uid="{2D572601-C46B-4498-95CD-858FD080879D}" name="Observaciones" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -42146,16 +42066,16 @@
       <c r="A8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8">
         <v>8</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8">
         <v>4</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8">
         <v>2</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8">
         <v>14</v>
       </c>
     </row>
@@ -42163,16 +42083,16 @@
       <c r="A9" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9">
         <v>10</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9">
         <v>2</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9">
         <v>13</v>
       </c>
     </row>
@@ -42180,16 +42100,16 @@
       <c r="A10" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10">
         <v>5</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10">
         <v>9</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10">
         <v>15</v>
       </c>
     </row>
@@ -42197,16 +42117,16 @@
       <c r="A11" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11">
         <v>11</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11">
         <v>1</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11">
         <v>13</v>
       </c>
     </row>
@@ -42214,16 +42134,16 @@
       <c r="A12" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B12" s="32">
+      <c r="B12">
         <v>7</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12">
         <v>2</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12">
         <v>3</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12">
         <v>12</v>
       </c>
     </row>
@@ -42231,14 +42151,13 @@
       <c r="A13" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32">
+      <c r="C13">
         <v>11</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13">
         <v>2</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13">
         <v>13</v>
       </c>
     </row>
@@ -42246,16 +42165,16 @@
       <c r="A14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="32">
+      <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14">
         <v>2</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14">
         <v>10</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14">
         <v>13</v>
       </c>
     </row>
@@ -42263,16 +42182,16 @@
       <c r="A15" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B15" s="32">
+      <c r="B15">
         <v>8</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15">
         <v>1</v>
       </c>
-      <c r="D15" s="32">
+      <c r="D15">
         <v>3</v>
       </c>
-      <c r="E15" s="32">
+      <c r="E15">
         <v>12</v>
       </c>
     </row>
@@ -42280,16 +42199,16 @@
       <c r="A16" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="32">
+      <c r="B16">
         <v>3</v>
       </c>
-      <c r="C16" s="32">
+      <c r="C16">
         <v>5</v>
       </c>
-      <c r="D16" s="32">
+      <c r="D16">
         <v>5</v>
       </c>
-      <c r="E16" s="32">
+      <c r="E16">
         <v>13</v>
       </c>
     </row>
@@ -42297,16 +42216,16 @@
       <c r="A17" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17">
         <v>6</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17">
         <v>4</v>
       </c>
-      <c r="D17" s="32">
+      <c r="D17">
         <v>4</v>
       </c>
-      <c r="E17" s="32">
+      <c r="E17">
         <v>14</v>
       </c>
     </row>
@@ -42314,16 +42233,16 @@
       <c r="A18" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B18" s="32">
+      <c r="B18">
         <v>8</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18">
         <v>2</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18">
         <v>1</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E18">
         <v>11</v>
       </c>
     </row>
@@ -42331,16 +42250,16 @@
       <c r="A19" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B19" s="32">
+      <c r="B19">
         <v>1</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19">
         <v>10</v>
       </c>
-      <c r="D19" s="32">
+      <c r="D19">
         <v>2</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E19">
         <v>13</v>
       </c>
     </row>
@@ -42348,12 +42267,10 @@
       <c r="A20" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="B20" s="32">
+      <c r="B20">
         <v>12</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32">
+      <c r="E20">
         <v>12</v>
       </c>
     </row>
@@ -42361,16 +42278,16 @@
       <c r="A21" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B21" s="32">
+      <c r="B21">
         <v>1</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21">
         <v>5</v>
       </c>
-      <c r="D21" s="32">
+      <c r="D21">
         <v>7</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21">
         <v>13</v>
       </c>
     </row>
@@ -42378,16 +42295,16 @@
       <c r="A22" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="B22" s="32">
+      <c r="B22">
         <v>67</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22">
         <v>64</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22">
         <v>50</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22">
         <v>181</v>
       </c>
     </row>
@@ -42436,14 +42353,13 @@
       <c r="A59" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B59" s="32">
+      <c r="B59">
         <v>7</v>
       </c>
-      <c r="C59" s="32">
+      <c r="C59">
         <v>7</v>
       </c>
-      <c r="D59" s="32"/>
-      <c r="E59" s="32">
+      <c r="E59">
         <v>14</v>
       </c>
     </row>
@@ -42451,16 +42367,16 @@
       <c r="A60" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B60" s="32">
+      <c r="B60">
         <v>6</v>
       </c>
-      <c r="C60" s="32">
+      <c r="C60">
         <v>1</v>
       </c>
-      <c r="D60" s="32">
+      <c r="D60">
         <v>6</v>
       </c>
-      <c r="E60" s="32">
+      <c r="E60">
         <v>13</v>
       </c>
     </row>
@@ -42468,16 +42384,16 @@
       <c r="A61" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B61" s="32">
+      <c r="B61">
         <v>3</v>
       </c>
-      <c r="C61" s="32">
+      <c r="C61">
         <v>9</v>
       </c>
-      <c r="D61" s="32">
+      <c r="D61">
         <v>3</v>
       </c>
-      <c r="E61" s="32">
+      <c r="E61">
         <v>15</v>
       </c>
     </row>
@@ -42485,12 +42401,10 @@
       <c r="A62" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="32"/>
-      <c r="C62" s="32">
+      <c r="C62">
         <v>13</v>
       </c>
-      <c r="D62" s="32"/>
-      <c r="E62" s="32">
+      <c r="E62">
         <v>13</v>
       </c>
     </row>
@@ -42498,14 +42412,13 @@
       <c r="A63" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B63" s="32">
+      <c r="B63">
         <v>10</v>
       </c>
-      <c r="C63" s="32">
+      <c r="C63">
         <v>2</v>
       </c>
-      <c r="D63" s="32"/>
-      <c r="E63" s="32">
+      <c r="E63">
         <v>12</v>
       </c>
     </row>
@@ -42513,16 +42426,16 @@
       <c r="A64" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B64" s="32">
+      <c r="B64">
         <v>3</v>
       </c>
-      <c r="C64" s="32">
+      <c r="C64">
         <v>9</v>
       </c>
-      <c r="D64" s="32">
+      <c r="D64">
         <v>1</v>
       </c>
-      <c r="E64" s="32">
+      <c r="E64">
         <v>13</v>
       </c>
     </row>
@@ -42530,16 +42443,16 @@
       <c r="A65" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B65" s="32">
+      <c r="B65">
         <v>7</v>
       </c>
-      <c r="C65" s="32">
+      <c r="C65">
         <v>3</v>
       </c>
-      <c r="D65" s="32">
+      <c r="D65">
         <v>3</v>
       </c>
-      <c r="E65" s="32">
+      <c r="E65">
         <v>13</v>
       </c>
     </row>
@@ -42547,16 +42460,16 @@
       <c r="A66" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B66" s="32">
+      <c r="B66">
         <v>9</v>
       </c>
-      <c r="C66" s="32">
+      <c r="C66">
         <v>2</v>
       </c>
-      <c r="D66" s="32">
+      <c r="D66">
         <v>1</v>
       </c>
-      <c r="E66" s="32">
+      <c r="E66">
         <v>12</v>
       </c>
     </row>
@@ -42564,12 +42477,10 @@
       <c r="A67" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B67" s="32"/>
-      <c r="C67" s="32">
+      <c r="C67">
         <v>13</v>
       </c>
-      <c r="D67" s="32"/>
-      <c r="E67" s="32">
+      <c r="E67">
         <v>13</v>
       </c>
     </row>
@@ -42577,16 +42488,16 @@
       <c r="A68" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B68" s="32">
+      <c r="B68">
         <v>7</v>
       </c>
-      <c r="C68" s="32">
+      <c r="C68">
         <v>3</v>
       </c>
-      <c r="D68" s="32">
+      <c r="D68">
         <v>4</v>
       </c>
-      <c r="E68" s="32">
+      <c r="E68">
         <v>14</v>
       </c>
     </row>
@@ -42594,14 +42505,13 @@
       <c r="A69" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B69" s="32">
+      <c r="B69">
         <v>2</v>
       </c>
-      <c r="C69" s="32">
+      <c r="C69">
         <v>9</v>
       </c>
-      <c r="D69" s="32"/>
-      <c r="E69" s="32">
+      <c r="E69">
         <v>11</v>
       </c>
     </row>
@@ -42609,16 +42519,16 @@
       <c r="A70" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B70" s="32">
+      <c r="B70">
         <v>11</v>
       </c>
-      <c r="C70" s="32">
+      <c r="C70">
         <v>1</v>
       </c>
-      <c r="D70" s="32">
+      <c r="D70">
         <v>1</v>
       </c>
-      <c r="E70" s="32">
+      <c r="E70">
         <v>13</v>
       </c>
     </row>
@@ -42626,14 +42536,13 @@
       <c r="A71" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="B71" s="32">
+      <c r="B71">
         <v>10</v>
       </c>
-      <c r="C71" s="32"/>
-      <c r="D71" s="32">
+      <c r="D71">
         <v>2</v>
       </c>
-      <c r="E71" s="32">
+      <c r="E71">
         <v>12</v>
       </c>
     </row>
@@ -42641,14 +42550,13 @@
       <c r="A72" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B72" s="32">
+      <c r="B72">
         <v>6</v>
       </c>
-      <c r="C72" s="32">
+      <c r="C72">
         <v>7</v>
       </c>
-      <c r="D72" s="32"/>
-      <c r="E72" s="32">
+      <c r="E72">
         <v>13</v>
       </c>
     </row>
@@ -42656,16 +42564,16 @@
       <c r="A73" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="B73" s="32">
+      <c r="B73">
         <v>81</v>
       </c>
-      <c r="C73" s="32">
+      <c r="C73">
         <v>79</v>
       </c>
-      <c r="D73" s="32">
+      <c r="D73">
         <v>21</v>
       </c>
-      <c r="E73" s="32">
+      <c r="E73">
         <v>181</v>
       </c>
     </row>
@@ -42740,10 +42648,10 @@
       <c r="X107" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="AI107" s="34" t="s">
+      <c r="AI107" s="33" t="s">
         <v>262</v>
       </c>
-      <c r="AJ107" s="36" t="s">
+      <c r="AJ107" s="32" t="s">
         <v>1091</v>
       </c>
     </row>
@@ -42760,31 +42668,31 @@
       <c r="D108" t="s">
         <v>263</v>
       </c>
-      <c r="K108" s="34" t="s">
+      <c r="K108" s="33" t="s">
         <v>262</v>
       </c>
-      <c r="L108" s="36" t="s">
+      <c r="L108" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="M108" s="36" t="s">
+      <c r="M108" s="32" t="s">
         <v>263</v>
       </c>
       <c r="N108" s="20"/>
       <c r="O108" s="20"/>
       <c r="P108" s="20"/>
-      <c r="W108" s="34" t="s">
+      <c r="W108" s="33" t="s">
         <v>262</v>
       </c>
       <c r="X108" t="s">
         <v>43</v>
       </c>
-      <c r="Y108" s="36" t="s">
+      <c r="Y108" s="32" t="s">
         <v>263</v>
       </c>
-      <c r="AI108" s="35" t="s">
+      <c r="AI108" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="AJ108" s="33">
+      <c r="AJ108" s="32">
         <v>10</v>
       </c>
     </row>
@@ -42792,38 +42700,37 @@
       <c r="A109" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B109" s="32">
+      <c r="B109">
         <v>606.1869999999999</v>
       </c>
-      <c r="C109" s="32"/>
-      <c r="D109" s="32">
+      <c r="D109">
         <v>606.1869999999999</v>
       </c>
-      <c r="K109" s="35" t="s">
+      <c r="K109" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="L109" s="33">
+      <c r="L109" s="32">
         <v>7</v>
       </c>
-      <c r="M109" s="33">
+      <c r="M109" s="32">
         <v>7</v>
       </c>
       <c r="N109" s="20"/>
       <c r="O109" s="20"/>
       <c r="P109" s="20"/>
-      <c r="W109" s="35" t="s">
+      <c r="W109" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="X109" s="33">
+      <c r="X109" s="32">
         <v>2</v>
       </c>
-      <c r="Y109" s="33">
+      <c r="Y109" s="32">
         <v>2</v>
       </c>
-      <c r="AI109" s="35" t="s">
+      <c r="AI109" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="AJ109" s="33">
+      <c r="AJ109" s="32">
         <v>9</v>
       </c>
     </row>
@@ -42831,38 +42738,37 @@
       <c r="A110" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B110" s="32"/>
-      <c r="C110" s="32">
+      <c r="C110">
         <v>629.04100000000005</v>
       </c>
-      <c r="D110" s="32">
+      <c r="D110">
         <v>629.04100000000005</v>
       </c>
-      <c r="K110" s="35" t="s">
+      <c r="K110" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="L110" s="33">
+      <c r="L110" s="32">
         <v>1</v>
       </c>
-      <c r="M110" s="33">
+      <c r="M110" s="32">
         <v>1</v>
       </c>
       <c r="N110" s="20"/>
       <c r="O110" s="20"/>
       <c r="P110" s="20"/>
-      <c r="W110" s="35" t="s">
+      <c r="W110" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="X110" s="33">
+      <c r="X110" s="32">
         <v>1</v>
       </c>
-      <c r="Y110" s="33">
+      <c r="Y110" s="32">
         <v>1</v>
       </c>
-      <c r="AI110" s="35" t="s">
+      <c r="AI110" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="AJ110" s="33">
+      <c r="AJ110" s="32">
         <v>11</v>
       </c>
     </row>
@@ -42870,40 +42776,40 @@
       <c r="A111" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B111" s="32">
+      <c r="B111">
         <v>399.06900000000002</v>
       </c>
-      <c r="C111" s="32">
+      <c r="C111">
         <v>165.02199999999999</v>
       </c>
-      <c r="D111" s="32">
+      <c r="D111">
         <v>564.09100000000001</v>
       </c>
-      <c r="K111" s="35" t="s">
+      <c r="K111" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="L111" s="33">
+      <c r="L111" s="32">
         <v>9</v>
       </c>
-      <c r="M111" s="33">
+      <c r="M111" s="32">
         <v>9</v>
       </c>
       <c r="N111" s="20"/>
       <c r="O111" s="20"/>
       <c r="P111" s="20"/>
-      <c r="W111" s="35" t="s">
+      <c r="W111" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="X111" s="33">
+      <c r="X111" s="32">
         <v>9</v>
       </c>
-      <c r="Y111" s="33">
+      <c r="Y111" s="32">
         <v>9</v>
       </c>
-      <c r="AI111" s="35" t="s">
+      <c r="AI111" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="AJ111" s="33">
+      <c r="AJ111" s="32">
         <v>9</v>
       </c>
     </row>
@@ -42911,38 +42817,37 @@
       <c r="A112" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B112" s="32">
+      <c r="B112">
         <v>722.3309999999999</v>
       </c>
-      <c r="C112" s="32"/>
-      <c r="D112" s="32">
+      <c r="D112">
         <v>722.3309999999999</v>
       </c>
-      <c r="K112" s="35" t="s">
+      <c r="K112" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="L112" s="33">
+      <c r="L112" s="32">
         <v>13</v>
       </c>
-      <c r="M112" s="33">
+      <c r="M112" s="32">
         <v>13</v>
       </c>
       <c r="N112" s="20"/>
       <c r="O112" s="20"/>
       <c r="P112" s="20"/>
-      <c r="W112" s="35" t="s">
+      <c r="W112" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="X112" s="33">
+      <c r="X112" s="32">
         <v>1</v>
       </c>
-      <c r="Y112" s="33">
+      <c r="Y112" s="32">
         <v>1</v>
       </c>
-      <c r="AI112" s="35" t="s">
+      <c r="AI112" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="AJ112" s="33">
+      <c r="AJ112" s="32">
         <v>8</v>
       </c>
     </row>
@@ -42950,38 +42855,37 @@
       <c r="A113" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B113" s="32"/>
-      <c r="C113" s="32">
+      <c r="C113">
         <v>399.66999999999996</v>
       </c>
-      <c r="D113" s="32">
+      <c r="D113">
         <v>399.66999999999996</v>
       </c>
-      <c r="K113" s="35" t="s">
+      <c r="K113" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="L113" s="33">
+      <c r="L113" s="32">
         <v>2</v>
       </c>
-      <c r="M113" s="33">
+      <c r="M113" s="32">
         <v>2</v>
       </c>
       <c r="N113" s="20"/>
       <c r="O113" s="20"/>
       <c r="P113" s="20"/>
-      <c r="W113" s="35" t="s">
+      <c r="W113" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="X113" s="33">
+      <c r="X113" s="32">
         <v>3</v>
       </c>
-      <c r="Y113" s="33">
+      <c r="Y113" s="32">
         <v>3</v>
       </c>
-      <c r="AI113" s="35" t="s">
+      <c r="AI113" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="AJ113" s="33">
+      <c r="AJ113" s="32">
         <v>9</v>
       </c>
     </row>
@@ -42989,38 +42893,37 @@
       <c r="A114" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B114" s="32">
+      <c r="B114">
         <v>469.54300000000001</v>
       </c>
-      <c r="C114" s="32"/>
-      <c r="D114" s="32">
+      <c r="D114">
         <v>469.54300000000001</v>
       </c>
-      <c r="K114" s="35" t="s">
+      <c r="K114" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="L114" s="33">
+      <c r="L114" s="32">
         <v>9</v>
       </c>
-      <c r="M114" s="33">
+      <c r="M114" s="32">
         <v>9</v>
       </c>
       <c r="N114" s="20"/>
       <c r="O114" s="20"/>
       <c r="P114" s="20"/>
-      <c r="W114" s="35" t="s">
+      <c r="W114" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="X114" s="33">
+      <c r="X114" s="32">
         <v>2</v>
       </c>
-      <c r="Y114" s="33">
+      <c r="Y114" s="32">
         <v>2</v>
       </c>
-      <c r="AI114" s="35" t="s">
+      <c r="AI114" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="AJ114" s="33">
+      <c r="AJ114" s="32">
         <v>9</v>
       </c>
     </row>
@@ -43028,38 +42931,37 @@
       <c r="A115" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B115" s="32">
+      <c r="B115">
         <v>684.553</v>
       </c>
-      <c r="C115" s="32"/>
-      <c r="D115" s="32">
+      <c r="D115">
         <v>684.553</v>
       </c>
-      <c r="K115" s="35" t="s">
+      <c r="K115" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="L115" s="33">
+      <c r="L115" s="32">
         <v>3</v>
       </c>
-      <c r="M115" s="33">
+      <c r="M115" s="32">
         <v>3</v>
       </c>
       <c r="N115" s="20"/>
       <c r="O115" s="20"/>
       <c r="P115" s="20"/>
-      <c r="W115" s="35" t="s">
+      <c r="W115" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="X115" s="33">
+      <c r="X115" s="32">
         <v>10</v>
       </c>
-      <c r="Y115" s="33">
+      <c r="Y115" s="32">
         <v>10</v>
       </c>
-      <c r="AI115" s="35" t="s">
+      <c r="AI115" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="AJ115" s="33">
+      <c r="AJ115" s="32">
         <v>8</v>
       </c>
     </row>
@@ -43067,38 +42969,37 @@
       <c r="A116" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B116" s="32"/>
-      <c r="C116" s="32">
+      <c r="C116">
         <v>919.75</v>
       </c>
-      <c r="D116" s="32">
+      <c r="D116">
         <v>919.75</v>
       </c>
-      <c r="K116" s="35" t="s">
+      <c r="K116" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="L116" s="33">
+      <c r="L116" s="32">
         <v>2</v>
       </c>
-      <c r="M116" s="33">
+      <c r="M116" s="32">
         <v>2</v>
       </c>
       <c r="N116" s="20"/>
       <c r="O116" s="20"/>
       <c r="P116" s="20"/>
-      <c r="W116" s="35" t="s">
+      <c r="W116" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="X116" s="33">
+      <c r="X116" s="32">
         <v>3</v>
       </c>
-      <c r="Y116" s="33">
+      <c r="Y116" s="32">
         <v>3</v>
       </c>
-      <c r="AI116" s="35" t="s">
+      <c r="AI116" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="AJ116" s="33">
+      <c r="AJ116" s="32">
         <v>9</v>
       </c>
     </row>
@@ -43106,38 +43007,37 @@
       <c r="A117" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B117" s="32">
+      <c r="B117">
         <v>492.46</v>
       </c>
-      <c r="C117" s="32"/>
-      <c r="D117" s="32">
+      <c r="D117">
         <v>492.46</v>
       </c>
-      <c r="K117" s="35" t="s">
+      <c r="K117" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="L117" s="33">
+      <c r="L117" s="32">
         <v>13</v>
       </c>
-      <c r="M117" s="33">
+      <c r="M117" s="32">
         <v>13</v>
       </c>
       <c r="N117" s="20"/>
       <c r="O117" s="20"/>
       <c r="P117" s="20"/>
-      <c r="W117" s="35" t="s">
+      <c r="W117" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="X117" s="33">
+      <c r="X117" s="32">
         <v>5</v>
       </c>
-      <c r="Y117" s="33">
+      <c r="Y117" s="32">
         <v>5</v>
       </c>
-      <c r="AI117" s="35" t="s">
+      <c r="AI117" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="AJ117" s="33">
+      <c r="AJ117" s="32">
         <v>9</v>
       </c>
     </row>
@@ -43145,38 +43045,37 @@
       <c r="A118" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B118" s="32">
+      <c r="B118">
         <v>1062.953</v>
       </c>
-      <c r="C118" s="32"/>
-      <c r="D118" s="32">
+      <c r="D118">
         <v>1062.953</v>
       </c>
-      <c r="K118" s="35" t="s">
+      <c r="K118" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="L118" s="33">
+      <c r="L118" s="32">
         <v>3</v>
       </c>
-      <c r="M118" s="33">
+      <c r="M118" s="32">
         <v>3</v>
       </c>
       <c r="N118" s="20"/>
       <c r="O118" s="20"/>
       <c r="P118" s="20"/>
-      <c r="W118" s="35" t="s">
+      <c r="W118" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="X118" s="33">
+      <c r="X118" s="32">
         <v>4</v>
       </c>
-      <c r="Y118" s="33">
+      <c r="Y118" s="32">
         <v>4</v>
       </c>
-      <c r="AI118" s="35" t="s">
+      <c r="AI118" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="AJ118" s="33">
+      <c r="AJ118" s="32">
         <v>7</v>
       </c>
     </row>
@@ -43184,38 +43083,37 @@
       <c r="A119" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B119" s="32"/>
-      <c r="C119" s="32">
+      <c r="C119">
         <v>394.79400000000004</v>
       </c>
-      <c r="D119" s="32">
+      <c r="D119">
         <v>394.79400000000004</v>
       </c>
-      <c r="K119" s="35" t="s">
+      <c r="K119" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="L119" s="33">
+      <c r="L119" s="32">
         <v>9</v>
       </c>
-      <c r="M119" s="33">
+      <c r="M119" s="32">
         <v>9</v>
       </c>
       <c r="N119" s="20"/>
       <c r="O119" s="20"/>
       <c r="P119" s="20"/>
-      <c r="W119" s="35" t="s">
+      <c r="W119" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="X119" s="33">
+      <c r="X119" s="32">
         <v>1</v>
       </c>
-      <c r="Y119" s="33">
+      <c r="Y119" s="32">
         <v>1</v>
       </c>
-      <c r="AI119" s="35" t="s">
+      <c r="AI119" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="AJ119" s="33">
+      <c r="AJ119" s="32">
         <v>10</v>
       </c>
     </row>
@@ -43223,40 +43121,40 @@
       <c r="A120" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B120" s="32">
+      <c r="B120">
         <v>522.69000000000005</v>
       </c>
-      <c r="C120" s="32">
+      <c r="C120">
         <v>45.506</v>
       </c>
-      <c r="D120" s="32">
+      <c r="D120">
         <v>568.19600000000003</v>
       </c>
-      <c r="K120" s="35" t="s">
+      <c r="K120" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="L120" s="33">
+      <c r="L120" s="32">
         <v>1</v>
       </c>
-      <c r="M120" s="33">
+      <c r="M120" s="32">
         <v>1</v>
       </c>
       <c r="N120" s="20"/>
       <c r="O120" s="20"/>
       <c r="P120" s="20"/>
-      <c r="W120" s="35" t="s">
+      <c r="W120" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="X120" s="33">
+      <c r="X120" s="32">
         <v>2</v>
       </c>
-      <c r="Y120" s="33">
+      <c r="Y120" s="32">
         <v>2</v>
       </c>
       <c r="AI120" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="AJ120" s="33">
+      <c r="AJ120" s="32">
         <v>8</v>
       </c>
     </row>
@@ -43264,38 +43162,37 @@
       <c r="A121" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="B121" s="32"/>
-      <c r="C121" s="32">
+      <c r="C121">
         <v>646.245</v>
       </c>
-      <c r="D121" s="32">
+      <c r="D121">
         <v>646.245</v>
       </c>
-      <c r="K121" s="35" t="s">
+      <c r="K121" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="L121" s="33">
+      <c r="L121" s="32">
         <v>7</v>
       </c>
-      <c r="M121" s="33">
+      <c r="M121" s="32">
         <v>7</v>
       </c>
       <c r="N121" s="20"/>
       <c r="O121" s="20"/>
       <c r="P121" s="20"/>
-      <c r="W121" s="35" t="s">
+      <c r="W121" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="X121" s="33">
+      <c r="X121" s="32">
         <v>7</v>
       </c>
-      <c r="Y121" s="33">
+      <c r="Y121" s="32">
         <v>7</v>
       </c>
-      <c r="AI121" s="35" t="s">
+      <c r="AI121" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="AJ121" s="33">
+      <c r="AJ121" s="32">
         <v>9</v>
       </c>
     </row>
@@ -43303,40 +43200,40 @@
       <c r="A122" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B122" s="32">
+      <c r="B122">
         <v>377.77300000000008</v>
       </c>
-      <c r="C122" s="32">
+      <c r="C122">
         <v>46.487000000000002</v>
       </c>
-      <c r="D122" s="32">
+      <c r="D122">
         <v>424.2600000000001</v>
       </c>
-      <c r="K122" s="35" t="s">
+      <c r="K122" s="34" t="s">
         <v>263</v>
       </c>
-      <c r="L122" s="33">
+      <c r="L122" s="32">
         <v>79</v>
       </c>
-      <c r="M122" s="33">
+      <c r="M122" s="32">
         <v>79</v>
       </c>
       <c r="N122" s="20"/>
       <c r="O122" s="20"/>
       <c r="P122" s="20"/>
-      <c r="W122" s="35" t="s">
+      <c r="W122" s="34" t="s">
         <v>263</v>
       </c>
-      <c r="X122" s="33">
+      <c r="X122" s="32">
         <v>50</v>
       </c>
-      <c r="Y122" s="33">
+      <c r="Y122" s="32">
         <v>50</v>
       </c>
-      <c r="AI122" s="35" t="s">
+      <c r="AI122" s="34" t="s">
         <v>263</v>
       </c>
-      <c r="AJ122" s="33">
+      <c r="AJ122" s="32">
         <v>125</v>
       </c>
     </row>
@@ -43344,13 +43241,13 @@
       <c r="A123" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="B123" s="32">
+      <c r="B123">
         <v>5337.5590000000002</v>
       </c>
-      <c r="C123" s="32">
+      <c r="C123">
         <v>3246.5149999999999</v>
       </c>
-      <c r="D123" s="32">
+      <c r="D123">
         <v>8584.0739999999987</v>
       </c>
       <c r="K123" s="20"/>
@@ -59492,7 +59389,7 @@
         <v>-75.569377000000003</v>
       </c>
       <c r="AM131" s="26">
-        <f t="shared" ref="AM131:AM177" si="2">IF(N131="INICIO TARDÍO",M131,0)+IF(R131="TERMINÓ ANTES",Q131,0)</f>
+        <f t="shared" ref="AM131:AM191" si="2">IF(N131="INICIO TARDÍO",M131,0)+IF(R131="TERMINÓ ANTES",Q131,0)</f>
         <v>0</v>
       </c>
       <c r="AN131" s="9"/>
@@ -65103,7 +65000,7 @@
       </c>
       <c r="AN177" s="9"/>
     </row>
-    <row r="178" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:40" ht="15" x14ac:dyDescent="0.25">
       <c r="A178" s="9" t="s">
         <v>1557</v>
       </c>
@@ -65218,9 +65115,13 @@
       <c r="AL178" s="9">
         <v>-75.602017000000004</v>
       </c>
+      <c r="AM178" s="26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="AN178" s="9"/>
     </row>
-    <row r="179" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:40" ht="15" x14ac:dyDescent="0.25">
       <c r="A179" s="9" t="s">
         <v>1564</v>
       </c>
@@ -65335,11 +65236,15 @@
       <c r="AL179" s="9">
         <v>-75.540291999999994</v>
       </c>
+      <c r="AM179" s="26">
+        <f t="shared" si="2"/>
+        <v>2.237268518518519E-2</v>
+      </c>
       <c r="AN179" s="9" t="s">
         <v>1596</v>
       </c>
     </row>
-    <row r="180" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:40" ht="15" x14ac:dyDescent="0.25">
       <c r="A180" s="9" t="s">
         <v>1572</v>
       </c>
@@ -65454,9 +65359,13 @@
       <c r="AL180" s="9">
         <v>-75.546537000000001</v>
       </c>
+      <c r="AM180" s="26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="AN180" s="9"/>
     </row>
-    <row r="181" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:40" ht="15" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
         <v>1580</v>
       </c>
@@ -65571,9 +65480,13 @@
       <c r="AL181" s="9">
         <v>-75.571967000000001</v>
       </c>
+      <c r="AM181" s="26">
+        <f t="shared" si="2"/>
+        <v>0.11057870370370371</v>
+      </c>
       <c r="AN181" s="9"/>
     </row>
-    <row r="182" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:40" ht="15" x14ac:dyDescent="0.25">
       <c r="A182" s="9" t="s">
         <v>1588</v>
       </c>
@@ -65688,33 +65601,1101 @@
       <c r="AL182" s="9">
         <v>-75.599374999999995</v>
       </c>
+      <c r="AM182" s="26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="AN182" s="9"/>
     </row>
-    <row r="183" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A183" s="9" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B183" s="9" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C183" s="9" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D183" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E183" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F183" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="G183" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H183" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I183" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J183" s="9">
+        <v>6065</v>
+      </c>
+      <c r="K183" s="9" t="s">
+        <v>1601</v>
+      </c>
+      <c r="L183" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M183" s="10">
+        <v>3.636782407407408E-3</v>
+      </c>
+      <c r="N183" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O183" s="9" t="s">
+        <v>1602</v>
+      </c>
+      <c r="P183" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q183" s="10">
+        <v>2.58599537037037E-3</v>
+      </c>
+      <c r="R183" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S183" s="10">
+        <v>0.31144921296296302</v>
+      </c>
+      <c r="T183" s="9">
+        <v>44.219000000000001</v>
+      </c>
+      <c r="U183" s="9">
+        <v>11.09</v>
+      </c>
+      <c r="V183" s="10">
+        <v>0.16620723379629629</v>
+      </c>
+      <c r="W183" s="10">
+        <v>0.1129801967592593</v>
+      </c>
+      <c r="X183" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y183" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD183" s="9">
+        <v>4</v>
+      </c>
+      <c r="AE183" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF183" s="9" t="s">
+        <v>1603</v>
+      </c>
+      <c r="AG183" s="9" t="s">
+        <v>1604</v>
+      </c>
+      <c r="AH183" s="9">
+        <v>6.2256109999999998</v>
+      </c>
+      <c r="AI183" s="9">
+        <v>-75.599078000000006</v>
+      </c>
+      <c r="AJ183" s="9" t="s">
+        <v>1605</v>
+      </c>
+      <c r="AK183" s="9">
+        <v>6.2387639999999998</v>
+      </c>
+      <c r="AL183" s="9">
+        <v>-75.607866000000001</v>
+      </c>
+      <c r="AM183" s="26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="AN183" s="9"/>
     </row>
-    <row r="184" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A184" s="9" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B184" s="9" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C184" s="9" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D184" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E184" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F184" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="G184" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H184" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I184" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J184" s="9">
+        <v>1949</v>
+      </c>
+      <c r="K184" s="9" t="s">
+        <v>1609</v>
+      </c>
+      <c r="L184" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M184" s="10">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="N184" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O184" s="9" t="s">
+        <v>1610</v>
+      </c>
+      <c r="P184" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q184" s="10">
+        <v>9.7222222222222219E-4</v>
+      </c>
+      <c r="R184" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S184" s="10">
+        <v>0.31374999999999997</v>
+      </c>
+      <c r="T184" s="9">
+        <v>27.864000000000001</v>
+      </c>
+      <c r="U184" s="9">
+        <v>5.21</v>
+      </c>
+      <c r="V184" s="10">
+        <v>0.22270833333333331</v>
+      </c>
+      <c r="W184" s="10">
+        <v>0.18104166666666671</v>
+      </c>
+      <c r="X184" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y184" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z184" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA184" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB184" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC184" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD184" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE184" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF184" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="AG184" s="9" t="s">
+        <v>1611</v>
+      </c>
+      <c r="AH184" s="9">
+        <v>6.2256970000000003</v>
+      </c>
+      <c r="AI184" s="9">
+        <v>-75.599435999999997</v>
+      </c>
+      <c r="AJ184" s="9" t="s">
+        <v>1612</v>
+      </c>
+      <c r="AK184" s="9">
+        <v>6.2477609999999997</v>
+      </c>
+      <c r="AL184" s="9">
+        <v>-75.614859999999993</v>
+      </c>
+      <c r="AM184" s="26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="AN184" s="9"/>
     </row>
-    <row r="185" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A185" s="9" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B185" s="9" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C185" s="9" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D185" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E185" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F185" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="G185" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="H185" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I185" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J185" s="9">
+        <v>1910</v>
+      </c>
+      <c r="K185" s="9" t="s">
+        <v>1616</v>
+      </c>
+      <c r="L185" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M185" s="10">
+        <v>5.5324074074074078E-3</v>
+      </c>
+      <c r="N185" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O185" s="9" t="s">
+        <v>1617</v>
+      </c>
+      <c r="P185" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q185" s="10">
+        <v>1.1898148148148151E-2</v>
+      </c>
+      <c r="R185" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S185" s="10">
+        <v>0.29506944444444438</v>
+      </c>
+      <c r="T185" s="9">
+        <v>25.187999999999999</v>
+      </c>
+      <c r="U185" s="9">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="V185" s="10">
+        <v>0.21243055555555559</v>
+      </c>
+      <c r="W185" s="10">
+        <v>0.17155092592592591</v>
+      </c>
+      <c r="X185" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y185" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z185" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA185" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB185" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC185" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD185" s="9">
+        <v>2</v>
+      </c>
+      <c r="AE185" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF185" s="9" t="s">
+        <v>1618</v>
+      </c>
+      <c r="AG185" s="9" t="s">
+        <v>1619</v>
+      </c>
+      <c r="AH185" s="9">
+        <v>6.2308159999999999</v>
+      </c>
+      <c r="AI185" s="9">
+        <v>-75.601883999999998</v>
+      </c>
+      <c r="AJ185" s="9" t="s">
+        <v>1620</v>
+      </c>
+      <c r="AK185" s="9">
+        <v>6.239649</v>
+      </c>
+      <c r="AL185" s="9">
+        <v>-75.608310000000003</v>
+      </c>
+      <c r="AM185" s="26">
+        <f t="shared" si="2"/>
+        <v>1.1898148148148151E-2</v>
+      </c>
       <c r="AN185" s="9"/>
     </row>
-    <row r="186" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A186" s="9" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B186" s="9" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C186" s="9" t="s">
+        <v>1623</v>
+      </c>
+      <c r="D186" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E186" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F186" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="G186" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H186" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I186" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J186" s="9">
+        <v>2871</v>
+      </c>
+      <c r="K186" s="9" t="s">
+        <v>1624</v>
+      </c>
+      <c r="L186" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M186" s="10">
+        <v>9.6874999999999999E-3</v>
+      </c>
+      <c r="N186" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O186" s="9" t="s">
+        <v>1625</v>
+      </c>
+      <c r="P186" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q186" s="10">
+        <v>0.16314814814814821</v>
+      </c>
+      <c r="R186" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S186" s="10">
+        <v>0.13966435185185189</v>
+      </c>
+      <c r="T186" s="9">
+        <v>39.378</v>
+      </c>
+      <c r="U186" s="9">
+        <v>14.69</v>
+      </c>
+      <c r="V186" s="10">
+        <v>0.1116550925925926</v>
+      </c>
+      <c r="W186" s="10">
+        <v>6.25E-2</v>
+      </c>
+      <c r="X186" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y186" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z186" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA186" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB186" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC186" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD186" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE186" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF186" s="9" t="s">
+        <v>1626</v>
+      </c>
+      <c r="AG186" s="9" t="s">
+        <v>1627</v>
+      </c>
+      <c r="AH186" s="9">
+        <v>6.2256850000000004</v>
+      </c>
+      <c r="AI186" s="9">
+        <v>-75.599091000000001</v>
+      </c>
+      <c r="AJ186" s="9" t="s">
+        <v>1628</v>
+      </c>
+      <c r="AK186" s="9">
+        <v>6.2371379999999998</v>
+      </c>
+      <c r="AL186" s="9">
+        <v>-75.558725999999993</v>
+      </c>
+      <c r="AM186" s="26">
+        <f t="shared" si="2"/>
+        <v>0.16314814814814821</v>
+      </c>
       <c r="AN186" s="9"/>
     </row>
-    <row r="187" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A187" s="9" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B187" s="9" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C187" s="9" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D187" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E187" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F187" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="G187" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H187" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I187" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J187" s="9">
+        <v>5700</v>
+      </c>
+      <c r="K187" s="9" t="s">
+        <v>1632</v>
+      </c>
+      <c r="L187" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M187" s="10">
+        <v>1.143086805555556E-2</v>
+      </c>
+      <c r="N187" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O187" s="9" t="s">
+        <v>1633</v>
+      </c>
+      <c r="P187" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q187" s="10">
+        <v>3.6722222222222218E-4</v>
+      </c>
+      <c r="R187" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S187" s="10">
+        <v>0.30143635416666659</v>
+      </c>
+      <c r="T187" s="9">
+        <v>36.863</v>
+      </c>
+      <c r="U187" s="9">
+        <v>22.3</v>
+      </c>
+      <c r="V187" s="10">
+        <v>6.8876597222222224E-2</v>
+      </c>
+      <c r="W187" s="10">
+        <v>2.4076944444444449E-2</v>
+      </c>
+      <c r="X187" s="10">
+        <v>5.5171064814814813E-3</v>
+      </c>
+      <c r="Y187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD187" s="9">
+        <v>11</v>
+      </c>
+      <c r="AE187" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF187" s="9" t="s">
+        <v>1634</v>
+      </c>
+      <c r="AG187" s="9" t="s">
+        <v>1635</v>
+      </c>
+      <c r="AH187" s="9">
+        <v>6.2256049999999998</v>
+      </c>
+      <c r="AI187" s="9">
+        <v>-75.599091000000001</v>
+      </c>
+      <c r="AJ187" s="9" t="s">
+        <v>1636</v>
+      </c>
+      <c r="AK187" s="9">
+        <v>6.2467709999999999</v>
+      </c>
+      <c r="AL187" s="9">
+        <v>-75.554137999999995</v>
+      </c>
+      <c r="AM187" s="26">
+        <f t="shared" si="2"/>
+        <v>1.143086805555556E-2</v>
+      </c>
       <c r="AN187" s="9"/>
     </row>
-    <row r="188" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="AN188" s="9"/>
+    <row r="188" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A188" s="9" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B188" s="9" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C188" s="9" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D188" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E188" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F188" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="G188" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H188" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I188" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J188" s="9">
+        <v>5344</v>
+      </c>
+      <c r="K188" s="9" t="s">
+        <v>1640</v>
+      </c>
+      <c r="L188" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M188" s="10">
+        <v>1.320601851851852E-2</v>
+      </c>
+      <c r="N188" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O188" s="9" t="s">
+        <v>1641</v>
+      </c>
+      <c r="P188" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q188" s="10">
+        <v>4.9953703703703702E-2</v>
+      </c>
+      <c r="R188" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S188" s="10">
+        <v>0.27575231481481483</v>
+      </c>
+      <c r="T188" s="9">
+        <v>72.647999999999996</v>
+      </c>
+      <c r="U188" s="9">
+        <v>15.45</v>
+      </c>
+      <c r="V188" s="10">
+        <v>0.19592592592592589</v>
+      </c>
+      <c r="W188" s="10">
+        <v>8.2939814814814813E-2</v>
+      </c>
+      <c r="X188" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y188" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z188" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA188" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB188" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC188" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD188" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE188" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF188" s="9" t="s">
+        <v>1642</v>
+      </c>
+      <c r="AG188" s="9" t="s">
+        <v>1643</v>
+      </c>
+      <c r="AH188" s="9">
+        <v>6.2266909999999998</v>
+      </c>
+      <c r="AI188" s="9">
+        <v>-75.599233999999996</v>
+      </c>
+      <c r="AJ188" s="9" t="s">
+        <v>1644</v>
+      </c>
+      <c r="AK188" s="9">
+        <v>6.2416510000000001</v>
+      </c>
+      <c r="AL188" s="9">
+        <v>-75.516547000000003</v>
+      </c>
+      <c r="AM188" s="26">
+        <f t="shared" si="2"/>
+        <v>4.9953703703703702E-2</v>
+      </c>
+      <c r="AN188" s="9" t="s">
+        <v>1670</v>
+      </c>
     </row>
-    <row r="189" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A189" s="9" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B189" s="9" t="s">
+        <v>1646</v>
+      </c>
+      <c r="C189" s="9" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D189" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E189" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F189" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="G189" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H189" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="I189" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J189" s="9">
+        <v>2704</v>
+      </c>
+      <c r="K189" s="9" t="s">
+        <v>1648</v>
+      </c>
+      <c r="L189" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M189" s="10">
+        <v>7.3032407407407404E-3</v>
+      </c>
+      <c r="N189" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O189" s="9" t="s">
+        <v>1649</v>
+      </c>
+      <c r="P189" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q189" s="10">
+        <v>2.164351851851852E-2</v>
+      </c>
+      <c r="R189" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S189" s="10">
+        <v>0.28355324074074068</v>
+      </c>
+      <c r="T189" s="9">
+        <v>34.909999999999997</v>
+      </c>
+      <c r="U189" s="9">
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="V189" s="10">
+        <v>0.16071759259259261</v>
+      </c>
+      <c r="W189" s="10">
+        <v>0.1092013888888889</v>
+      </c>
+      <c r="X189" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y189" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE189" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF189" s="9" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AG189" s="9" t="s">
+        <v>1651</v>
+      </c>
+      <c r="AH189" s="9">
+        <v>6.225759</v>
+      </c>
+      <c r="AI189" s="9">
+        <v>-75.599410000000006</v>
+      </c>
+      <c r="AJ189" s="9" t="s">
+        <v>1652</v>
+      </c>
+      <c r="AK189" s="9">
+        <v>6.3049289999999996</v>
+      </c>
+      <c r="AL189" s="9">
+        <v>-75.577501999999996</v>
+      </c>
+      <c r="AM189" s="26">
+        <f t="shared" si="2"/>
+        <v>2.164351851851852E-2</v>
+      </c>
       <c r="AN189" s="9"/>
     </row>
-    <row r="190" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A190" s="9" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B190" s="9" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C190" s="9" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D190" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E190" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F190" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="G190" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H190" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I190" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J190" s="9">
+        <v>3812</v>
+      </c>
+      <c r="K190" s="9" t="s">
+        <v>1656</v>
+      </c>
+      <c r="L190" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M190" s="10">
+        <v>1.196759259259259E-2</v>
+      </c>
+      <c r="N190" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O190" s="9" t="s">
+        <v>1657</v>
+      </c>
+      <c r="P190" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q190" s="10">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="R190" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S190" s="10">
+        <v>0.30040509259259263</v>
+      </c>
+      <c r="T190" s="9">
+        <v>51.332000000000001</v>
+      </c>
+      <c r="U190" s="9">
+        <v>11.03</v>
+      </c>
+      <c r="V190" s="10">
+        <v>0.19396990740740741</v>
+      </c>
+      <c r="W190" s="10">
+        <v>0.11443287037037039</v>
+      </c>
+      <c r="X190" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y190" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE190" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF190" s="9" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AG190" s="9" t="s">
+        <v>1659</v>
+      </c>
+      <c r="AH190" s="9">
+        <v>6.2256499999999999</v>
+      </c>
+      <c r="AI190" s="9">
+        <v>-75.599074000000002</v>
+      </c>
+      <c r="AJ190" s="9" t="s">
+        <v>1660</v>
+      </c>
+      <c r="AK190" s="9">
+        <v>6.2587320000000002</v>
+      </c>
+      <c r="AL190" s="9">
+        <v>-75.616245000000006</v>
+      </c>
+      <c r="AM190" s="26">
+        <f t="shared" si="2"/>
+        <v>1.196759259259259E-2</v>
+      </c>
       <c r="AN190" s="9"/>
     </row>
-    <row r="191" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A191" s="9" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B191" s="9" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C191" s="9" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D191" s="9" t="s">
+        <v>1664</v>
+      </c>
+      <c r="E191" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F191" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="G191" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="H191" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I191" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J191" s="9">
+        <v>1982</v>
+      </c>
+      <c r="K191" s="9" t="s">
+        <v>1665</v>
+      </c>
+      <c r="L191" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M191" s="10">
+        <v>4.0578703703703707E-2</v>
+      </c>
+      <c r="N191" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O191" s="9" t="s">
+        <v>1666</v>
+      </c>
+      <c r="P191" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q191" s="10">
+        <v>6.7418981481481483E-2</v>
+      </c>
+      <c r="R191" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S191" s="10">
+        <v>0.20450231481481479</v>
+      </c>
+      <c r="T191" s="9">
+        <v>25.9</v>
+      </c>
+      <c r="U191" s="9">
+        <v>8.75</v>
+      </c>
+      <c r="V191" s="10">
+        <v>0.123275462962963</v>
+      </c>
+      <c r="W191" s="10">
+        <v>8.0879629629629635E-2</v>
+      </c>
+      <c r="X191" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y191" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z191" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA191" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB191" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC191" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD191" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE191" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF191" s="9" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AG191" s="9" t="s">
+        <v>1668</v>
+      </c>
+      <c r="AH191" s="9">
+        <v>6.2526510000000002</v>
+      </c>
+      <c r="AI191" s="9">
+        <v>-75.609696999999997</v>
+      </c>
+      <c r="AJ191" s="9" t="s">
+        <v>1669</v>
+      </c>
+      <c r="AK191" s="9">
+        <v>6.2434329999999996</v>
+      </c>
+      <c r="AL191" s="9">
+        <v>-75.602992999999998</v>
+      </c>
+      <c r="AM191" s="26">
+        <f t="shared" si="2"/>
+        <v>0.10799768518518518</v>
+      </c>
       <c r="AN191" s="9"/>
     </row>
     <row r="192" spans="1:40" x14ac:dyDescent="0.25">
@@ -66137,24 +67118,24 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="N1:N1048576">
-    <cfRule type="cellIs" dxfId="60" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"INICIO ANTES DEL HORARIO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"INICIO CUMPLE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"INICIO TARDÍO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R1048573">
-    <cfRule type="cellIs" dxfId="57" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"TERMINÓ DESPUÉS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"TERMINÓ ANTES"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"FIN CUMPLE"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/BASE_RECORRIDOS_PRO_JCA.xlsx
+++ b/BASE_RECORRIDOS_PRO_JCA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\INTERVENTORIA VELNEC\Recorridos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9A81BD-C59B-405A-9957-E01AC8A41196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD2C1E5-DC97-41D2-9A03-66630DB74FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GRAFICAS" sheetId="7" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4577" uniqueCount="1671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="1727">
   <si>
     <t>ID</t>
   </si>
@@ -5062,7 +5062,175 @@
     <t>6.243433, -75.602993</t>
   </si>
   <si>
-    <t>retubieron el vehiculo donde estaba laborando en el corregimineto de Santa Elena</t>
+    <t>retuvieron el vehículo donde estaba laborando en el corregimiento de Santa Elena</t>
+  </si>
+  <si>
+    <t>d7b664ef81ad9651</t>
+  </si>
+  <si>
+    <t>18_09_2026_DV_Noct1.gpx</t>
+  </si>
+  <si>
+    <t>d7b664ef81ad9651554f4d4fa4321cd936eac554b8e90b2d1b9a7efec9642fb0</t>
+  </si>
+  <si>
+    <t>18/09/2026 18:14:24</t>
+  </si>
+  <si>
+    <t>18/09/2026 23:07:55</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS anticipado: 00:52:05 antes de las 00:00.; 1 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.270135, -75.601358</t>
+  </si>
+  <si>
+    <t>6.246358, -75.604612</t>
+  </si>
+  <si>
+    <t>0b3b3e04436c9877</t>
+  </si>
+  <si>
+    <t>18_09_2026_DV_Noct2.gpx</t>
+  </si>
+  <si>
+    <t>0b3b3e04436c9877c98cc7e76170acac75d69b6bfb77bc702a6e8b91134c7379</t>
+  </si>
+  <si>
+    <t>18/09/2026 22:19:50</t>
+  </si>
+  <si>
+    <t>19/09/2026 00:13:49</t>
+  </si>
+  <si>
+    <t>Inicio GPS tardío: 04:19:51 después de las 18:00.; Fin GPS dentro de la tolerancia del horario programado.; 1 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.251355, -75.607428</t>
+  </si>
+  <si>
+    <t>6.272566, -75.602164</t>
+  </si>
+  <si>
+    <t>411c6fb03be049a0</t>
+  </si>
+  <si>
+    <t>18_09_2026_IQ_Noct.gpx</t>
+  </si>
+  <si>
+    <t>411c6fb03be049a075a3b26e6982874b7088874c41de9683287188622862b445</t>
+  </si>
+  <si>
+    <t>18/09/2026 18:02:40</t>
+  </si>
+  <si>
+    <t>18/09/2026 23:44:35</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS anticipado: 00:15:25 antes de las 00:00.; 3 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.271953, -75.540673</t>
+  </si>
+  <si>
+    <t>6.264430, -75.570660</t>
+  </si>
+  <si>
+    <t>1c33940de6d83ac0</t>
+  </si>
+  <si>
+    <t>18_09_2026_JHP_Noct.gpx</t>
+  </si>
+  <si>
+    <t>1c33940de6d83ac0ea53dec915860f2c48d3fa189da38e1c9f34d7786ab4c7ba</t>
+  </si>
+  <si>
+    <t>18/09/2026 17:31:58</t>
+  </si>
+  <si>
+    <t>19/09/2026 00:21:47</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 00:28:02 antes de las 18:00.; Fin GPS posterior: 00:21:47 después de las 00:00.</t>
+  </si>
+  <si>
+    <t>6.290363, -75.546539</t>
+  </si>
+  <si>
+    <t>6.290377, -75.546586</t>
+  </si>
+  <si>
+    <t>1f282216ee6e37f2</t>
+  </si>
+  <si>
+    <t>18_09_2026_JP_Noct.gpx</t>
+  </si>
+  <si>
+    <t>1f282216ee6e37f2520889c4282cf35711e63dfc3ceb4eb4602373514907a767</t>
+  </si>
+  <si>
+    <t>18/09/2026 17:58:21</t>
+  </si>
+  <si>
+    <t>18/09/2026 23:59:00</t>
+  </si>
+  <si>
+    <t>6.252467, -75.551827</t>
+  </si>
+  <si>
+    <t>6.251812, -75.551810</t>
+  </si>
+  <si>
+    <t>4eaa6f0e3139ce9c</t>
+  </si>
+  <si>
+    <t>18_09_2026_LA_Noct.gpx</t>
+  </si>
+  <si>
+    <t>4eaa6f0e3139ce9c3a1da9d13c538d9ea5f60c113e3a1e72c2c5288d79d3016e</t>
+  </si>
+  <si>
+    <t>18/09/2026 17:27:27</t>
+  </si>
+  <si>
+    <t>19/09/2026 00:00:48</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 00:32:33 antes de las 18:00.; Fin GPS dentro de la tolerancia del horario programado.; 2 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.268908, -75.598983</t>
+  </si>
+  <si>
+    <t>6.239752, -75.575770</t>
+  </si>
+  <si>
+    <t>3045fae0d268338d</t>
+  </si>
+  <si>
+    <t>19_09_2026_AR_Noct.gpx</t>
+  </si>
+  <si>
+    <t>3045fae0d268338d25d3cd23bdd9fd7b7ab66535277cf52b510b0f2255c64b2c</t>
+  </si>
+  <si>
+    <t>19/09/2026 18:23:21</t>
+  </si>
+  <si>
+    <t>20/09/2026 00:05:17</t>
+  </si>
+  <si>
+    <t>Inicio GPS tardío: 00:23:21 después de las 18:00.; Fin GPS dentro de la tolerancia del horario programado.; Sábado nocturno: verificar técnico asignado.</t>
+  </si>
+  <si>
+    <t>6.247751, -75.614997</t>
+  </si>
+  <si>
+    <t>6.247642, -75.614915</t>
+  </si>
+  <si>
+    <t>Este recorrido inicio temprano</t>
   </si>
 </sst>
 </file>
@@ -5374,6 +5542,14 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
       <font>
         <sz val="14"/>
       </font>
@@ -5429,11 +5605,9 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
-    </dxf>
-    <dxf>
       <font>
-        <sz val="14"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -5459,12 +5633,6 @@
     <dxf>
       <font>
         <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -39146,834 +39314,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D330A9A-54B8-43DD-8D11-CC5633B99CDA}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
-  <location ref="A6:E22" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item m="1" x="4"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="13"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="6" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="9">
-    <chartFormat chart="5" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="10" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="11" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="12" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
-  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item h="1" m="1" x="4"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="13"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="10">
-    <format dxfId="15">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="14">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="13">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="12">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="11">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="10">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="9">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="8">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="7">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="6">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="34" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
-  <location ref="A107:D123" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="8"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Suma de Kilómetros" fld="19" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="6">
-    <chartFormat chart="16" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="12"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="12"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{238AB259-E577-48AC-B3A0-09F752F5685D}" name="TablaDinámica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A169:B185" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="43">
@@ -40772,7 +40112,7 @@
     <dataField name="Suma de Sumatoria de tiempo total sin recorrido" fld="38" baseField="6" baseItem="0" numFmtId="21"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="16">
+    <format dxfId="6">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -40799,308 +40139,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B44BF58-179E-4C57-BD89-E6E3367D37B9}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
-  <location ref="K107:M122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item h="1" x="0"/>
-        <item h="1" m="1" x="4"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="17"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="12">
-    <format dxfId="28">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="27">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="26">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="25">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="24">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="17" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="23">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="22">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="21">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="20">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="19">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="18">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="17" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="17">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="28" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="28" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="28" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="28" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E67C1C-2F15-4D2B-A97A-A1B46B6F5B69}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
   <location ref="A57:E73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
@@ -41376,7 +40415,883 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D330A9A-54B8-43DD-8D11-CC5633B99CDA}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+  <location ref="A6:E22" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item m="1" x="4"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="13"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="6" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="9">
+    <chartFormat chart="5" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B44BF58-179E-4C57-BD89-E6E3367D37B9}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
+  <location ref="K107:M122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item h="1" x="0"/>
+        <item h="1" m="1" x="4"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="17"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="12">
+    <format dxfId="18">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="15">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="17" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="9">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="17" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="28" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="28" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="28" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="28" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
+  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" m="1" x="4"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="13"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="28">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="25">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="34" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0966AFF-8B15-4A0E-BE48-1F64EB76CB37}" name="TablaDinámica7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="57">
   <location ref="AI107:AJ122" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
@@ -41620,6 +41535,259 @@
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
+  <location ref="A107:D123" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="8"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Suma de Kilómetros" fld="19" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="16" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
@@ -66699,54 +66867,854 @@
       <c r="AN191" s="9"/>
     </row>
     <row r="192" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A192" s="9" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B192" s="9" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C192" s="9" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D192" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E192" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F192" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="G192" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H192" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I192" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J192" s="9">
+        <v>2110</v>
+      </c>
+      <c r="K192" s="9" t="s">
+        <v>1674</v>
+      </c>
+      <c r="L192" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M192" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="N192" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O192" s="9" t="s">
+        <v>1675</v>
+      </c>
+      <c r="P192" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q192" s="10">
+        <v>3.6168981481481483E-2</v>
+      </c>
+      <c r="R192" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S192" s="10">
+        <v>0.20383101851851851</v>
+      </c>
+      <c r="T192" s="9">
+        <v>26.300999999999998</v>
+      </c>
+      <c r="U192" s="9">
+        <v>7.48</v>
+      </c>
+      <c r="V192" s="10">
+        <v>0.14656250000000001</v>
+      </c>
+      <c r="W192" s="10">
+        <v>7.8009259259259264E-2</v>
+      </c>
+      <c r="X192" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y192" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z192" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA192" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB192" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC192" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD192" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE192" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF192" s="9" t="s">
+        <v>1676</v>
+      </c>
+      <c r="AG192" s="9" t="s">
+        <v>1677</v>
+      </c>
+      <c r="AH192" s="9">
+        <v>6.2701349999999998</v>
+      </c>
+      <c r="AI192" s="9">
+        <v>-75.601358000000005</v>
+      </c>
+      <c r="AJ192" s="9" t="s">
+        <v>1678</v>
+      </c>
+      <c r="AK192" s="9">
+        <v>6.2463579999999999</v>
+      </c>
+      <c r="AL192" s="9">
+        <v>-75.604612000000003</v>
+      </c>
       <c r="AN192" s="9"/>
     </row>
-    <row r="193" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN193" s="9"/>
+    <row r="193" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A193" s="9" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B193" s="9" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C193" s="9" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D193" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E193" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F193" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="G193" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H193" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I193" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J193" s="9">
+        <v>3418</v>
+      </c>
+      <c r="K193" s="9" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L193" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M193" s="10">
+        <v>0.18044956018518521</v>
+      </c>
+      <c r="N193" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O193" s="9" t="s">
+        <v>1683</v>
+      </c>
+      <c r="P193" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q193" s="10">
+        <v>9.5990509259259258E-3</v>
+      </c>
+      <c r="R193" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S193" s="10">
+        <v>7.9149490740740736E-2</v>
+      </c>
+      <c r="T193" s="9">
+        <v>16.713999999999999</v>
+      </c>
+      <c r="U193" s="9">
+        <v>19.91</v>
+      </c>
+      <c r="V193" s="10">
+        <v>3.4982083333333337E-2</v>
+      </c>
+      <c r="W193" s="10">
+        <v>2.1908865740740739E-2</v>
+      </c>
+      <c r="X193" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y193" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z193" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA193" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB193" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC193" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD193" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE193" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF193" s="9" t="s">
+        <v>1684</v>
+      </c>
+      <c r="AG193" s="9" t="s">
+        <v>1685</v>
+      </c>
+      <c r="AH193" s="9">
+        <v>6.2513550000000002</v>
+      </c>
+      <c r="AI193" s="9">
+        <v>-75.607427999999999</v>
+      </c>
+      <c r="AJ193" s="9" t="s">
+        <v>1686</v>
+      </c>
+      <c r="AK193" s="9">
+        <v>6.2725660000000003</v>
+      </c>
+      <c r="AL193" s="9">
+        <v>-75.602164000000002</v>
+      </c>
+      <c r="AN193" s="9" t="s">
+        <v>1726</v>
+      </c>
     </row>
-    <row r="194" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A194" s="9" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B194" s="9" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C194" s="9" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D194" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E194" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F194" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="G194" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="H194" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="I194" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J194" s="9">
+        <v>1869</v>
+      </c>
+      <c r="K194" s="9" t="s">
+        <v>1690</v>
+      </c>
+      <c r="L194" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M194" s="10">
+        <v>1.8518518518518519E-3</v>
+      </c>
+      <c r="N194" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O194" s="9" t="s">
+        <v>1691</v>
+      </c>
+      <c r="P194" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q194" s="10">
+        <v>1.0706018518518519E-2</v>
+      </c>
+      <c r="R194" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S194" s="10">
+        <v>0.2374421296296296</v>
+      </c>
+      <c r="T194" s="9">
+        <v>34.732999999999997</v>
+      </c>
+      <c r="U194" s="9">
+        <v>19.53</v>
+      </c>
+      <c r="V194" s="10">
+        <v>7.4097222222222217E-2</v>
+      </c>
+      <c r="W194" s="10">
+        <v>3.2002314814814817E-2</v>
+      </c>
+      <c r="X194" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y194" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z194" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA194" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB194" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC194" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD194" s="9">
+        <v>3</v>
+      </c>
+      <c r="AE194" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF194" s="9" t="s">
+        <v>1692</v>
+      </c>
+      <c r="AG194" s="9" t="s">
+        <v>1693</v>
+      </c>
+      <c r="AH194" s="9">
+        <v>6.2719529999999999</v>
+      </c>
+      <c r="AI194" s="9">
+        <v>-75.540672999999998</v>
+      </c>
+      <c r="AJ194" s="9" t="s">
+        <v>1694</v>
+      </c>
+      <c r="AK194" s="9">
+        <v>6.2644299999999999</v>
+      </c>
+      <c r="AL194" s="9">
+        <v>-75.570660000000004</v>
+      </c>
       <c r="AN194" s="9"/>
     </row>
-    <row r="195" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A195" s="9" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B195" s="9" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C195" s="9" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D195" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E195" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F195" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="G195" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="H195" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="I195" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J195" s="9">
+        <v>7141</v>
+      </c>
+      <c r="K195" s="9" t="s">
+        <v>1698</v>
+      </c>
+      <c r="L195" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M195" s="10">
+        <v>1.9467592592592588E-2</v>
+      </c>
+      <c r="N195" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O195" s="9" t="s">
+        <v>1699</v>
+      </c>
+      <c r="P195" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q195" s="10">
+        <v>1.5127314814814821E-2</v>
+      </c>
+      <c r="R195" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="S195" s="10">
+        <v>0.28459490740740739</v>
+      </c>
+      <c r="T195" s="9">
+        <v>95.653000000000006</v>
+      </c>
+      <c r="U195" s="9">
+        <v>18.7</v>
+      </c>
+      <c r="V195" s="10">
+        <v>0.21315972222222221</v>
+      </c>
+      <c r="W195" s="10">
+        <v>4.5879629629629631E-2</v>
+      </c>
+      <c r="X195" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y195" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE195" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF195" s="9" t="s">
+        <v>1700</v>
+      </c>
+      <c r="AG195" s="9" t="s">
+        <v>1701</v>
+      </c>
+      <c r="AH195" s="9">
+        <v>6.2903630000000001</v>
+      </c>
+      <c r="AI195" s="9">
+        <v>-75.546538999999996</v>
+      </c>
+      <c r="AJ195" s="9" t="s">
+        <v>1702</v>
+      </c>
+      <c r="AK195" s="9">
+        <v>6.2903770000000003</v>
+      </c>
+      <c r="AL195" s="9">
+        <v>-75.546586000000005</v>
+      </c>
       <c r="AN195" s="9"/>
     </row>
-    <row r="196" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A196" s="9" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B196" s="9" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C196" s="9" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D196" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E196" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F196" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="G196" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H196" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="I196" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J196" s="9">
+        <v>1651</v>
+      </c>
+      <c r="K196" s="9" t="s">
+        <v>1706</v>
+      </c>
+      <c r="L196" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M196" s="10">
+        <v>1.1458333333333329E-3</v>
+      </c>
+      <c r="N196" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O196" s="9" t="s">
+        <v>1707</v>
+      </c>
+      <c r="P196" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q196" s="10">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="R196" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S196" s="10">
+        <v>0.2504513888888889</v>
+      </c>
+      <c r="T196" s="9">
+        <v>19.93</v>
+      </c>
+      <c r="U196" s="9">
+        <v>3.93</v>
+      </c>
+      <c r="V196" s="10">
+        <v>0.21122685185185189</v>
+      </c>
+      <c r="W196" s="10">
+        <v>0.1576967592592593</v>
+      </c>
+      <c r="X196" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y196" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z196" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA196" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB196" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC196" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD196" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE196" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF196" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="AG196" s="9" t="s">
+        <v>1708</v>
+      </c>
+      <c r="AH196" s="9">
+        <v>6.2524670000000002</v>
+      </c>
+      <c r="AI196" s="9">
+        <v>-75.551827000000003</v>
+      </c>
+      <c r="AJ196" s="9" t="s">
+        <v>1709</v>
+      </c>
+      <c r="AK196" s="9">
+        <v>6.2518120000000001</v>
+      </c>
+      <c r="AL196" s="9">
+        <v>-75.551810000000003</v>
+      </c>
       <c r="AN196" s="9"/>
     </row>
-    <row r="197" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A197" s="9" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C197" s="9" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D197" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E197" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F197" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="G197" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="H197" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="I197" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J197" s="9">
+        <v>11062</v>
+      </c>
+      <c r="K197" s="9" t="s">
+        <v>1713</v>
+      </c>
+      <c r="L197" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M197" s="10">
+        <v>2.2600856481481479E-2</v>
+      </c>
+      <c r="N197" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O197" s="9" t="s">
+        <v>1714</v>
+      </c>
+      <c r="P197" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q197" s="10">
+        <v>5.5555555555555556E-4</v>
+      </c>
+      <c r="R197" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S197" s="10">
+        <v>0.27315641203703711</v>
+      </c>
+      <c r="T197" s="9">
+        <v>54.726999999999997</v>
+      </c>
+      <c r="U197" s="9">
+        <v>12.98</v>
+      </c>
+      <c r="V197" s="10">
+        <v>0.17561365740740739</v>
+      </c>
+      <c r="W197" s="10">
+        <v>0.1248032407407407</v>
+      </c>
+      <c r="X197" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y197" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z197" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA197" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB197" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC197" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD197" s="9">
+        <v>2</v>
+      </c>
+      <c r="AE197" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF197" s="9" t="s">
+        <v>1715</v>
+      </c>
+      <c r="AG197" s="9" t="s">
+        <v>1716</v>
+      </c>
+      <c r="AH197" s="9">
+        <v>6.2689079999999997</v>
+      </c>
+      <c r="AI197" s="9">
+        <v>-75.598983000000004</v>
+      </c>
+      <c r="AJ197" s="9" t="s">
+        <v>1717</v>
+      </c>
+      <c r="AK197" s="9">
+        <v>6.2397520000000002</v>
+      </c>
+      <c r="AL197" s="9">
+        <v>-75.575770000000006</v>
+      </c>
       <c r="AN197" s="9"/>
     </row>
-    <row r="198" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A198" s="9" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B198" s="9" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C198" s="9" t="s">
+        <v>1720</v>
+      </c>
+      <c r="D198" s="9" t="s">
+        <v>1664</v>
+      </c>
+      <c r="E198" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F198" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="G198" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H198" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I198" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J198" s="9">
+        <v>1907</v>
+      </c>
+      <c r="K198" s="9" t="s">
+        <v>1721</v>
+      </c>
+      <c r="L198" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M198" s="10">
+        <v>1.621527777777778E-2</v>
+      </c>
+      <c r="N198" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O198" s="9" t="s">
+        <v>1722</v>
+      </c>
+      <c r="P198" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q198" s="10">
+        <v>3.668981481481481E-3</v>
+      </c>
+      <c r="R198" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S198" s="10">
+        <v>0.23745370370370369</v>
+      </c>
+      <c r="T198" s="9">
+        <v>25.712</v>
+      </c>
+      <c r="U198" s="9">
+        <v>7.32</v>
+      </c>
+      <c r="V198" s="10">
+        <v>0.1464236111111111</v>
+      </c>
+      <c r="W198" s="10">
+        <v>0.1012268518518518</v>
+      </c>
+      <c r="X198" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y198" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z198" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA198" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB198" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC198" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD198" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE198" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF198" s="9" t="s">
+        <v>1723</v>
+      </c>
+      <c r="AG198" s="9" t="s">
+        <v>1724</v>
+      </c>
+      <c r="AH198" s="9">
+        <v>6.2477510000000001</v>
+      </c>
+      <c r="AI198" s="9">
+        <v>-75.614997000000002</v>
+      </c>
+      <c r="AJ198" s="9" t="s">
+        <v>1725</v>
+      </c>
+      <c r="AK198" s="9">
+        <v>6.2476419999999999</v>
+      </c>
+      <c r="AL198" s="9">
+        <v>-75.614914999999996</v>
+      </c>
       <c r="AN198" s="9"/>
     </row>
-    <row r="199" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN199" s="9"/>
     </row>
-    <row r="200" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN200" s="9"/>
     </row>
-    <row r="201" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN201" s="9"/>
     </row>
-    <row r="202" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN202" s="9"/>
     </row>
-    <row r="203" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN203" s="9"/>
     </row>
-    <row r="204" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN204" s="9"/>
     </row>
-    <row r="205" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN205" s="9"/>
     </row>
-    <row r="206" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN206" s="9"/>
     </row>
-    <row r="207" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN207" s="9"/>
     </row>
-    <row r="208" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN208" s="9"/>
     </row>
     <row r="209" spans="40:40" x14ac:dyDescent="0.25">

--- a/BASE_RECORRIDOS_PRO_JCA.xlsx
+++ b/BASE_RECORRIDOS_PRO_JCA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\INTERVENTORIA VELNEC\Recorridos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD2C1E5-DC97-41D2-9A03-66630DB74FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9414E4CE-574D-43AF-8939-B80943A55B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GRAFICAS" sheetId="7" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="1727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4882" uniqueCount="1798">
   <si>
     <t>ID</t>
   </si>
@@ -5231,6 +5231,219 @@
   </si>
   <si>
     <t>Este recorrido inicio temprano</t>
+  </si>
+  <si>
+    <t>f5cb150a19768be1</t>
+  </si>
+  <si>
+    <t>21_09_2026_AO_Diur.gpx</t>
+  </si>
+  <si>
+    <t>f5cb150a19768be11f5f5f899eca0440e6e3b31b79532bd3d2717e1843b2aeee</t>
+  </si>
+  <si>
+    <t>21/09/2026</t>
+  </si>
+  <si>
+    <t>21/09/2026 09:19:43</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:31:57</t>
+  </si>
+  <si>
+    <t>Inicio GPS tardío: 00:49:43 después de las 08:30.; Fin GPS dentro de la tolerancia del horario programado.; 7 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.215855, -75.597796</t>
+  </si>
+  <si>
+    <t>6.232111, -75.597014</t>
+  </si>
+  <si>
+    <t>4af9429c979acd31</t>
+  </si>
+  <si>
+    <t>21_09_2026_AR_Diur.gpx</t>
+  </si>
+  <si>
+    <t>4af9429c979acd311095eb9d774c8740b3b098e341a257bcd082b7d3d591eaf8</t>
+  </si>
+  <si>
+    <t>21/09/2026 08:30:35</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:31:01</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS dentro de la tolerancia del horario programado.; 3 hueco(s) GPS &gt;= 10 min.; 1 permanencia(s) GPS detectada(s); requiere contexto.</t>
+  </si>
+  <si>
+    <t>6.225557, -75.599429</t>
+  </si>
+  <si>
+    <t>6.247690, -75.614950</t>
+  </si>
+  <si>
+    <t>b710dc61d83a58bb</t>
+  </si>
+  <si>
+    <t>21_09_2026_DR_Diur.gpx</t>
+  </si>
+  <si>
+    <t>b710dc61d83a58bb2fd6232a2081ad7f1b35edb95d53d9681cfb5d0fc0a9002f</t>
+  </si>
+  <si>
+    <t>21/09/2026 08:34:46</t>
+  </si>
+  <si>
+    <t>21/09/2026 15:11:17</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS anticipado: 01:18:43 antes de las 16:30.; 1 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.229786, -75.602256</t>
+  </si>
+  <si>
+    <t>6.250664, -75.602300</t>
+  </si>
+  <si>
+    <t>df723bcb444a9b89</t>
+  </si>
+  <si>
+    <t>21_09_2026_HC_Diur.gpx</t>
+  </si>
+  <si>
+    <t>df723bcb444a9b89a96cfe59b0b091589c7ded961c305d4de77c75f601da7f63</t>
+  </si>
+  <si>
+    <t>21/09/2026 08:20:27</t>
+  </si>
+  <si>
+    <t>21/09/2026 14:33:13</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS anticipado: 01:56:47 antes de las 16:30.</t>
+  </si>
+  <si>
+    <t>6.225705, -75.599133</t>
+  </si>
+  <si>
+    <t>6.272694, -75.593395</t>
+  </si>
+  <si>
+    <t>6f27f1f7911931ca</t>
+  </si>
+  <si>
+    <t>21_09_2026_JA_Diur.gpx</t>
+  </si>
+  <si>
+    <t>6f27f1f7911931ca3828937e00b0d9d7e4b7f2e3b4a744bbd82905cb69fa15fb</t>
+  </si>
+  <si>
+    <t>21/09/2026 08:36:56</t>
+  </si>
+  <si>
+    <t>21/09/2026 12:04:26</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS anticipado: 04:25:34 antes de las 16:30.</t>
+  </si>
+  <si>
+    <t>6.225869, -75.599106</t>
+  </si>
+  <si>
+    <t>6.239244, -75.561041</t>
+  </si>
+  <si>
+    <t>27e8aa2b9041b83e</t>
+  </si>
+  <si>
+    <t>21_09_2026_JO_Diur.gpx</t>
+  </si>
+  <si>
+    <t>27e8aa2b9041b83e20a191f2772b4630e814d805f38d3a0411d9332a0dae3660</t>
+  </si>
+  <si>
+    <t>21/09/2026 08:37:28</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:43:37</t>
+  </si>
+  <si>
+    <t>6.225603, -75.599496</t>
+  </si>
+  <si>
+    <t>6.259267, -75.620907</t>
+  </si>
+  <si>
+    <t>dde7444915f2b4e9</t>
+  </si>
+  <si>
+    <t>21_09_2026_JZ_Diur.gpx</t>
+  </si>
+  <si>
+    <t>dde7444915f2b4e92aec2f1f976d41ad31491801b484ddb32cf638a5e3f4489c</t>
+  </si>
+  <si>
+    <t>21/09/2026 08:24:13</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:37:06</t>
+  </si>
+  <si>
+    <t>6.226645, -75.599253</t>
+  </si>
+  <si>
+    <t>6.279198, -75.569200</t>
+  </si>
+  <si>
+    <t>b634bea971084078</t>
+  </si>
+  <si>
+    <t>21_09_2026_SJ_Diur.gpx</t>
+  </si>
+  <si>
+    <t>b634bea971084078b58e036e265cc4e8a09286138fc0ba3da01e624fcd462fef</t>
+  </si>
+  <si>
+    <t>21/09/2026 08:26:09</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:07:56</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS anticipado: 00:22:04 antes de las 16:30.; 1 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.225533, -75.599530</t>
+  </si>
+  <si>
+    <t>6.305275, -75.581861</t>
+  </si>
+  <si>
+    <t>04d5b448cbe1d3e9</t>
+  </si>
+  <si>
+    <t>21_09_2026_YL_Diur.gpx</t>
+  </si>
+  <si>
+    <t>04d5b448cbe1d3e9f8fbfd0ec274e7c976ba2c0c9862da1199250c1f56a6b3e4</t>
+  </si>
+  <si>
+    <t>21/09/2026 08:53:20</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:34:39</t>
+  </si>
+  <si>
+    <t>Inicio GPS tardío: 00:23:20 después de las 08:30.; Fin GPS dentro de la tolerancia del horario programado.; 2 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.225541, -75.599001</t>
+  </si>
+  <si>
+    <t>6.258346, -75.615844</t>
   </si>
 </sst>
 </file>
@@ -5542,14 +5755,6 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
       <font>
         <sz val="14"/>
       </font>
@@ -5605,9 +5810,11 @@
       </font>
     </dxf>
     <dxf>
+      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
+    </dxf>
+    <dxf>
       <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
+        <sz val="14"/>
       </font>
     </dxf>
     <dxf>
@@ -5633,6 +5840,12 @@
     <dxf>
       <font>
         <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -39314,6 +39527,267 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0966AFF-8B15-4A0E-BE48-1F64EB76CB37}" name="TablaDinámica7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="57">
+  <location ref="AI107:AJ122" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="13"/>
+        <item h="1" x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Turno" fld="8" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="15">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="48" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="53" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="56" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{238AB259-E577-48AC-B3A0-09F752F5685D}" name="TablaDinámica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A169:B185" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="43">
@@ -40112,7 +40586,7 @@
     <dataField name="Suma de Sumatoria de tiempo total sin recorrido" fld="38" baseField="6" baseItem="0" numFmtId="21"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="6">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -40139,7 +40613,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E67C1C-2F15-4D2B-A97A-A1B46B6F5B69}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
   <location ref="A57:E73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
@@ -40415,7 +40889,260 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
+  <location ref="A107:D123" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="8"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Suma de Kilómetros" fld="19" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="16" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D330A9A-54B8-43DD-8D11-CC5633B99CDA}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A6:E22" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
@@ -40703,7 +41430,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B44BF58-179E-4C57-BD89-E6E3367D37B9}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
   <location ref="K107:M122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
@@ -40861,13 +41588,13 @@
     <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="18">
+    <format dxfId="28">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="27">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="13">
@@ -40888,26 +41615,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="22">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="21">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="13">
@@ -40928,17 +41655,17 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="9">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -41004,7 +41731,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
   <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
@@ -41162,279 +41889,6 @@
     <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="10">
-    <format dxfId="28">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="27">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="26">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="25">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="24">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="23">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="22">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="21">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="20">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="19">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="34" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0966AFF-8B15-4A0E-BE48-1F64EB76CB37}" name="TablaDinámica7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="57">
-  <location ref="AI107:AJ122" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item h="1" x="11"/>
-        <item h="1" x="12"/>
-        <item h="1" x="13"/>
-        <item h="1" x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Turno" fld="8" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="10">
     <format dxfId="38">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
@@ -41503,291 +41957,50 @@
     </format>
   </formats>
   <chartFormats count="4">
-    <chartFormat chart="48" format="8" series="1">
+    <chartFormat chart="34" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
+        <references count="2">
           <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="39" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="53" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="56" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
-  <location ref="A107:D123" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="8"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Suma de Kilómetros" fld="19" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="6">
-    <chartFormat chart="16" format="0" series="1">
+    <chartFormat chart="34" format="1" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="16" format="1" series="1">
+    <chartFormat chart="34" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="16" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="12"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="6" series="1">
+    <chartFormat chart="34" format="3" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="12"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
+          <reference field="13" count="1" selected="0">
+            <x v="3"/>
           </reference>
         </references>
       </pivotArea>
@@ -59557,7 +59770,7 @@
         <v>-75.569377000000003</v>
       </c>
       <c r="AM131" s="26">
-        <f t="shared" ref="AM131:AM191" si="2">IF(N131="INICIO TARDÍO",M131,0)+IF(R131="TERMINÓ ANTES",Q131,0)</f>
+        <f t="shared" ref="AM131:AM194" si="2">IF(N131="INICIO TARDÍO",M131,0)+IF(R131="TERMINÓ ANTES",Q131,0)</f>
         <v>0</v>
       </c>
       <c r="AN131" s="9"/>
@@ -66866,7 +67079,7 @@
       </c>
       <c r="AN191" s="9"/>
     </row>
-    <row r="192" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:40" ht="15" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
         <v>1671</v>
       </c>
@@ -66981,9 +67194,13 @@
       <c r="AL192" s="9">
         <v>-75.604612000000003</v>
       </c>
+      <c r="AM192" s="26">
+        <f t="shared" si="2"/>
+        <v>3.6168981481481483E-2</v>
+      </c>
       <c r="AN192" s="9"/>
     </row>
-    <row r="193" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:40" ht="15" x14ac:dyDescent="0.25">
       <c r="A193" s="9" t="s">
         <v>1679</v>
       </c>
@@ -67098,11 +67315,15 @@
       <c r="AL193" s="9">
         <v>-75.602164000000002</v>
       </c>
+      <c r="AM193" s="26">
+        <f t="shared" si="2"/>
+        <v>0.18044956018518521</v>
+      </c>
       <c r="AN193" s="9" t="s">
         <v>1726</v>
       </c>
     </row>
-    <row r="194" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:40" ht="15" x14ac:dyDescent="0.25">
       <c r="A194" s="9" t="s">
         <v>1687</v>
       </c>
@@ -67217,9 +67438,13 @@
       <c r="AL194" s="9">
         <v>-75.570660000000004</v>
       </c>
+      <c r="AM194" s="26">
+        <f t="shared" si="2"/>
+        <v>1.0706018518518519E-2</v>
+      </c>
       <c r="AN194" s="9"/>
     </row>
-    <row r="195" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:40" ht="15" x14ac:dyDescent="0.25">
       <c r="A195" s="9" t="s">
         <v>1695</v>
       </c>
@@ -67334,9 +67559,13 @@
       <c r="AL195" s="9">
         <v>-75.546586000000005</v>
       </c>
+      <c r="AM195" s="26">
+        <f t="shared" ref="AM195:AM207" si="3">IF(N195="INICIO TARDÍO",M195,0)+IF(R195="TERMINÓ ANTES",Q195,0)</f>
+        <v>0</v>
+      </c>
       <c r="AN195" s="9"/>
     </row>
-    <row r="196" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:40" ht="15" x14ac:dyDescent="0.25">
       <c r="A196" s="9" t="s">
         <v>1703</v>
       </c>
@@ -67451,9 +67680,13 @@
       <c r="AL196" s="9">
         <v>-75.551810000000003</v>
       </c>
+      <c r="AM196" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN196" s="9"/>
     </row>
-    <row r="197" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:40" ht="15" x14ac:dyDescent="0.25">
       <c r="A197" s="9" t="s">
         <v>1710</v>
       </c>
@@ -67568,9 +67801,13 @@
       <c r="AL197" s="9">
         <v>-75.575770000000006</v>
       </c>
+      <c r="AM197" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN197" s="9"/>
     </row>
-    <row r="198" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:40" ht="15" x14ac:dyDescent="0.25">
       <c r="A198" s="9" t="s">
         <v>1718</v>
       </c>
@@ -67685,33 +67922,1099 @@
       <c r="AL198" s="9">
         <v>-75.614914999999996</v>
       </c>
+      <c r="AM198" s="26">
+        <f t="shared" si="3"/>
+        <v>1.621527777777778E-2</v>
+      </c>
       <c r="AN198" s="9"/>
     </row>
-    <row r="199" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A199" s="9" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B199" s="9" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C199" s="9" t="s">
+        <v>1729</v>
+      </c>
+      <c r="D199" s="9" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E199" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F199" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="G199" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H199" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I199" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J199" s="9">
+        <v>5940</v>
+      </c>
+      <c r="K199" s="9" t="s">
+        <v>1731</v>
+      </c>
+      <c r="L199" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M199" s="10">
+        <v>3.4527638888888892E-2</v>
+      </c>
+      <c r="N199" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O199" s="9" t="s">
+        <v>1732</v>
+      </c>
+      <c r="P199" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q199" s="10">
+        <v>1.3615277777777779E-3</v>
+      </c>
+      <c r="R199" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S199" s="10">
+        <v>0.30016722222222231</v>
+      </c>
+      <c r="T199" s="9">
+        <v>46.2</v>
+      </c>
+      <c r="U199" s="9">
+        <v>18.46</v>
+      </c>
+      <c r="V199" s="10">
+        <v>0.1042935185185186</v>
+      </c>
+      <c r="W199" s="10">
+        <v>4.9700833333333333E-2</v>
+      </c>
+      <c r="X199" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y199" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD199" s="9">
+        <v>7</v>
+      </c>
+      <c r="AE199" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF199" s="9" t="s">
+        <v>1733</v>
+      </c>
+      <c r="AG199" s="9" t="s">
+        <v>1734</v>
+      </c>
+      <c r="AH199" s="9">
+        <v>6.2158550000000004</v>
+      </c>
+      <c r="AI199" s="9">
+        <v>-75.597796000000002</v>
+      </c>
+      <c r="AJ199" s="9" t="s">
+        <v>1735</v>
+      </c>
+      <c r="AK199" s="9">
+        <v>6.2321109999999997</v>
+      </c>
+      <c r="AL199" s="9">
+        <v>-75.597014000000001</v>
+      </c>
+      <c r="AM199" s="26">
+        <f t="shared" si="3"/>
+        <v>3.4527638888888892E-2</v>
+      </c>
       <c r="AN199" s="9"/>
     </row>
-    <row r="200" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A200" s="9" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B200" s="9" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C200" s="9" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D200" s="9" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E200" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F200" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="G200" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H200" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I200" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J200" s="9">
+        <v>2849</v>
+      </c>
+      <c r="K200" s="9" t="s">
+        <v>1739</v>
+      </c>
+      <c r="L200" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M200" s="10">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="N200" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O200" s="9" t="s">
+        <v>1740</v>
+      </c>
+      <c r="P200" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q200" s="10">
+        <v>7.0601851851851847E-4</v>
+      </c>
+      <c r="R200" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S200" s="10">
+        <v>0.33363425925925932</v>
+      </c>
+      <c r="T200" s="9">
+        <v>37.97</v>
+      </c>
+      <c r="U200" s="9">
+        <v>5.67</v>
+      </c>
+      <c r="V200" s="10">
+        <v>0.27901620370370372</v>
+      </c>
+      <c r="W200" s="10">
+        <v>0.22410879629629629</v>
+      </c>
+      <c r="X200" s="10">
+        <v>7.9745370370370369E-3</v>
+      </c>
+      <c r="Y200" s="9">
+        <v>1</v>
+      </c>
+      <c r="Z200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD200" s="9">
+        <v>3</v>
+      </c>
+      <c r="AE200" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF200" s="9" t="s">
+        <v>1741</v>
+      </c>
+      <c r="AG200" s="9" t="s">
+        <v>1742</v>
+      </c>
+      <c r="AH200" s="9">
+        <v>6.2255570000000002</v>
+      </c>
+      <c r="AI200" s="9">
+        <v>-75.599429000000001</v>
+      </c>
+      <c r="AJ200" s="9" t="s">
+        <v>1743</v>
+      </c>
+      <c r="AK200" s="9">
+        <v>6.2476900000000004</v>
+      </c>
+      <c r="AL200" s="9">
+        <v>-75.614949999999993</v>
+      </c>
+      <c r="AM200" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN200" s="9"/>
     </row>
-    <row r="201" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A201" s="9" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B201" s="9" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C201" s="9" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D201" s="9" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E201" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F201" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="G201" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="H201" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I201" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J201" s="9">
+        <v>2438</v>
+      </c>
+      <c r="K201" s="9" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L201" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M201" s="10">
+        <v>3.3101851851851851E-3</v>
+      </c>
+      <c r="N201" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O201" s="9" t="s">
+        <v>1748</v>
+      </c>
+      <c r="P201" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q201" s="10">
+        <v>5.4664351851851853E-2</v>
+      </c>
+      <c r="R201" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S201" s="10">
+        <v>0.27535879629629628</v>
+      </c>
+      <c r="T201" s="9">
+        <v>31.468</v>
+      </c>
+      <c r="U201" s="9">
+        <v>6.52</v>
+      </c>
+      <c r="V201" s="10">
+        <v>0.20113425925925929</v>
+      </c>
+      <c r="W201" s="10">
+        <v>0.15133101851851849</v>
+      </c>
+      <c r="X201" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y201" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z201" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA201" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB201" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC201" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD201" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE201" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF201" s="9" t="s">
+        <v>1749</v>
+      </c>
+      <c r="AG201" s="9" t="s">
+        <v>1750</v>
+      </c>
+      <c r="AH201" s="9">
+        <v>6.2297859999999998</v>
+      </c>
+      <c r="AI201" s="9">
+        <v>-75.602255999999997</v>
+      </c>
+      <c r="AJ201" s="9" t="s">
+        <v>1751</v>
+      </c>
+      <c r="AK201" s="9">
+        <v>6.2506640000000004</v>
+      </c>
+      <c r="AL201" s="9">
+        <v>-75.6023</v>
+      </c>
+      <c r="AM201" s="26">
+        <f t="shared" si="3"/>
+        <v>5.4664351851851853E-2</v>
+      </c>
       <c r="AN201" s="9"/>
     </row>
-    <row r="202" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A202" s="9" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B202" s="9" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C202" s="9" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D202" s="9" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E202" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F202" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="G202" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H202" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I202" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J202" s="9">
+        <v>4843</v>
+      </c>
+      <c r="K202" s="9" t="s">
+        <v>1755</v>
+      </c>
+      <c r="L202" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M202" s="10">
+        <v>6.6319444444444446E-3</v>
+      </c>
+      <c r="N202" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O202" s="9" t="s">
+        <v>1756</v>
+      </c>
+      <c r="P202" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q202" s="10">
+        <v>8.1099537037037039E-2</v>
+      </c>
+      <c r="R202" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S202" s="10">
+        <v>0.25886574074074081</v>
+      </c>
+      <c r="T202" s="9">
+        <v>62.777000000000001</v>
+      </c>
+      <c r="U202" s="9">
+        <v>13.85</v>
+      </c>
+      <c r="V202" s="10">
+        <v>0.18884259259259259</v>
+      </c>
+      <c r="W202" s="10">
+        <v>6.1122685185185183E-2</v>
+      </c>
+      <c r="X202" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y202" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z202" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA202" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB202" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC202" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD202" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE202" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF202" s="9" t="s">
+        <v>1757</v>
+      </c>
+      <c r="AG202" s="9" t="s">
+        <v>1758</v>
+      </c>
+      <c r="AH202" s="9">
+        <v>6.2257049999999996</v>
+      </c>
+      <c r="AI202" s="9">
+        <v>-75.599132999999995</v>
+      </c>
+      <c r="AJ202" s="9" t="s">
+        <v>1759</v>
+      </c>
+      <c r="AK202" s="9">
+        <v>6.2726940000000004</v>
+      </c>
+      <c r="AL202" s="9">
+        <v>-75.593395000000001</v>
+      </c>
+      <c r="AM202" s="26">
+        <f t="shared" si="3"/>
+        <v>8.1099537037037039E-2</v>
+      </c>
       <c r="AN202" s="9"/>
     </row>
-    <row r="203" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A203" s="9" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B203" s="9" t="s">
+        <v>1761</v>
+      </c>
+      <c r="C203" s="9" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D203" s="9" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E203" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F203" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="G203" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H203" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I203" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J203" s="9">
+        <v>3629</v>
+      </c>
+      <c r="K203" s="9" t="s">
+        <v>1763</v>
+      </c>
+      <c r="L203" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M203" s="10">
+        <v>4.8148148148148152E-3</v>
+      </c>
+      <c r="N203" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O203" s="9" t="s">
+        <v>1764</v>
+      </c>
+      <c r="P203" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q203" s="10">
+        <v>0.18442129629629631</v>
+      </c>
+      <c r="R203" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S203" s="10">
+        <v>0.14409722222222221</v>
+      </c>
+      <c r="T203" s="9">
+        <v>48.866</v>
+      </c>
+      <c r="U203" s="9">
+        <v>15.48</v>
+      </c>
+      <c r="V203" s="10">
+        <v>0.13149305555555549</v>
+      </c>
+      <c r="W203" s="10">
+        <v>4.3900462962962961E-2</v>
+      </c>
+      <c r="X203" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y203" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z203" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA203" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB203" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC203" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD203" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE203" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF203" s="9" t="s">
+        <v>1765</v>
+      </c>
+      <c r="AG203" s="9" t="s">
+        <v>1766</v>
+      </c>
+      <c r="AH203" s="9">
+        <v>6.2258690000000003</v>
+      </c>
+      <c r="AI203" s="9">
+        <v>-75.599106000000006</v>
+      </c>
+      <c r="AJ203" s="9" t="s">
+        <v>1767</v>
+      </c>
+      <c r="AK203" s="9">
+        <v>6.2392440000000002</v>
+      </c>
+      <c r="AL203" s="9">
+        <v>-75.561041000000003</v>
+      </c>
+      <c r="AM203" s="26">
+        <f t="shared" si="3"/>
+        <v>0.18442129629629631</v>
+      </c>
       <c r="AN203" s="9"/>
     </row>
-    <row r="204" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A204" s="9" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B204" s="9" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C204" s="9" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D204" s="9" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E204" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F204" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="G204" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H204" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I204" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J204" s="9">
+        <v>6889</v>
+      </c>
+      <c r="K204" s="9" t="s">
+        <v>1771</v>
+      </c>
+      <c r="L204" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M204" s="10">
+        <v>5.1966435185185188E-3</v>
+      </c>
+      <c r="N204" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O204" s="9" t="s">
+        <v>1772</v>
+      </c>
+      <c r="P204" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q204" s="10">
+        <v>9.4578240740740734E-3</v>
+      </c>
+      <c r="R204" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S204" s="10">
+        <v>0.33759451388888889</v>
+      </c>
+      <c r="T204" s="9">
+        <v>50.584000000000003</v>
+      </c>
+      <c r="U204" s="9">
+        <v>20.420000000000002</v>
+      </c>
+      <c r="V204" s="10">
+        <v>0.10319652777777751</v>
+      </c>
+      <c r="W204" s="10">
+        <v>4.3017199074074072E-2</v>
+      </c>
+      <c r="X204" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y204" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z204" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA204" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB204" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC204" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD204" s="9">
+        <v>13</v>
+      </c>
+      <c r="AE204" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF204" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="AG204" s="9" t="s">
+        <v>1773</v>
+      </c>
+      <c r="AH204" s="9">
+        <v>6.2256030000000004</v>
+      </c>
+      <c r="AI204" s="9">
+        <v>-75.599496000000002</v>
+      </c>
+      <c r="AJ204" s="9" t="s">
+        <v>1774</v>
+      </c>
+      <c r="AK204" s="9">
+        <v>6.2592670000000004</v>
+      </c>
+      <c r="AL204" s="9">
+        <v>-75.620907000000003</v>
+      </c>
+      <c r="AM204" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN204" s="9"/>
     </row>
-    <row r="205" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A205" s="9" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B205" s="9" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C205" s="9" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D205" s="9" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E205" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F205" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="G205" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H205" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I205" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J205" s="9">
+        <v>6424</v>
+      </c>
+      <c r="K205" s="9" t="s">
+        <v>1778</v>
+      </c>
+      <c r="L205" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M205" s="10">
+        <v>4.0162037037037041E-3</v>
+      </c>
+      <c r="N205" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O205" s="9" t="s">
+        <v>1779</v>
+      </c>
+      <c r="P205" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q205" s="10">
+        <v>4.9305555555555552E-3</v>
+      </c>
+      <c r="R205" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S205" s="10">
+        <v>0.34228009259259262</v>
+      </c>
+      <c r="T205" s="9">
+        <v>86.244</v>
+      </c>
+      <c r="U205" s="9">
+        <v>13.99</v>
+      </c>
+      <c r="V205" s="10">
+        <v>0.25685185185185178</v>
+      </c>
+      <c r="W205" s="10">
+        <v>0.10101851851851849</v>
+      </c>
+      <c r="X205" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y205" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE205" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF205" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="AG205" s="9" t="s">
+        <v>1780</v>
+      </c>
+      <c r="AH205" s="9">
+        <v>6.2266450000000004</v>
+      </c>
+      <c r="AI205" s="9">
+        <v>-75.599253000000004</v>
+      </c>
+      <c r="AJ205" s="9" t="s">
+        <v>1781</v>
+      </c>
+      <c r="AK205" s="9">
+        <v>6.2791980000000001</v>
+      </c>
+      <c r="AL205" s="9">
+        <v>-75.569199999999995</v>
+      </c>
+      <c r="AM205" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN205" s="9"/>
     </row>
-    <row r="206" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A206" s="9" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B206" s="9" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C206" s="9" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D206" s="9" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E206" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F206" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="G206" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H206" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="I206" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J206" s="9">
+        <v>3387</v>
+      </c>
+      <c r="K206" s="9" t="s">
+        <v>1785</v>
+      </c>
+      <c r="L206" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M206" s="10">
+        <v>2.673611111111111E-3</v>
+      </c>
+      <c r="N206" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O206" s="9" t="s">
+        <v>1786</v>
+      </c>
+      <c r="P206" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q206" s="10">
+        <v>1.532407407407407E-2</v>
+      </c>
+      <c r="R206" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S206" s="10">
+        <v>0.32068287037037041</v>
+      </c>
+      <c r="T206" s="9">
+        <v>44.941000000000003</v>
+      </c>
+      <c r="U206" s="9">
+        <v>10.050000000000001</v>
+      </c>
+      <c r="V206" s="10">
+        <v>0.18630787037037039</v>
+      </c>
+      <c r="W206" s="10">
+        <v>0.1088078703703704</v>
+      </c>
+      <c r="X206" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y206" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD206" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE206" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF206" s="9" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AG206" s="9" t="s">
+        <v>1788</v>
+      </c>
+      <c r="AH206" s="9">
+        <v>6.2255330000000004</v>
+      </c>
+      <c r="AI206" s="9">
+        <v>-75.599530000000001</v>
+      </c>
+      <c r="AJ206" s="9" t="s">
+        <v>1789</v>
+      </c>
+      <c r="AK206" s="9">
+        <v>6.305275</v>
+      </c>
+      <c r="AL206" s="9">
+        <v>-75.581861000000004</v>
+      </c>
+      <c r="AM206" s="26">
+        <f t="shared" si="3"/>
+        <v>1.532407407407407E-2</v>
+      </c>
       <c r="AN206" s="9"/>
     </row>
-    <row r="207" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A207" s="9" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B207" s="9" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C207" s="9" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D207" s="9" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E207" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F207" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="G207" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H207" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I207" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J207" s="9">
+        <v>2857</v>
+      </c>
+      <c r="K207" s="9" t="s">
+        <v>1793</v>
+      </c>
+      <c r="L207" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M207" s="10">
+        <v>1.6203703703703699E-2</v>
+      </c>
+      <c r="N207" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O207" s="9" t="s">
+        <v>1794</v>
+      </c>
+      <c r="P207" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q207" s="10">
+        <v>3.2291666666666671E-3</v>
+      </c>
+      <c r="R207" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S207" s="10">
+        <v>0.32035879629629632</v>
+      </c>
+      <c r="T207" s="9">
+        <v>39.404000000000003</v>
+      </c>
+      <c r="U207" s="9">
+        <v>7.43</v>
+      </c>
+      <c r="V207" s="10">
+        <v>0.22092592592592589</v>
+      </c>
+      <c r="W207" s="10">
+        <v>0.16953703703703699</v>
+      </c>
+      <c r="X207" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD207" s="9">
+        <v>2</v>
+      </c>
+      <c r="AE207" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF207" s="9" t="s">
+        <v>1795</v>
+      </c>
+      <c r="AG207" s="9" t="s">
+        <v>1796</v>
+      </c>
+      <c r="AH207" s="9">
+        <v>6.2255409999999998</v>
+      </c>
+      <c r="AI207" s="9">
+        <v>-75.599001000000001</v>
+      </c>
+      <c r="AJ207" s="9" t="s">
+        <v>1797</v>
+      </c>
+      <c r="AK207" s="9">
+        <v>6.2583460000000004</v>
+      </c>
+      <c r="AL207" s="9">
+        <v>-75.615843999999996</v>
+      </c>
+      <c r="AM207" s="26">
+        <f t="shared" si="3"/>
+        <v>1.6203703703703699E-2</v>
+      </c>
       <c r="AN207" s="9"/>
     </row>
     <row r="208" spans="1:40" x14ac:dyDescent="0.25">

--- a/BASE_RECORRIDOS_PRO_JCA.xlsx
+++ b/BASE_RECORRIDOS_PRO_JCA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\INTERVENTORIA VELNEC\Recorridos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9414E4CE-574D-43AF-8939-B80943A55B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4007FCDD-5BE3-4D98-A1B1-FD31D0B6EB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GRAFICAS" sheetId="7" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4882" uniqueCount="1798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4958" uniqueCount="1830">
   <si>
     <t>ID</t>
   </si>
@@ -5444,6 +5444,102 @@
   </si>
   <si>
     <t>6.258346, -75.615844</t>
+  </si>
+  <si>
+    <t>4884f203cb19cd6f</t>
+  </si>
+  <si>
+    <t>21_09_2026_DV_Noct.gpx</t>
+  </si>
+  <si>
+    <t>4884f203cb19cd6f079a749132d411d17323f85c044649c665815bb14f94daf2</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:49:40</t>
+  </si>
+  <si>
+    <t>22/09/2026 00:19:36</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 01:10:20 antes de las 18:00.; Fin GPS posterior: 00:19:36 después de las 00:00.</t>
+  </si>
+  <si>
+    <t>6.230358, -75.596036</t>
+  </si>
+  <si>
+    <t>6.272685, -75.601995</t>
+  </si>
+  <si>
+    <t>9e22990e3b4a2ca1</t>
+  </si>
+  <si>
+    <t>21_09_2026_JHP_Noct.gpx</t>
+  </si>
+  <si>
+    <t>9e22990e3b4a2ca1d3a52ec4fc41e1d02c472c3565f3e888499da61f9f20fd26</t>
+  </si>
+  <si>
+    <t>21/09/2026 17:13:19</t>
+  </si>
+  <si>
+    <t>21/09/2026 23:53:16</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 00:46:41 antes de las 18:00.; Fin GPS dentro de la tolerancia del horario programado.</t>
+  </si>
+  <si>
+    <t>6.226799, -75.599269</t>
+  </si>
+  <si>
+    <t>6.290376, -75.546627</t>
+  </si>
+  <si>
+    <t>835e20c04a53828a</t>
+  </si>
+  <si>
+    <t>21_09_2026_JP_Noct.gpx</t>
+  </si>
+  <si>
+    <t>835e20c04a53828ac368be1f9fdba8cf009f6fbc15008e849ce99879df0dfc8c</t>
+  </si>
+  <si>
+    <t>21/09/2026 17:18:13</t>
+  </si>
+  <si>
+    <t>21/09/2026 21:40:42</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 00:41:47 antes de las 18:00.; Fin GPS anticipado: 02:19:18 antes de las 00:00.; 1 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.227053, -75.599640</t>
+  </si>
+  <si>
+    <t>6.251827, -75.551843</t>
+  </si>
+  <si>
+    <t>b907b156e6a5331b</t>
+  </si>
+  <si>
+    <t>b907b156e6a5331be632ae339c782b82f2745169ca62414b285562508b1a292d</t>
+  </si>
+  <si>
+    <t>21/09/2026 17:05:19</t>
+  </si>
+  <si>
+    <t>21/09/2026 23:58:09</t>
+  </si>
+  <si>
+    <t>6.226718, -75.599287</t>
+  </si>
+  <si>
+    <t>6.261535, -75.592328</t>
+  </si>
+  <si>
+    <t>21_09_2026_LA_Noct.gpx</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 00:54:41 antes de las 18:00.; Fin GPS dentro de la tolerancia del horario programado.; 2 hueco(s) GPS &gt;= 10 min.</t>
   </si>
 </sst>
 </file>
@@ -5781,6 +5877,11 @@
     </dxf>
     <dxf>
       <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
@@ -5810,11 +5911,9 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
-    </dxf>
-    <dxf>
       <font>
-        <sz val="14"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -5873,10 +5972,7 @@
       </font>
     </dxf>
     <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
+      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
     </dxf>
     <dxf>
       <font>
@@ -24135,7 +24231,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="USER" refreshedDate="46283.800954629631" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="192" xr:uid="{FDEF9B37-15CF-42E8-BC5E-E1CE4649CF2B}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:AM554" sheet="RECORRIDOS"/>
+    <worksheetSource ref="A1:AM553" sheet="RECORRIDOS"/>
   </cacheSource>
   <cacheFields count="43">
     <cacheField name="ID" numFmtId="0">
@@ -24955,7 +25051,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="USER" refreshedDate="46283.800954861108" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="192" xr:uid="{4743F9B8-9139-4DCD-A807-2514F242574C}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:AF1048573" sheet="RECORRIDOS"/>
+    <worksheetSource ref="A1:AF1048572" sheet="RECORRIDOS"/>
   </cacheSource>
   <cacheFields count="32">
     <cacheField name="ID" numFmtId="0">
@@ -39527,6 +39623,307 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B44BF58-179E-4C57-BD89-E6E3367D37B9}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
+  <location ref="K107:M122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item h="1" x="0"/>
+        <item h="1" m="1" x="4"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="17"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="12">
+    <format dxfId="17">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="17" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="17" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="28" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="28" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="28" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="28" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0966AFF-8B15-4A0E-BE48-1F64EB76CB37}" name="TablaDinámica7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="57">
   <location ref="AI107:AJ122" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
@@ -39670,13 +40067,13 @@
     <dataField name="Cuenta de Turno" fld="8" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="10">
-    <format dxfId="15">
+    <format dxfId="27">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="26">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="13">
@@ -39697,19 +40094,19 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="22">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="21">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="13">
@@ -39730,10 +40127,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -39787,7 +40184,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{238AB259-E577-48AC-B3A0-09F752F5685D}" name="TablaDinámica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A169:B185" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="43">
@@ -40586,7 +40983,7 @@
     <dataField name="Suma de Sumatoria de tiempo total sin recorrido" fld="38" baseField="6" baseItem="0" numFmtId="21"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="16">
+    <format dxfId="28">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -40613,7 +41010,294 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
+  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" m="1" x="4"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="13"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="38">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="37">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="35">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="33">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="32">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="31">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="34" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E67C1C-2F15-4D2B-A97A-A1B46B6F5B69}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
   <location ref="A57:E73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
@@ -40889,7 +41573,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
   <location ref="A107:D123" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
@@ -41142,7 +41826,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D330A9A-54B8-43DD-8D11-CC5633B99CDA}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A6:E22" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
@@ -41430,597 +42114,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B44BF58-179E-4C57-BD89-E6E3367D37B9}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
-  <location ref="K107:M122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item h="1" x="0"/>
-        <item h="1" m="1" x="4"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="17"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="12">
-    <format dxfId="28">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="27">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="26">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="25">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="24">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="17" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="23">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="22">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="21">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="20">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="19">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="18">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="17" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="17">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="28" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="28" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="28" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="28" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
-  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item h="1" m="1" x="4"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="13"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="10">
-    <format dxfId="38">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="37">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="36">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="35">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="34">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="33">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="32">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="31">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="30">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="29">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="34" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{07721E28-36B5-4676-BFC5-097A3B63190A}" name="Tabla1" displayName="Tabla1" ref="A1:AF1048573" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71">
-  <autoFilter ref="A1:AF1048573" xr:uid="{07721E28-36B5-4676-BFC5-097A3B63190A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{07721E28-36B5-4676-BFC5-097A3B63190A}" name="Tabla1" displayName="Tabla1" ref="A1:AF1048572" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71">
+  <autoFilter ref="A1:AF1048572" xr:uid="{07721E28-36B5-4676-BFC5-097A3B63190A}"/>
   <tableColumns count="32">
     <tableColumn id="1" xr3:uid="{BFACFB74-E6A6-4648-B0DA-7D6E1FC88A79}" name="ID" dataDxfId="70"/>
     <tableColumn id="2" xr3:uid="{B67B24E0-3585-47FC-A130-8F37C8640BC4}" name="Archivo" dataDxfId="69"/>
@@ -43858,13 +43954,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BB330"/>
+  <dimension ref="A1:BB329"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" style="9" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="41.42578125" style="9" customWidth="1"/>
     <col min="3" max="3" width="17" style="9" customWidth="1"/>
-    <col min="4" max="4" width="11" style="9" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="9" customWidth="1"/>
     <col min="5" max="5" width="12.140625" style="9" customWidth="1"/>
     <col min="6" max="6" width="11" style="9" customWidth="1"/>
     <col min="7" max="7" width="26.140625" style="9" customWidth="1"/>
@@ -67560,7 +67656,7 @@
         <v>-75.546586000000005</v>
       </c>
       <c r="AM195" s="26">
-        <f t="shared" ref="AM195:AM207" si="3">IF(N195="INICIO TARDÍO",M195,0)+IF(R195="TERMINÓ ANTES",Q195,0)</f>
+        <f t="shared" ref="AM195:AM211" si="3">IF(N195="INICIO TARDÍO",M195,0)+IF(R195="TERMINÓ ANTES",Q195,0)</f>
         <v>0</v>
       </c>
       <c r="AN195" s="9"/>
@@ -69017,55 +69113,527 @@
       </c>
       <c r="AN207" s="9"/>
     </row>
-    <row r="208" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A208" s="9" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B208" s="9" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C208" s="9" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D208" s="9" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E208" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F208" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="G208" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H208" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I208" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J208" s="9">
+        <v>6533</v>
+      </c>
+      <c r="K208" s="9" t="s">
+        <v>1801</v>
+      </c>
+      <c r="L208" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M208" s="10">
+        <v>4.884259259259259E-2</v>
+      </c>
+      <c r="N208" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O208" s="9" t="s">
+        <v>1802</v>
+      </c>
+      <c r="P208" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q208" s="10">
+        <v>1.361111111111111E-2</v>
+      </c>
+      <c r="R208" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="S208" s="10">
+        <v>0.31245370370370368</v>
+      </c>
+      <c r="T208" s="9">
+        <v>88.581999999999994</v>
+      </c>
+      <c r="U208" s="9">
+        <v>16.45</v>
+      </c>
+      <c r="V208" s="10">
+        <v>0.22439814814814821</v>
+      </c>
+      <c r="W208" s="10">
+        <v>5.6400462962962958E-2</v>
+      </c>
+      <c r="X208" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y208" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z208" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA208" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB208" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC208" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD208" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE208" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF208" s="9" t="s">
+        <v>1803</v>
+      </c>
+      <c r="AG208" s="9" t="s">
+        <v>1804</v>
+      </c>
+      <c r="AH208" s="9">
+        <v>6.2303579999999998</v>
+      </c>
+      <c r="AI208" s="9">
+        <v>-75.596035999999998</v>
+      </c>
+      <c r="AJ208" s="9" t="s">
+        <v>1805</v>
+      </c>
+      <c r="AK208" s="9">
+        <v>6.2726850000000001</v>
+      </c>
+      <c r="AL208" s="9">
+        <v>-75.601995000000002</v>
+      </c>
+      <c r="AM208" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN208" s="9"/>
     </row>
-    <row r="209" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A209" s="9" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B209" s="9" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C209" s="9" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D209" s="9" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E209" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F209" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="G209" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="H209" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="I209" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J209" s="9">
+        <v>6535</v>
+      </c>
+      <c r="K209" s="9" t="s">
+        <v>1809</v>
+      </c>
+      <c r="L209" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M209" s="10">
+        <v>3.2418981481481479E-2</v>
+      </c>
+      <c r="N209" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O209" s="9" t="s">
+        <v>1810</v>
+      </c>
+      <c r="P209" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q209" s="10">
+        <v>4.6759259259259263E-3</v>
+      </c>
+      <c r="R209" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S209" s="10">
+        <v>0.27774305555555562</v>
+      </c>
+      <c r="T209" s="9">
+        <v>86.786000000000001</v>
+      </c>
+      <c r="U209" s="9">
+        <v>17.77</v>
+      </c>
+      <c r="V209" s="10">
+        <v>0.20351851851851849</v>
+      </c>
+      <c r="W209" s="10">
+        <v>5.3148148148148153E-2</v>
+      </c>
+      <c r="X209" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y209" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z209" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA209" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB209" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC209" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD209" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE209" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF209" s="9" t="s">
+        <v>1811</v>
+      </c>
+      <c r="AG209" s="9" t="s">
+        <v>1812</v>
+      </c>
+      <c r="AH209" s="9">
+        <v>6.2267989999999998</v>
+      </c>
+      <c r="AI209" s="9">
+        <v>-75.599269000000007</v>
+      </c>
+      <c r="AJ209" s="9" t="s">
+        <v>1813</v>
+      </c>
+      <c r="AK209" s="9">
+        <v>6.2903760000000002</v>
+      </c>
+      <c r="AL209" s="9">
+        <v>-75.546627000000001</v>
+      </c>
+      <c r="AM209" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN209" s="9"/>
     </row>
-    <row r="210" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A210" s="9" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B210" s="9" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C210" s="9" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D210" s="9" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E210" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F210" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="G210" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H210" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="I210" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J210" s="9">
+        <v>2501</v>
+      </c>
+      <c r="K210" s="9" t="s">
+        <v>1817</v>
+      </c>
+      <c r="L210" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M210" s="10">
+        <v>2.90162037037037E-2</v>
+      </c>
+      <c r="N210" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O210" s="9" t="s">
+        <v>1818</v>
+      </c>
+      <c r="P210" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q210" s="10">
+        <v>9.6736111111111106E-2</v>
+      </c>
+      <c r="R210" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S210" s="10">
+        <v>0.18228009259259259</v>
+      </c>
+      <c r="T210" s="9">
+        <v>34.625999999999998</v>
+      </c>
+      <c r="U210" s="9">
+        <v>9.35</v>
+      </c>
+      <c r="V210" s="10">
+        <v>0.1542708333333333</v>
+      </c>
+      <c r="W210" s="10">
+        <v>0.1052777777777778</v>
+      </c>
+      <c r="X210" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y210" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z210" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA210" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB210" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC210" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD210" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE210" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF210" s="9" t="s">
+        <v>1819</v>
+      </c>
+      <c r="AG210" s="9" t="s">
+        <v>1820</v>
+      </c>
+      <c r="AH210" s="9">
+        <v>6.2270529999999997</v>
+      </c>
+      <c r="AI210" s="9">
+        <v>-75.599639999999994</v>
+      </c>
+      <c r="AJ210" s="9" t="s">
+        <v>1821</v>
+      </c>
+      <c r="AK210" s="9">
+        <v>6.2518269999999996</v>
+      </c>
+      <c r="AL210" s="9">
+        <v>-75.551843000000005</v>
+      </c>
+      <c r="AM210" s="26">
+        <f t="shared" si="3"/>
+        <v>9.6736111111111106E-2</v>
+      </c>
       <c r="AN210" s="9"/>
     </row>
-    <row r="211" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A211" s="9" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B211" s="9" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C211" s="9" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D211" s="9" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E211" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F211" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="G211" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="H211" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="I211" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J211" s="9">
+        <v>7696</v>
+      </c>
+      <c r="K211" s="9" t="s">
+        <v>1824</v>
+      </c>
+      <c r="L211" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M211" s="10">
+        <v>3.7970972222222232E-2</v>
+      </c>
+      <c r="N211" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O211" s="9" t="s">
+        <v>1825</v>
+      </c>
+      <c r="P211" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q211" s="10">
+        <v>1.2811458333333329E-3</v>
+      </c>
+      <c r="R211" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S211" s="10">
+        <v>0.2866898263888889</v>
+      </c>
+      <c r="T211" s="9">
+        <v>44.908000000000001</v>
+      </c>
+      <c r="U211" s="9">
+        <v>9.27</v>
+      </c>
+      <c r="V211" s="10">
+        <v>0.20188391203703701</v>
+      </c>
+      <c r="W211" s="10">
+        <v>0.15990696759259251</v>
+      </c>
+      <c r="X211" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y211" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z211" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA211" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB211" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC211" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD211" s="9">
+        <v>2</v>
+      </c>
+      <c r="AE211" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF211" s="9" t="s">
+        <v>1829</v>
+      </c>
+      <c r="AG211" s="9" t="s">
+        <v>1826</v>
+      </c>
+      <c r="AH211" s="9">
+        <v>6.226718</v>
+      </c>
+      <c r="AI211" s="9">
+        <v>-75.599287000000004</v>
+      </c>
+      <c r="AJ211" s="9" t="s">
+        <v>1827</v>
+      </c>
+      <c r="AK211" s="9">
+        <v>6.2615350000000003</v>
+      </c>
+      <c r="AL211" s="9">
+        <v>-75.592327999999995</v>
+      </c>
+      <c r="AM211" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN211" s="9"/>
     </row>
-    <row r="212" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN212" s="9"/>
     </row>
-    <row r="213" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN213" s="9"/>
     </row>
-    <row r="214" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN214" s="9"/>
     </row>
-    <row r="215" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN215" s="9"/>
     </row>
-    <row r="216" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN216" s="9"/>
     </row>
-    <row r="217" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN217" s="9"/>
     </row>
-    <row r="218" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN218" s="9"/>
     </row>
-    <row r="219" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN219" s="9"/>
     </row>
-    <row r="220" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN220" s="9"/>
     </row>
-    <row r="221" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN221" s="9"/>
     </row>
-    <row r="222" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN222" s="9"/>
     </row>
-    <row r="223" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN223" s="9"/>
     </row>
-    <row r="224" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN224" s="9"/>
     </row>
     <row r="225" spans="40:40" x14ac:dyDescent="0.25">
@@ -69383,9 +69951,6 @@
     <row r="329" spans="40:40" x14ac:dyDescent="0.25">
       <c r="AN329" s="9"/>
     </row>
-    <row r="330" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN330" s="9"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="N1:N1048576">
@@ -69399,7 +69964,7 @@
       <formula>"INICIO TARDÍO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R1048573">
+  <conditionalFormatting sqref="R1:R1048572">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"TERMINÓ DESPUÉS"</formula>
     </cfRule>

--- a/BASE_RECORRIDOS_PRO_JCA.xlsx
+++ b/BASE_RECORRIDOS_PRO_JCA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\INTERVENTORIA VELNEC\Recorridos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4007FCDD-5BE3-4D98-A1B1-FD31D0B6EB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F03448-E295-4203-BC9A-465C4CD71B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4958" uniqueCount="1830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4977" uniqueCount="1837">
   <si>
     <t>ID</t>
   </si>
@@ -5540,6 +5540,27 @@
   </si>
   <si>
     <t>Inicio GPS anterior al horario: 00:54:41 antes de las 18:00.; Fin GPS dentro de la tolerancia del horario programado.; 2 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>74495a6fa19689de</t>
+  </si>
+  <si>
+    <t>21_09_2026_IQ_Noct.gpx</t>
+  </si>
+  <si>
+    <t>74495a6fa19689dec156654a51031c211e6db1b376f23ddef8a0e02cd742a84e</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:52:55</t>
+  </si>
+  <si>
+    <t>21/09/2026 23:52:10</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 01:07:05 antes de las 18:00.; Fin GPS dentro de la tolerancia del horario programado.; 4 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.307972, -75.566957</t>
   </si>
 </sst>
 </file>
@@ -67656,7 +67677,7 @@
         <v>-75.546586000000005</v>
       </c>
       <c r="AM195" s="26">
-        <f t="shared" ref="AM195:AM211" si="3">IF(N195="INICIO TARDÍO",M195,0)+IF(R195="TERMINÓ ANTES",Q195,0)</f>
+        <f t="shared" ref="AM195:AM212" si="3">IF(N195="INICIO TARDÍO",M195,0)+IF(R195="TERMINÓ ANTES",Q195,0)</f>
         <v>0</v>
       </c>
       <c r="AN195" s="9"/>
@@ -69597,7 +69618,125 @@
       </c>
       <c r="AN211" s="9"/>
     </row>
-    <row r="212" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A212" s="9" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B212" s="9" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C212" s="9" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D212" s="9" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E212" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F212" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="G212" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="H212" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="I212" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J212" s="9">
+        <v>1903</v>
+      </c>
+      <c r="K212" s="9" t="s">
+        <v>1833</v>
+      </c>
+      <c r="L212" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M212" s="10">
+        <v>4.6585648148148147E-2</v>
+      </c>
+      <c r="N212" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O212" s="9" t="s">
+        <v>1834</v>
+      </c>
+      <c r="P212" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q212" s="10">
+        <v>5.4398148148148149E-3</v>
+      </c>
+      <c r="R212" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S212" s="10">
+        <v>0.29114583333333333</v>
+      </c>
+      <c r="T212" s="9">
+        <v>37.201000000000001</v>
+      </c>
+      <c r="U212" s="9">
+        <v>11.62</v>
+      </c>
+      <c r="V212" s="10">
+        <v>0.13340277777777779</v>
+      </c>
+      <c r="W212" s="10">
+        <v>9.931712962962963E-2</v>
+      </c>
+      <c r="X212" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y212" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z212" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA212" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB212" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC212" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD212" s="9">
+        <v>4</v>
+      </c>
+      <c r="AE212" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF212" s="9" t="s">
+        <v>1835</v>
+      </c>
+      <c r="AG212" s="9" t="s">
+        <v>1694</v>
+      </c>
+      <c r="AH212" s="9">
+        <v>6.2644299999999999</v>
+      </c>
+      <c r="AI212" s="9">
+        <v>-75.570660000000004</v>
+      </c>
+      <c r="AJ212" s="9" t="s">
+        <v>1836</v>
+      </c>
+      <c r="AK212" s="9">
+        <v>6.3079720000000004</v>
+      </c>
+      <c r="AL212" s="9">
+        <v>-75.566957000000002</v>
+      </c>
+      <c r="AM212" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN212" s="9"/>
     </row>
     <row r="213" spans="1:40" x14ac:dyDescent="0.25">

--- a/BASE_RECORRIDOS_PRO_JCA.xlsx
+++ b/BASE_RECORRIDOS_PRO_JCA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\INTERVENTORIA VELNEC\Recorridos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F03448-E295-4203-BC9A-465C4CD71B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9ECCAE1-EBAA-4BF1-A439-C1C011CD6745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="24240" windowHeight="13020" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GRAFICAS" sheetId="7" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4977" uniqueCount="1837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5148" uniqueCount="1906">
   <si>
     <t>ID</t>
   </si>
@@ -5561,6 +5561,213 @@
   </si>
   <si>
     <t>6.307972, -75.566957</t>
+  </si>
+  <si>
+    <t>2a5d12d522d0ec56</t>
+  </si>
+  <si>
+    <t>22_09_2026_AO_Diur.gpx</t>
+  </si>
+  <si>
+    <t>2a5d12d522d0ec56261ab7d8d6b1630a43e635bab73594f1404ba06b34c31210</t>
+  </si>
+  <si>
+    <t>22/09/2026</t>
+  </si>
+  <si>
+    <t>22/09/2026 08:59:19</t>
+  </si>
+  <si>
+    <t>22/09/2026 15:52:59</t>
+  </si>
+  <si>
+    <t>Inicio GPS tardío: 00:29:20 después de las 08:30.; Fin GPS anticipado: 00:37:01 antes de las 16:30.; 4 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.202817, -75.600998</t>
+  </si>
+  <si>
+    <t>6.221707, -75.593844</t>
+  </si>
+  <si>
+    <t>7dc74d5317f3bd9f</t>
+  </si>
+  <si>
+    <t>22_09_2026_AR_Diur.gpx</t>
+  </si>
+  <si>
+    <t>7dc74d5317f3bd9fe1c3149f518fceb8b65009e52b7a0f0f33c11d75a47426b8</t>
+  </si>
+  <si>
+    <t>22/09/2026 08:02:58</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:27:39</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 00:27:02 antes de las 08:30.; Fin GPS dentro de la tolerancia del horario programado.; 2 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.225834, -75.599425</t>
+  </si>
+  <si>
+    <t>6.243712, -75.598613</t>
+  </si>
+  <si>
+    <t>70230eb672e9cc1f</t>
+  </si>
+  <si>
+    <t>22_09_2026_DR_Diur.gpx</t>
+  </si>
+  <si>
+    <t>70230eb672e9cc1f3460be4ad96f5705a18da9ce7ecdad2e58586d5e223e77af</t>
+  </si>
+  <si>
+    <t>22/09/2026 08:32:25</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:42:18</t>
+  </si>
+  <si>
+    <t>6.235689, -75.602202</t>
+  </si>
+  <si>
+    <t>6.256139, -75.598315</t>
+  </si>
+  <si>
+    <t>98c040a5bcec5b7b</t>
+  </si>
+  <si>
+    <t>22_09_2026_HC_Diur.gpx</t>
+  </si>
+  <si>
+    <t>98c040a5bcec5b7bf78e262a0f96c39560ec3f7438dae6d9eda28651eefdd49d</t>
+  </si>
+  <si>
+    <t>22/09/2026 08:22:01</t>
+  </si>
+  <si>
+    <t>22/09/2026 14:08:55</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS anticipado: 02:21:05 antes de las 16:30.; 1 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.225723, -75.599263</t>
+  </si>
+  <si>
+    <t>6.259351, -75.597240</t>
+  </si>
+  <si>
+    <t>244c815a07a75689</t>
+  </si>
+  <si>
+    <t>22_09_2026_JA_Diur.gpx</t>
+  </si>
+  <si>
+    <t>244c815a07a75689811bc095a5e4a5678d913ccb5415086f04a495333900a1b9</t>
+  </si>
+  <si>
+    <t>22/09/2026 08:33:40</t>
+  </si>
+  <si>
+    <t>22/09/2026 13:22:19</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS anticipado: 03:07:41 antes de las 16:30.</t>
+  </si>
+  <si>
+    <t>6.225658, -75.599198</t>
+  </si>
+  <si>
+    <t>6.236572, -75.558755</t>
+  </si>
+  <si>
+    <t>6c10f9a23867b808</t>
+  </si>
+  <si>
+    <t>22_09_2026_JO_Diur.gpx</t>
+  </si>
+  <si>
+    <t>6c10f9a23867b80804f0e0d3026cbd2377a4e84295aabb81f604aef45752b27f</t>
+  </si>
+  <si>
+    <t>22/09/2026 08:20:47</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:34:54</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS dentro de la tolerancia del horario programado.; 14 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.225457, -75.599381</t>
+  </si>
+  <si>
+    <t>6.259262, -75.620933</t>
+  </si>
+  <si>
+    <t>f27b71b164cba290</t>
+  </si>
+  <si>
+    <t>22_09_2026_JZ_Diur.gpx</t>
+  </si>
+  <si>
+    <t>f27b71b164cba290e70f9cddfe830ad09af83e603900c2951d4a153691fc0b60</t>
+  </si>
+  <si>
+    <t>22/09/2026 08:30:53</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:32:51</t>
+  </si>
+  <si>
+    <t>6.226507, -75.599345</t>
+  </si>
+  <si>
+    <t>6.279424, -75.569649</t>
+  </si>
+  <si>
+    <t>0b975ab9cf7f549f</t>
+  </si>
+  <si>
+    <t>22_09_2026_SJ_Diur.gpx</t>
+  </si>
+  <si>
+    <t>0b975ab9cf7f549facbafc790c2cc7d87714627553ac9528f465dd26e9525b18</t>
+  </si>
+  <si>
+    <t>22/09/2026 08:22:52</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:24:55</t>
+  </si>
+  <si>
+    <t>6.225703, -75.599447</t>
+  </si>
+  <si>
+    <t>6.308651, -75.580760</t>
+  </si>
+  <si>
+    <t>08614fea07320d08</t>
+  </si>
+  <si>
+    <t>22_09_2026_YL_Diur.gpx</t>
+  </si>
+  <si>
+    <t>08614fea07320d08084c2296fd70d2e13d8b0c1f17fdd4872e33583594595dbf</t>
+  </si>
+  <si>
+    <t>22/09/2026 08:32:21</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:33:25</t>
+  </si>
+  <si>
+    <t>6.225757, -75.599180</t>
+  </si>
+  <si>
+    <t>6.258719, -75.616753</t>
   </si>
 </sst>
 </file>
@@ -5898,6 +6105,61 @@
     </dxf>
     <dxf>
       <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <sz val="14"/>
       </font>
     </dxf>
@@ -5994,61 +6256,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="26" formatCode="h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -39644,6 +39851,546 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
+  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" m="1" x="4"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="13"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="15">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="34" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
+  <location ref="A107:D123" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="8"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Suma de Kilómetros" fld="19" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="16" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B44BF58-179E-4C57-BD89-E6E3367D37B9}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
   <location ref="K107:M122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
@@ -39801,13 +40548,13 @@
     <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="17">
+    <format dxfId="27">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="26">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="13">
@@ -39828,26 +40575,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="21">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="20">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="13">
@@ -39868,17 +40615,17 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="8">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -39944,7 +40691,283 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E67C1C-2F15-4D2B-A97A-A1B46B6F5B69}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
+  <location ref="A57:E73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item m="1" x="4"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="17"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="8">
+    <chartFormat chart="24" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="15" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="16" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="21" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="22" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="23" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="24" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0966AFF-8B15-4A0E-BE48-1F64EB76CB37}" name="TablaDinámica7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="57">
   <location ref="AI107:AJ122" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
@@ -40088,13 +41111,13 @@
     <dataField name="Cuenta de Turno" fld="8" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="10">
-    <format dxfId="27">
+    <format dxfId="37">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="36">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="35">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="13">
@@ -40115,19 +41138,19 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="24">
+    <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="33">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="32">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="31">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="13">
@@ -40148,10 +41171,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="28">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -40205,7 +41228,295 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D330A9A-54B8-43DD-8D11-CC5633B99CDA}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+  <location ref="A6:E22" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item m="1" x="4"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="13"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="6" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="9">
+    <chartFormat chart="5" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{238AB259-E577-48AC-B3A0-09F752F5685D}" name="TablaDinámica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A169:B185" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="43">
@@ -41004,7 +42315,7 @@
     <dataField name="Suma de Sumatoria de tiempo total sin recorrido" fld="38" baseField="6" baseItem="0" numFmtId="21"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="28">
+    <format dxfId="38">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -41014,1110 +42325,6 @@
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
-  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item h="1" m="1" x="4"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="13"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="10">
-    <format dxfId="38">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="37">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="36">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="35">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="34">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="33">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="32">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="31">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="30">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="29">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="34" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E67C1C-2F15-4D2B-A97A-A1B46B6F5B69}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
-  <location ref="A57:E73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item m="1" x="4"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="17"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="8">
-    <chartFormat chart="24" format="13" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="14" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="15" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="16" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="21" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="22" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="23" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="24" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
-  <location ref="A107:D123" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="8"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Suma de Kilómetros" fld="19" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="6">
-    <chartFormat chart="16" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="12"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="12"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D330A9A-54B8-43DD-8D11-CC5633B99CDA}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
-  <location ref="A6:E22" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item m="1" x="4"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="13"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="6" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="9">
-    <chartFormat chart="5" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="10" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="11" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="12" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="3"/>
           </reference>
         </references>
       </pivotArea>
@@ -67677,7 +67884,7 @@
         <v>-75.546586000000005</v>
       </c>
       <c r="AM195" s="26">
-        <f t="shared" ref="AM195:AM212" si="3">IF(N195="INICIO TARDÍO",M195,0)+IF(R195="TERMINÓ ANTES",Q195,0)</f>
+        <f t="shared" ref="AM195:AM221" si="3">IF(N195="INICIO TARDÍO",M195,0)+IF(R195="TERMINÓ ANTES",Q195,0)</f>
         <v>0</v>
       </c>
       <c r="AN195" s="9"/>
@@ -69739,31 +69946,1093 @@
       </c>
       <c r="AN212" s="9"/>
     </row>
-    <row r="213" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A213" s="9" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B213" s="9" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C213" s="9" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D213" s="9" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E213" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F213" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G213" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H213" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I213" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J213" s="9">
+        <v>7151</v>
+      </c>
+      <c r="K213" s="9" t="s">
+        <v>1841</v>
+      </c>
+      <c r="L213" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M213" s="10">
+        <v>2.036958333333333E-2</v>
+      </c>
+      <c r="N213" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O213" s="9" t="s">
+        <v>1842</v>
+      </c>
+      <c r="P213" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q213" s="10">
+        <v>2.5703993055555551E-2</v>
+      </c>
+      <c r="R213" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S213" s="10">
+        <v>0.28725975694444439</v>
+      </c>
+      <c r="T213" s="9">
+        <v>52.847999999999999</v>
+      </c>
+      <c r="U213" s="9">
+        <v>16.52</v>
+      </c>
+      <c r="V213" s="10">
+        <v>0.13325322916666699</v>
+      </c>
+      <c r="W213" s="10">
+        <v>7.095622685185185E-2</v>
+      </c>
+      <c r="X213" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y213" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z213" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA213" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB213" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC213" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD213" s="9">
+        <v>4</v>
+      </c>
+      <c r="AE213" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF213" s="9" t="s">
+        <v>1843</v>
+      </c>
+      <c r="AG213" s="9" t="s">
+        <v>1844</v>
+      </c>
+      <c r="AH213" s="9">
+        <v>6.2028169999999996</v>
+      </c>
+      <c r="AI213" s="9">
+        <v>-75.600998000000004</v>
+      </c>
+      <c r="AJ213" s="9" t="s">
+        <v>1845</v>
+      </c>
+      <c r="AK213" s="9">
+        <v>6.2217070000000003</v>
+      </c>
+      <c r="AL213" s="9">
+        <v>-75.593844000000004</v>
+      </c>
+      <c r="AM213" s="26">
+        <f t="shared" si="3"/>
+        <v>4.6073576388888884E-2</v>
+      </c>
       <c r="AN213" s="9"/>
     </row>
-    <row r="214" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A214" s="9" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B214" s="9" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C214" s="9" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D214" s="9" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E214" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F214" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G214" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H214" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I214" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J214" s="9">
+        <v>3653</v>
+      </c>
+      <c r="K214" s="9" t="s">
+        <v>1849</v>
+      </c>
+      <c r="L214" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M214" s="10">
+        <v>1.877314814814815E-2</v>
+      </c>
+      <c r="N214" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O214" s="9" t="s">
+        <v>1850</v>
+      </c>
+      <c r="P214" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q214" s="10">
+        <v>1.631944444444445E-3</v>
+      </c>
+      <c r="R214" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S214" s="10">
+        <v>0.35047453703703701</v>
+      </c>
+      <c r="T214" s="9">
+        <v>47.334000000000003</v>
+      </c>
+      <c r="U214" s="9">
+        <v>8.1300000000000008</v>
+      </c>
+      <c r="V214" s="10">
+        <v>0.2426388888888889</v>
+      </c>
+      <c r="W214" s="10">
+        <v>0.16981481481481481</v>
+      </c>
+      <c r="X214" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y214" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z214" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA214" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB214" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC214" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD214" s="9">
+        <v>2</v>
+      </c>
+      <c r="AE214" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF214" s="9" t="s">
+        <v>1851</v>
+      </c>
+      <c r="AG214" s="9" t="s">
+        <v>1852</v>
+      </c>
+      <c r="AH214" s="9">
+        <v>6.2258339999999999</v>
+      </c>
+      <c r="AI214" s="9">
+        <v>-75.599424999999997</v>
+      </c>
+      <c r="AJ214" s="9" t="s">
+        <v>1853</v>
+      </c>
+      <c r="AK214" s="9">
+        <v>6.2437120000000004</v>
+      </c>
+      <c r="AL214" s="9">
+        <v>-75.598613</v>
+      </c>
+      <c r="AM214" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN214" s="9"/>
     </row>
-    <row r="215" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A215" s="9" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C215" s="9" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D215" s="9" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E215" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F215" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G215" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="H215" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I215" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J215" s="9">
+        <v>1798</v>
+      </c>
+      <c r="K215" s="9" t="s">
+        <v>1857</v>
+      </c>
+      <c r="L215" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M215" s="10">
+        <v>1.678240740740741E-3</v>
+      </c>
+      <c r="N215" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O215" s="9" t="s">
+        <v>1858</v>
+      </c>
+      <c r="P215" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q215" s="10">
+        <v>8.5416666666666662E-3</v>
+      </c>
+      <c r="R215" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S215" s="10">
+        <v>0.34019675925925918</v>
+      </c>
+      <c r="T215" s="9">
+        <v>23.113</v>
+      </c>
+      <c r="U215" s="9">
+        <v>3.66</v>
+      </c>
+      <c r="V215" s="10">
+        <v>0.26317129629629632</v>
+      </c>
+      <c r="W215" s="10">
+        <v>0.22045138888888891</v>
+      </c>
+      <c r="X215" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y215" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z215" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA215" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB215" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC215" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD215" s="9">
+        <v>2</v>
+      </c>
+      <c r="AE215" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF215" s="9" t="s">
+        <v>1384</v>
+      </c>
+      <c r="AG215" s="9" t="s">
+        <v>1859</v>
+      </c>
+      <c r="AH215" s="9">
+        <v>6.2356889999999998</v>
+      </c>
+      <c r="AI215" s="9">
+        <v>-75.602202000000005</v>
+      </c>
+      <c r="AJ215" s="9" t="s">
+        <v>1860</v>
+      </c>
+      <c r="AK215" s="9">
+        <v>6.2561390000000001</v>
+      </c>
+      <c r="AL215" s="9">
+        <v>-75.598314999999999</v>
+      </c>
+      <c r="AM215" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN215" s="9"/>
     </row>
-    <row r="216" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A216" s="9" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B216" s="9" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C216" s="9" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D216" s="9" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E216" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F216" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G216" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H216" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I216" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J216" s="9">
+        <v>3615</v>
+      </c>
+      <c r="K216" s="9" t="s">
+        <v>1864</v>
+      </c>
+      <c r="L216" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M216" s="10">
+        <v>5.5439814814814813E-3</v>
+      </c>
+      <c r="N216" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O216" s="9" t="s">
+        <v>1865</v>
+      </c>
+      <c r="P216" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q216" s="10">
+        <v>9.7974537037037041E-2</v>
+      </c>
+      <c r="R216" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S216" s="10">
+        <v>0.2409027777777778</v>
+      </c>
+      <c r="T216" s="9">
+        <v>46.113</v>
+      </c>
+      <c r="U216" s="9">
+        <v>12.03</v>
+      </c>
+      <c r="V216" s="10">
+        <v>0.15967592592592589</v>
+      </c>
+      <c r="W216" s="10">
+        <v>6.6458333333333328E-2</v>
+      </c>
+      <c r="X216" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y216" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD216" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE216" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF216" s="9" t="s">
+        <v>1866</v>
+      </c>
+      <c r="AG216" s="9" t="s">
+        <v>1867</v>
+      </c>
+      <c r="AH216" s="9">
+        <v>6.2257230000000003</v>
+      </c>
+      <c r="AI216" s="9">
+        <v>-75.599262999999993</v>
+      </c>
+      <c r="AJ216" s="9" t="s">
+        <v>1868</v>
+      </c>
+      <c r="AK216" s="9">
+        <v>6.2593509999999997</v>
+      </c>
+      <c r="AL216" s="9">
+        <v>-75.597239999999999</v>
+      </c>
+      <c r="AM216" s="26">
+        <f t="shared" si="3"/>
+        <v>9.7974537037037041E-2</v>
+      </c>
       <c r="AN216" s="9"/>
     </row>
-    <row r="217" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A217" s="9" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B217" s="9" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C217" s="9" t="s">
+        <v>1871</v>
+      </c>
+      <c r="D217" s="9" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E217" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F217" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G217" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H217" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I217" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J217" s="9">
+        <v>3597</v>
+      </c>
+      <c r="K217" s="9" t="s">
+        <v>1872</v>
+      </c>
+      <c r="L217" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M217" s="10">
+        <v>2.5462962962962969E-3</v>
+      </c>
+      <c r="N217" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O217" s="9" t="s">
+        <v>1873</v>
+      </c>
+      <c r="P217" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q217" s="10">
+        <v>0.13033564814814819</v>
+      </c>
+      <c r="R217" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S217" s="10">
+        <v>0.20045138888888889</v>
+      </c>
+      <c r="T217" s="9">
+        <v>49.512</v>
+      </c>
+      <c r="U217" s="9">
+        <v>13.5</v>
+      </c>
+      <c r="V217" s="10">
+        <v>0.15283564814814821</v>
+      </c>
+      <c r="W217" s="10">
+        <v>8.7638888888888891E-2</v>
+      </c>
+      <c r="X217" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y217" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z217" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA217" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB217" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC217" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD217" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE217" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF217" s="9" t="s">
+        <v>1874</v>
+      </c>
+      <c r="AG217" s="9" t="s">
+        <v>1875</v>
+      </c>
+      <c r="AH217" s="9">
+        <v>6.2256580000000001</v>
+      </c>
+      <c r="AI217" s="9">
+        <v>-75.599198000000001</v>
+      </c>
+      <c r="AJ217" s="9" t="s">
+        <v>1876</v>
+      </c>
+      <c r="AK217" s="9">
+        <v>6.2365719999999998</v>
+      </c>
+      <c r="AL217" s="9">
+        <v>-75.558755000000005</v>
+      </c>
+      <c r="AM217" s="26">
+        <f t="shared" si="3"/>
+        <v>0.13033564814814819</v>
+      </c>
       <c r="AN217" s="9"/>
     </row>
-    <row r="218" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A218" s="9" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B218" s="9" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C218" s="9" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D218" s="9" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E218" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F218" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G218" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H218" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I218" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J218" s="9">
+        <v>6586</v>
+      </c>
+      <c r="K218" s="9" t="s">
+        <v>1880</v>
+      </c>
+      <c r="L218" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M218" s="10">
+        <v>6.3894212962962967E-3</v>
+      </c>
+      <c r="N218" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O218" s="9" t="s">
+        <v>1881</v>
+      </c>
+      <c r="P218" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q218" s="10">
+        <v>3.4135300925925921E-3</v>
+      </c>
+      <c r="R218" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S218" s="10">
+        <v>0.34313628472222218</v>
+      </c>
+      <c r="T218" s="9">
+        <v>44.564</v>
+      </c>
+      <c r="U218" s="9">
+        <v>18.09</v>
+      </c>
+      <c r="V218" s="10">
+        <v>0.102656215277778</v>
+      </c>
+      <c r="W218" s="10">
+        <v>4.8033599537037043E-2</v>
+      </c>
+      <c r="X218" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y218" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z218" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA218" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB218" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC218" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD218" s="9">
+        <v>14</v>
+      </c>
+      <c r="AE218" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF218" s="9" t="s">
+        <v>1882</v>
+      </c>
+      <c r="AG218" s="9" t="s">
+        <v>1883</v>
+      </c>
+      <c r="AH218" s="9">
+        <v>6.2254569999999996</v>
+      </c>
+      <c r="AI218" s="9">
+        <v>-75.599380999999994</v>
+      </c>
+      <c r="AJ218" s="9" t="s">
+        <v>1884</v>
+      </c>
+      <c r="AK218" s="9">
+        <v>6.2592619999999997</v>
+      </c>
+      <c r="AL218" s="9">
+        <v>-75.620932999999994</v>
+      </c>
+      <c r="AM218" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN218" s="9"/>
     </row>
-    <row r="219" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A219" s="9" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B219" s="9" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C219" s="9" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D219" s="9" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E219" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F219" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G219" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H219" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I219" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J219" s="9">
+        <v>4949</v>
+      </c>
+      <c r="K219" s="9" t="s">
+        <v>1888</v>
+      </c>
+      <c r="L219" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M219" s="10">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="N219" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O219" s="9" t="s">
+        <v>1889</v>
+      </c>
+      <c r="P219" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q219" s="10">
+        <v>1.9791666666666668E-3</v>
+      </c>
+      <c r="R219" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S219" s="10">
+        <v>0.33469907407407412</v>
+      </c>
+      <c r="T219" s="9">
+        <v>69.007999999999996</v>
+      </c>
+      <c r="U219" s="9">
+        <v>11.6</v>
+      </c>
+      <c r="V219" s="10">
+        <v>0.24787037037037041</v>
+      </c>
+      <c r="W219" s="10">
+        <v>0.1212037037037037</v>
+      </c>
+      <c r="X219" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y219" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z219" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA219" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB219" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC219" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD219" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE219" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF219" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="AG219" s="9" t="s">
+        <v>1890</v>
+      </c>
+      <c r="AH219" s="9">
+        <v>6.2265069999999998</v>
+      </c>
+      <c r="AI219" s="9">
+        <v>-75.599345</v>
+      </c>
+      <c r="AJ219" s="9" t="s">
+        <v>1891</v>
+      </c>
+      <c r="AK219" s="9">
+        <v>6.2794239999999997</v>
+      </c>
+      <c r="AL219" s="9">
+        <v>-75.569648999999998</v>
+      </c>
+      <c r="AM219" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN219" s="9"/>
     </row>
-    <row r="220" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A220" s="9" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B220" s="9" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C220" s="9" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D220" s="9" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E220" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F220" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G220" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H220" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="I220" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J220" s="9">
+        <v>2061</v>
+      </c>
+      <c r="K220" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="L220" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M220" s="10">
+        <v>4.9537037037037041E-3</v>
+      </c>
+      <c r="N220" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O220" s="9" t="s">
+        <v>1896</v>
+      </c>
+      <c r="P220" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q220" s="10">
+        <v>3.530092592592592E-3</v>
+      </c>
+      <c r="R220" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S220" s="10">
+        <v>0.33475694444444443</v>
+      </c>
+      <c r="T220" s="9">
+        <v>26.77</v>
+      </c>
+      <c r="U220" s="9">
+        <v>6.61</v>
+      </c>
+      <c r="V220" s="10">
+        <v>0.16878472222222221</v>
+      </c>
+      <c r="W220" s="10">
+        <v>0.1227314814814815</v>
+      </c>
+      <c r="X220" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y220" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z220" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA220" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB220" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC220" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD220" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE220" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF220" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="AG220" s="9" t="s">
+        <v>1897</v>
+      </c>
+      <c r="AH220" s="9">
+        <v>6.2257030000000002</v>
+      </c>
+      <c r="AI220" s="9">
+        <v>-75.599446999999998</v>
+      </c>
+      <c r="AJ220" s="9" t="s">
+        <v>1898</v>
+      </c>
+      <c r="AK220" s="9">
+        <v>6.3086510000000002</v>
+      </c>
+      <c r="AL220" s="9">
+        <v>-75.580759999999998</v>
+      </c>
+      <c r="AM220" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN220" s="9"/>
     </row>
-    <row r="221" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A221" s="9" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B221" s="9" t="s">
+        <v>1900</v>
+      </c>
+      <c r="C221" s="9" t="s">
+        <v>1901</v>
+      </c>
+      <c r="D221" s="9" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E221" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F221" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G221" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H221" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I221" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J221" s="9">
+        <v>3254</v>
+      </c>
+      <c r="K221" s="9" t="s">
+        <v>1902</v>
+      </c>
+      <c r="L221" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M221" s="10">
+        <v>1.631944444444445E-3</v>
+      </c>
+      <c r="N221" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O221" s="9" t="s">
+        <v>1903</v>
+      </c>
+      <c r="P221" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q221" s="10">
+        <v>2.3726851851851851E-3</v>
+      </c>
+      <c r="R221" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S221" s="10">
+        <v>0.33407407407407408</v>
+      </c>
+      <c r="T221" s="9">
+        <v>43.088000000000001</v>
+      </c>
+      <c r="U221" s="9">
+        <v>11.09</v>
+      </c>
+      <c r="V221" s="10">
+        <v>0.1618171296296296</v>
+      </c>
+      <c r="W221" s="10">
+        <v>9.2245370370370366E-2</v>
+      </c>
+      <c r="X221" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y221" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z221" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA221" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB221" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC221" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD221" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE221" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF221" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="AG221" s="9" t="s">
+        <v>1904</v>
+      </c>
+      <c r="AH221" s="9">
+        <v>6.2257569999999998</v>
+      </c>
+      <c r="AI221" s="9">
+        <v>-75.599180000000004</v>
+      </c>
+      <c r="AJ221" s="9" t="s">
+        <v>1905</v>
+      </c>
+      <c r="AK221" s="9">
+        <v>6.2587190000000001</v>
+      </c>
+      <c r="AL221" s="9">
+        <v>-75.616753000000003</v>
+      </c>
+      <c r="AM221" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN221" s="9"/>
     </row>
     <row r="222" spans="1:40" x14ac:dyDescent="0.25">

--- a/BASE_RECORRIDOS_PRO_JCA.xlsx
+++ b/BASE_RECORRIDOS_PRO_JCA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\INTERVENTORIA VELNEC\Recorridos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9ECCAE1-EBAA-4BF1-A439-C1C011CD6745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F6031B-1325-442A-9C49-23403B488E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="24240" windowHeight="13020" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5148" uniqueCount="1906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5243" uniqueCount="1946">
   <si>
     <t>ID</t>
   </si>
@@ -5768,6 +5768,126 @@
   </si>
   <si>
     <t>6.258719, -75.616753</t>
+  </si>
+  <si>
+    <t>22e3cf1e69577752</t>
+  </si>
+  <si>
+    <t>22_09_2026_IQ_Noct.gpx</t>
+  </si>
+  <si>
+    <t>22e3cf1e6957775221afa64285023da562984dae936caa954ee47dc6fc339b1e</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:26:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 23:44:29</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 01:34:00 antes de las 18:00.; Fin GPS anticipado: 00:15:31 antes de las 00:00.; 3 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.225582, -75.599125</t>
+  </si>
+  <si>
+    <t>6.243778, -75.556727</t>
+  </si>
+  <si>
+    <t>030c093ed850598e</t>
+  </si>
+  <si>
+    <t>22_09_2026_JHP_Noct.gpx</t>
+  </si>
+  <si>
+    <t>030c093ed850598ec0b41fe7b3c85401960f95f2dbbed6b59963263368016517</t>
+  </si>
+  <si>
+    <t>22/09/2026 17:21:13</t>
+  </si>
+  <si>
+    <t>23/09/2026 00:01:55</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 00:38:47 antes de las 18:00.; Fin GPS dentro de la tolerancia del horario programado.</t>
+  </si>
+  <si>
+    <t>6.226689, -75.599312</t>
+  </si>
+  <si>
+    <t>6.290541, -75.546397</t>
+  </si>
+  <si>
+    <t>6c6a01bf19af2e78</t>
+  </si>
+  <si>
+    <t>22_09_2026_JP_Noct.gpx</t>
+  </si>
+  <si>
+    <t>6c6a01bf19af2e78e9bcfc6cc317e47b2a3f8fca1ba9f4a003178fda7d114836</t>
+  </si>
+  <si>
+    <t>22/09/2026 17:43:40</t>
+  </si>
+  <si>
+    <t>22/09/2026 22:07:06</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 00:16:20 antes de las 18:00.; Fin GPS anticipado: 01:52:54 antes de las 00:00.</t>
+  </si>
+  <si>
+    <t>6.226945, -75.599697</t>
+  </si>
+  <si>
+    <t>6.251832, -75.551803</t>
+  </si>
+  <si>
+    <t>e2ed9061be63926a</t>
+  </si>
+  <si>
+    <t>e2ed9061be63926a391cd48dc7c044e90a74ac21cbda166b2d4e8ac09b45c814</t>
+  </si>
+  <si>
+    <t>22/09/2026 17:01:15</t>
+  </si>
+  <si>
+    <t>22/09/2026 23:57:14</t>
+  </si>
+  <si>
+    <t>6.226620, -75.598615</t>
+  </si>
+  <si>
+    <t>6.252440, -75.582687</t>
+  </si>
+  <si>
+    <t>43299031c0ccff50</t>
+  </si>
+  <si>
+    <t>22_09_2026_DV_Noct.gpx</t>
+  </si>
+  <si>
+    <t>43299031c0ccff50294b6f975c848301f36803586ffe271406e537e2a79cdfa0</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:55:24</t>
+  </si>
+  <si>
+    <t>23/09/2026 00:21:54</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 01:04:36 antes de las 18:00.; Fin GPS posterior: 00:21:54 después de las 00:00.</t>
+  </si>
+  <si>
+    <t>6.263043, -75.595582</t>
+  </si>
+  <si>
+    <t>6.272825, -75.602050</t>
+  </si>
+  <si>
+    <t>22_09_2026_LA_Noct.gpx</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 00:58:45 antes de las 18:00.; Fin GPS dentro de la tolerancia del horario programado.; 3 hueco(s) GPS &gt;= 10 min.</t>
   </si>
 </sst>
 </file>
@@ -6134,6 +6254,9 @@
       </font>
     </dxf>
     <dxf>
+      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
+    </dxf>
+    <dxf>
       <font>
         <sz val="14"/>
       </font>
@@ -6253,9 +6376,6 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
     </dxf>
     <dxf>
       <font>
@@ -24459,7 +24579,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="USER" refreshedDate="46283.800954629631" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="192" xr:uid="{FDEF9B37-15CF-42E8-BC5E-E1CE4649CF2B}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:AM553" sheet="RECORRIDOS"/>
+    <worksheetSource ref="A1:AM552" sheet="RECORRIDOS"/>
   </cacheSource>
   <cacheFields count="43">
     <cacheField name="ID" numFmtId="0">
@@ -25279,7 +25399,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="USER" refreshedDate="46283.800954861108" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="192" xr:uid="{4743F9B8-9139-4DCD-A807-2514F242574C}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:AF1048572" sheet="RECORRIDOS"/>
+    <worksheetSource ref="A1:AF1048571" sheet="RECORRIDOS"/>
   </cacheSource>
   <cacheFields count="32">
     <cacheField name="ID" numFmtId="0">
@@ -39851,1384 +39971,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
-  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item h="1" m="1" x="4"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="13"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="10">
-    <format dxfId="15">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="14">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="13">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="12">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="11">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="10">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="9">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="8">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="7">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="6">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="34" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
-  <location ref="A107:D123" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="8"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Suma de Kilómetros" fld="19" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="6">
-    <chartFormat chart="16" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="12"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="12"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B44BF58-179E-4C57-BD89-E6E3367D37B9}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
-  <location ref="K107:M122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item h="1" x="0"/>
-        <item h="1" m="1" x="4"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="17"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="12">
-    <format dxfId="27">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="26">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="25">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="24">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="23">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="17" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="22">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="21">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="20">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="19">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="18">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="17">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="17" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="16">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="28" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="28" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="28" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="28" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E67C1C-2F15-4D2B-A97A-A1B46B6F5B69}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
-  <location ref="A57:E73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item m="1" x="4"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="17"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="8">
-    <chartFormat chart="24" format="13" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="14" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="15" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="16" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="21" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="22" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="23" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="24" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0966AFF-8B15-4A0E-BE48-1F64EB76CB37}" name="TablaDinámica7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="57">
-  <location ref="AI107:AJ122" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item h="1" x="11"/>
-        <item h="1" x="12"/>
-        <item h="1" x="13"/>
-        <item h="1" x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Turno" fld="8" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="10">
-    <format dxfId="37">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="36">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="35">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="34">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="33">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="32">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="31">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="30">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="29">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="28">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="48" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="53" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="56" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D330A9A-54B8-43DD-8D11-CC5633B99CDA}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A6:E22" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
@@ -41516,7 +40258,547 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
+  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" m="1" x="4"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="13"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="15">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="34" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
+  <location ref="A107:D123" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="8"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Suma de Kilómetros" fld="19" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="16" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{238AB259-E577-48AC-B3A0-09F752F5685D}" name="TablaDinámica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A169:B185" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="43">
@@ -42315,7 +41597,7 @@
     <dataField name="Suma de Sumatoria de tiempo total sin recorrido" fld="38" baseField="6" baseItem="0" numFmtId="21"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="38">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -42342,9 +41624,847 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B44BF58-179E-4C57-BD89-E6E3367D37B9}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
+  <location ref="K107:M122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item h="1" x="0"/>
+        <item h="1" m="1" x="4"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="17"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="12">
+    <format dxfId="28">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="25">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="17" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="17" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="17">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="28" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="28" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="28" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="28" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E67C1C-2F15-4D2B-A97A-A1B46B6F5B69}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
+  <location ref="A57:E73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item m="1" x="4"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="17"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="8">
+    <chartFormat chart="24" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="15" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="16" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="21" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="22" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="23" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="24" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0966AFF-8B15-4A0E-BE48-1F64EB76CB37}" name="TablaDinámica7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="57">
+  <location ref="AI107:AJ122" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="13"/>
+        <item h="1" x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Turno" fld="8" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="38">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="37">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="35">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="33">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="32">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="31">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="48" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="53" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="56" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{07721E28-36B5-4676-BFC5-097A3B63190A}" name="Tabla1" displayName="Tabla1" ref="A1:AF1048572" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71">
-  <autoFilter ref="A1:AF1048572" xr:uid="{07721E28-36B5-4676-BFC5-097A3B63190A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{07721E28-36B5-4676-BFC5-097A3B63190A}" name="Tabla1" displayName="Tabla1" ref="A1:AF1048571" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71">
+  <autoFilter ref="A1:AF1048571" xr:uid="{07721E28-36B5-4676-BFC5-097A3B63190A}"/>
   <tableColumns count="32">
     <tableColumn id="1" xr3:uid="{BFACFB74-E6A6-4648-B0DA-7D6E1FC88A79}" name="ID" dataDxfId="70"/>
     <tableColumn id="2" xr3:uid="{B67B24E0-3585-47FC-A130-8F37C8640BC4}" name="Archivo" dataDxfId="69"/>
@@ -44182,7 +44302,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BB329"/>
+  <dimension ref="A1:BB328"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" style="9" customWidth="1"/>
@@ -44191,7 +44311,7 @@
     <col min="4" max="4" width="14.7109375" style="9" customWidth="1"/>
     <col min="5" max="5" width="12.140625" style="9" customWidth="1"/>
     <col min="6" max="6" width="11" style="9" customWidth="1"/>
-    <col min="7" max="7" width="26.140625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" style="9" customWidth="1"/>
     <col min="8" max="9" width="11" style="9" customWidth="1"/>
     <col min="10" max="10" width="15.140625" style="9" customWidth="1"/>
     <col min="11" max="11" width="24.85546875" style="9" customWidth="1"/>
@@ -67884,7 +68004,7 @@
         <v>-75.546586000000005</v>
       </c>
       <c r="AM195" s="26">
-        <f t="shared" ref="AM195:AM221" si="3">IF(N195="INICIO TARDÍO",M195,0)+IF(R195="TERMINÓ ANTES",Q195,0)</f>
+        <f t="shared" ref="AM195:AM226" si="3">IF(N195="INICIO TARDÍO",M195,0)+IF(R195="TERMINÓ ANTES",Q195,0)</f>
         <v>0</v>
       </c>
       <c r="AN195" s="9"/>
@@ -71035,61 +71155,651 @@
       </c>
       <c r="AN221" s="9"/>
     </row>
-    <row r="222" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A222" s="9" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C222" s="9" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D222" s="9" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E222" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F222" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G222" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="H222" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="I222" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J222" s="9">
+        <v>3626</v>
+      </c>
+      <c r="K222" s="9" t="s">
+        <v>1909</v>
+      </c>
+      <c r="L222" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M222" s="10">
+        <v>6.5277777777777782E-2</v>
+      </c>
+      <c r="N222" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O222" s="9" t="s">
+        <v>1910</v>
+      </c>
+      <c r="P222" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q222" s="10">
+        <v>1.0775462962962961E-2</v>
+      </c>
+      <c r="R222" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S222" s="10">
+        <v>0.30450231481481482</v>
+      </c>
+      <c r="T222" s="9">
+        <v>51.329000000000001</v>
+      </c>
+      <c r="U222" s="9">
+        <v>13.16</v>
+      </c>
+      <c r="V222" s="10">
+        <v>0.16250000000000001</v>
+      </c>
+      <c r="W222" s="10">
+        <v>9.2280092592592594E-2</v>
+      </c>
+      <c r="X222" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y222" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z222" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA222" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB222" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC222" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD222" s="9">
+        <v>3</v>
+      </c>
+      <c r="AE222" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF222" s="9" t="s">
+        <v>1911</v>
+      </c>
+      <c r="AG222" s="9" t="s">
+        <v>1912</v>
+      </c>
+      <c r="AH222" s="9">
+        <v>6.2255820000000002</v>
+      </c>
+      <c r="AI222" s="9">
+        <v>-75.599125000000001</v>
+      </c>
+      <c r="AJ222" s="9" t="s">
+        <v>1913</v>
+      </c>
+      <c r="AK222" s="9">
+        <v>6.2437779999999998</v>
+      </c>
+      <c r="AL222" s="9">
+        <v>-75.556726999999995</v>
+      </c>
+      <c r="AM222" s="26">
+        <f t="shared" si="3"/>
+        <v>1.0775462962962961E-2</v>
+      </c>
       <c r="AN222" s="9"/>
     </row>
-    <row r="223" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A223" s="9" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B223" s="9" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C223" s="9" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D223" s="9" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E223" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F223" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G223" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="H223" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="I223" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J223" s="9">
+        <v>6526</v>
+      </c>
+      <c r="K223" s="9" t="s">
+        <v>1917</v>
+      </c>
+      <c r="L223" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M223" s="10">
+        <v>2.6932870370370371E-2</v>
+      </c>
+      <c r="N223" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O223" s="9" t="s">
+        <v>1918</v>
+      </c>
+      <c r="P223" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q223" s="10">
+        <v>1.3310185185185181E-3</v>
+      </c>
+      <c r="R223" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S223" s="10">
+        <v>0.27826388888888892</v>
+      </c>
+      <c r="T223" s="9">
+        <v>90.361999999999995</v>
+      </c>
+      <c r="U223" s="9">
+        <v>16.829999999999998</v>
+      </c>
+      <c r="V223" s="10">
+        <v>0.22364583333333329</v>
+      </c>
+      <c r="W223" s="10">
+        <v>8.1701388888888893E-2</v>
+      </c>
+      <c r="X223" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y223" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z223" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA223" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB223" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC223" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD223" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE223" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF223" s="9" t="s">
+        <v>1919</v>
+      </c>
+      <c r="AG223" s="9" t="s">
+        <v>1920</v>
+      </c>
+      <c r="AH223" s="9">
+        <v>6.2266890000000004</v>
+      </c>
+      <c r="AI223" s="9">
+        <v>-75.599311999999998</v>
+      </c>
+      <c r="AJ223" s="9" t="s">
+        <v>1921</v>
+      </c>
+      <c r="AK223" s="9">
+        <v>6.2905410000000002</v>
+      </c>
+      <c r="AL223" s="9">
+        <v>-75.546396999999999</v>
+      </c>
+      <c r="AM223" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN223" s="9"/>
     </row>
-    <row r="224" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A224" s="9" t="s">
+        <v>1922</v>
+      </c>
+      <c r="B224" s="9" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C224" s="9" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D224" s="9" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E224" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F224" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G224" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H224" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="I224" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J224" s="9">
+        <v>2470</v>
+      </c>
+      <c r="K224" s="9" t="s">
+        <v>1925</v>
+      </c>
+      <c r="L224" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M224" s="10">
+        <v>1.134259259259259E-2</v>
+      </c>
+      <c r="N224" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O224" s="9" t="s">
+        <v>1926</v>
+      </c>
+      <c r="P224" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q224" s="10">
+        <v>7.840277777777778E-2</v>
+      </c>
+      <c r="R224" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S224" s="10">
+        <v>0.18293981481481481</v>
+      </c>
+      <c r="T224" s="9">
+        <v>32.774000000000001</v>
+      </c>
+      <c r="U224" s="9">
+        <v>10.53</v>
+      </c>
+      <c r="V224" s="10">
+        <v>0.12971064814814809</v>
+      </c>
+      <c r="W224" s="10">
+        <v>8.3935185185185182E-2</v>
+      </c>
+      <c r="X224" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y224" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z224" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA224" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB224" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC224" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD224" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE224" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF224" s="9" t="s">
+        <v>1927</v>
+      </c>
+      <c r="AG224" s="9" t="s">
+        <v>1928</v>
+      </c>
+      <c r="AH224" s="9">
+        <v>6.2269449999999997</v>
+      </c>
+      <c r="AI224" s="9">
+        <v>-75.599697000000006</v>
+      </c>
+      <c r="AJ224" s="9" t="s">
+        <v>1929</v>
+      </c>
+      <c r="AK224" s="9">
+        <v>6.2518320000000003</v>
+      </c>
+      <c r="AL224" s="9">
+        <v>-75.551803000000007</v>
+      </c>
+      <c r="AM224" s="26">
+        <f t="shared" si="3"/>
+        <v>7.840277777777778E-2</v>
+      </c>
       <c r="AN224" s="9"/>
     </row>
-    <row r="225" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A225" s="9" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B225" s="9" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C225" s="9" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D225" s="9" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E225" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F225" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G225" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H225" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I225" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J225" s="9">
+        <v>4471</v>
+      </c>
+      <c r="K225" s="9" t="s">
+        <v>1939</v>
+      </c>
+      <c r="L225" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M225" s="10">
+        <v>4.4861111111111109E-2</v>
+      </c>
+      <c r="N225" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O225" s="9" t="s">
+        <v>1940</v>
+      </c>
+      <c r="P225" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q225" s="10">
+        <v>1.5208333333333331E-2</v>
+      </c>
+      <c r="R225" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="S225" s="10">
+        <v>0.31006944444444451</v>
+      </c>
+      <c r="T225" s="9">
+        <v>56.018999999999998</v>
+      </c>
+      <c r="U225" s="9">
+        <v>11.32</v>
+      </c>
+      <c r="V225" s="10">
+        <v>0.20616898148148149</v>
+      </c>
+      <c r="W225" s="10">
+        <v>5.7951388888888893E-2</v>
+      </c>
+      <c r="X225" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y225" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z225" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA225" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB225" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC225" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD225" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE225" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF225" s="9" t="s">
+        <v>1941</v>
+      </c>
+      <c r="AG225" s="9" t="s">
+        <v>1942</v>
+      </c>
+      <c r="AH225" s="9">
+        <v>6.2630429999999997</v>
+      </c>
+      <c r="AI225" s="9">
+        <v>-75.595581999999993</v>
+      </c>
+      <c r="AJ225" s="9" t="s">
+        <v>1943</v>
+      </c>
+      <c r="AK225" s="9">
+        <v>6.2728250000000001</v>
+      </c>
+      <c r="AL225" s="9">
+        <v>-75.602050000000006</v>
+      </c>
+      <c r="AM225" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN225" s="9"/>
     </row>
-    <row r="226" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A226" s="9" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B226" s="9" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C226" s="9" t="s">
+        <v>1931</v>
+      </c>
+      <c r="D226" s="9" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E226" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F226" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G226" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="H226" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="I226" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J226" s="9">
+        <v>7824</v>
+      </c>
+      <c r="K226" s="9" t="s">
+        <v>1932</v>
+      </c>
+      <c r="L226" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M226" s="10">
+        <v>4.0795046296296288E-2</v>
+      </c>
+      <c r="N226" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O226" s="9" t="s">
+        <v>1933</v>
+      </c>
+      <c r="P226" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q226" s="10">
+        <v>1.9177314814814821E-3</v>
+      </c>
+      <c r="R226" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S226" s="10">
+        <v>0.28887731481481482</v>
+      </c>
+      <c r="T226" s="9">
+        <v>50.188000000000002</v>
+      </c>
+      <c r="U226" s="9">
+        <v>12.01</v>
+      </c>
+      <c r="V226" s="10">
+        <v>0.17411025462962959</v>
+      </c>
+      <c r="W226" s="10">
+        <v>0.1166204050925926</v>
+      </c>
+      <c r="X226" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y226" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z226" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA226" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB226" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC226" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD226" s="9">
+        <v>3</v>
+      </c>
+      <c r="AE226" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF226" s="9" t="s">
+        <v>1945</v>
+      </c>
+      <c r="AG226" s="9" t="s">
+        <v>1934</v>
+      </c>
+      <c r="AH226" s="9">
+        <v>6.2266199999999996</v>
+      </c>
+      <c r="AI226" s="9">
+        <v>-75.598614999999995</v>
+      </c>
+      <c r="AJ226" s="9" t="s">
+        <v>1935</v>
+      </c>
+      <c r="AK226" s="9">
+        <v>6.25244</v>
+      </c>
+      <c r="AL226" s="9">
+        <v>-75.582687000000007</v>
+      </c>
+      <c r="AM226" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN226" s="9"/>
     </row>
-    <row r="227" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN227" s="9"/>
     </row>
-    <row r="228" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN228" s="9"/>
     </row>
-    <row r="229" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN229" s="9"/>
     </row>
-    <row r="230" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN230" s="9"/>
     </row>
-    <row r="231" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN231" s="9"/>
     </row>
-    <row r="232" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN232" s="9"/>
     </row>
-    <row r="233" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN233" s="9"/>
     </row>
-    <row r="234" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN234" s="9"/>
     </row>
-    <row r="235" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN235" s="9"/>
     </row>
-    <row r="236" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN236" s="9"/>
     </row>
-    <row r="237" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN237" s="9"/>
     </row>
-    <row r="238" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN238" s="9"/>
     </row>
-    <row r="239" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN239" s="9"/>
     </row>
-    <row r="240" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN240" s="9"/>
     </row>
     <row r="241" spans="40:40" x14ac:dyDescent="0.25">
@@ -71356,9 +72066,6 @@
     <row r="328" spans="40:40" x14ac:dyDescent="0.25">
       <c r="AN328" s="9"/>
     </row>
-    <row r="329" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN329" s="9"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="N1:N1048576">
@@ -71372,7 +72079,7 @@
       <formula>"INICIO TARDÍO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R1048572">
+  <conditionalFormatting sqref="R1:R1048571">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"TERMINÓ DESPUÉS"</formula>
     </cfRule>

--- a/BASE_RECORRIDOS_PRO_JCA.xlsx
+++ b/BASE_RECORRIDOS_PRO_JCA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\INTERVENTORIA VELNEC\Recorridos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F6031B-1325-442A-9C49-23403B488E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B38211-433F-4341-93F3-4A430725F856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="24240" windowHeight="13020" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,8 +30,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId8"/>
-    <pivotCache cacheId="1" r:id="rId9"/>
+    <pivotCache cacheId="2" r:id="rId8"/>
+    <pivotCache cacheId="3" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5243" uniqueCount="1946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5433" uniqueCount="2028">
   <si>
     <t>ID</t>
   </si>
@@ -5888,6 +5888,252 @@
   </si>
   <si>
     <t>Inicio GPS anterior al horario: 00:58:45 antes de las 18:00.; Fin GPS dentro de la tolerancia del horario programado.; 3 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>27bf9ccc57f408d3</t>
+  </si>
+  <si>
+    <t>23_09_2026_AO_Diur.gpx</t>
+  </si>
+  <si>
+    <t>27bf9ccc57f408d3a1e58989de7178cb85dd167049fa727b70aa3a0879a845cb</t>
+  </si>
+  <si>
+    <t>23/09/2026</t>
+  </si>
+  <si>
+    <t>23/09/2026 09:17:02</t>
+  </si>
+  <si>
+    <t>23/09/2026 17:09:42</t>
+  </si>
+  <si>
+    <t>Inicio GPS tardío: 00:47:03 después de las 08:30.; Fin GPS posterior: 00:39:43 después de las 16:30.; 4 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.203335, -75.600755</t>
+  </si>
+  <si>
+    <t>6.233316, -75.603455</t>
+  </si>
+  <si>
+    <t>7a91edd00a841142</t>
+  </si>
+  <si>
+    <t>23_09_2026_AR_Diur.gpx</t>
+  </si>
+  <si>
+    <t>7a91edd00a8411422c22e48ab6aa40db972723a3e6f81e1d911b47c901f33c40</t>
+  </si>
+  <si>
+    <t>23/09/2026 08:16:16</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:11:11</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS anticipado: 00:18:49 antes de las 16:30.; 2 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.225747, -75.599410</t>
+  </si>
+  <si>
+    <t>6.255957, -75.616418</t>
+  </si>
+  <si>
+    <t>4408ac1d649faca3</t>
+  </si>
+  <si>
+    <t>23_09_2026_DR_Diur.gpx</t>
+  </si>
+  <si>
+    <t>4408ac1d649faca302b1a8ecf19b979de608bcd9adef35bce34292cd26b3aeb6</t>
+  </si>
+  <si>
+    <t>23/09/2026 08:51:52</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:41:32</t>
+  </si>
+  <si>
+    <t>Inicio GPS tardío: 00:21:52 después de las 08:30.; Fin GPS dentro de la tolerancia del horario programado.; 3 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.232912, -75.602197</t>
+  </si>
+  <si>
+    <t>6.250884, -75.621311</t>
+  </si>
+  <si>
+    <t>cee7dbc94d8380b9</t>
+  </si>
+  <si>
+    <t>23_09_2026_HC_Diur.gpx</t>
+  </si>
+  <si>
+    <t>cee7dbc94d8380b967c51fa1a926584f6f8387e40221a1c8e56431369faf5ba9</t>
+  </si>
+  <si>
+    <t>23/09/2026 08:20:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:17:50</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS anticipado: 02:12:10 antes de las 16:30.</t>
+  </si>
+  <si>
+    <t>6.225662, -75.599078</t>
+  </si>
+  <si>
+    <t>6.271636, -75.597142</t>
+  </si>
+  <si>
+    <t>abbfd962adecc6f9</t>
+  </si>
+  <si>
+    <t>23_09_2026_JA_Diur1.gpx</t>
+  </si>
+  <si>
+    <t>abbfd962adecc6f91b4e71bf28b254f741a22c8e9aedc308cb409194fbd1ad5b</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:26:53</t>
+  </si>
+  <si>
+    <t>23/09/2026 17:31:38</t>
+  </si>
+  <si>
+    <t>PARTE DE RECORRIDO</t>
+  </si>
+  <si>
+    <t>dba3452836ba7e50</t>
+  </si>
+  <si>
+    <t>23_09_2026_JA_Diur2.gpx</t>
+  </si>
+  <si>
+    <t>dba3452836ba7e50cc3f660a7059238423e73768e6e6d9c1ebe7ef47a5a38bab</t>
+  </si>
+  <si>
+    <t>23/09/2026 08:50:57</t>
+  </si>
+  <si>
+    <t>23/09/2026 12:14:38</t>
+  </si>
+  <si>
+    <t>025a647a490108ab</t>
+  </si>
+  <si>
+    <t>23_09_2026_JO_Diur.gpx</t>
+  </si>
+  <si>
+    <t>025a647a490108ab58e8e211691c0f25058cad25387522be9e59a593723a511c</t>
+  </si>
+  <si>
+    <t>23/09/2026 08:45:49</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:45:11</t>
+  </si>
+  <si>
+    <t>Inicio GPS tardío: 00:15:49 después de las 08:30.; Fin GPS posterior: 00:15:11 después de las 16:30.; 10 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.225619, -75.599349</t>
+  </si>
+  <si>
+    <t>6.246063, -75.561330</t>
+  </si>
+  <si>
+    <t>902a3fd7e70712ae</t>
+  </si>
+  <si>
+    <t>23_09_2026_JZ_Diur.gpx</t>
+  </si>
+  <si>
+    <t>902a3fd7e70712aeca6629d519f06105047cecdd8a4069792258d07bdd369e43</t>
+  </si>
+  <si>
+    <t>23/09/2026 08:04:28</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:34:36</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 00:25:32 antes de las 08:30.; Fin GPS dentro de la tolerancia del horario programado.; 3 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.226573, -75.599305</t>
+  </si>
+  <si>
+    <t>6.279455, -75.570395</t>
+  </si>
+  <si>
+    <t>a87b9c61f88f6dc6</t>
+  </si>
+  <si>
+    <t>23_09_2026_SJ_Diur.gpx</t>
+  </si>
+  <si>
+    <t>a87b9c61f88f6dc61d7c57e704a7019cfeeb155863211b6fcd05b1a5345a41e2</t>
+  </si>
+  <si>
+    <t>23/09/2026 08:39:04</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:04:43</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS anticipado: 00:25:17 antes de las 16:30.; 1 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.225663, -75.599389</t>
+  </si>
+  <si>
+    <t>6.308000, -75.581952</t>
+  </si>
+  <si>
+    <t>562b967a6b961354</t>
+  </si>
+  <si>
+    <t>23_09_2026_YL_Diur.gpx</t>
+  </si>
+  <si>
+    <t>562b967a6b961354db78b9cffe2da313776b367f0271c4f71ff1efefdac672ff</t>
+  </si>
+  <si>
+    <t>23/09/2026 08:49:21</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:45:00</t>
+  </si>
+  <si>
+    <t>Inicio GPS tardío: 00:19:21 después de las 08:30.; Fin GPS dentro de la tolerancia del horario programado.</t>
+  </si>
+  <si>
+    <t>6.225580, -75.599298</t>
+  </si>
+  <si>
+    <t>6.258559, -75.616272</t>
+  </si>
+  <si>
+    <t>Recorrido fragmentado 2 parte(s): INICIO DE RECORRIDO. Inicio operativo 08:50:57 y fin operativo 17:31:38.; Inicio GPS tardío: 00:20:57 después de las 08:30.</t>
+  </si>
+  <si>
+    <t>6.225734, -75.599447</t>
+  </si>
+  <si>
+    <t>6.235813, -75.555079</t>
+  </si>
+  <si>
+    <t>Recorrido fragmentado 2 parte(s): FIN DE RECORRIDO. Inicio operativo 08:50:57 y fin operativo 17:31:38.; Fin GPS posterior: 01:01:38 después de las 16:30.</t>
+  </si>
+  <si>
+    <t>6.236402, -75.560054</t>
+  </si>
+  <si>
+    <t>6.237026, -75.558757</t>
   </si>
 </sst>
 </file>
@@ -5965,6 +6211,7 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -24579,7 +24826,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="USER" refreshedDate="46283.800954629631" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="192" xr:uid="{FDEF9B37-15CF-42E8-BC5E-E1CE4649CF2B}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:AM552" sheet="RECORRIDOS"/>
+    <worksheetSource ref="A1:AM550" sheet="RECORRIDOS"/>
   </cacheSource>
   <cacheFields count="43">
     <cacheField name="ID" numFmtId="0">
@@ -25399,7 +25646,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="USER" refreshedDate="46283.800954861108" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="192" xr:uid="{4743F9B8-9139-4DCD-A807-2514F242574C}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:AF1048571" sheet="RECORRIDOS"/>
+    <worksheetSource ref="A1:AF1048569" sheet="RECORRIDOS"/>
   </cacheSource>
   <cacheFields count="32">
     <cacheField name="ID" numFmtId="0">
@@ -39971,7 +40218,268 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D330A9A-54B8-43DD-8D11-CC5633B99CDA}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0966AFF-8B15-4A0E-BE48-1F64EB76CB37}" name="TablaDinámica7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="57">
+  <location ref="AI107:AJ122" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="13"/>
+        <item h="1" x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Turno" fld="8" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="15">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="48" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="53" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="56" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D330A9A-54B8-43DD-8D11-CC5633B99CDA}" name="TablaDinámica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A6:E22" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
     <pivotField showAll="0"/>
@@ -40258,295 +40766,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
-  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item h="1" m="1" x="4"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="13"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="10">
-    <format dxfId="15">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="14">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="13">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="12">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="11">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="10">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="9">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="8">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="7">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="6">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="34" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
   <location ref="A107:D123" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
     <pivotField showAll="0"/>
@@ -40799,7 +41020,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{238AB259-E577-48AC-B3A0-09F752F5685D}" name="TablaDinámica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{238AB259-E577-48AC-B3A0-09F752F5685D}" name="TablaDinámica6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A169:B185" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="43">
     <pivotField showAll="0"/>
@@ -41625,7 +41846,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B44BF58-179E-4C57-BD89-E6E3367D37B9}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B44BF58-179E-4C57-BD89-E6E3367D37B9}" name="TablaDinámica4" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
   <location ref="K107:M122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
     <pivotField showAll="0"/>
@@ -41926,7 +42147,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E67C1C-2F15-4D2B-A97A-A1B46B6F5B69}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E67C1C-2F15-4D2B-A97A-A1B46B6F5B69}" name="TablaDinámica2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
   <location ref="A57:E73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
     <pivotField showAll="0"/>
@@ -42202,8 +42423,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0966AFF-8B15-4A0E-BE48-1F64EB76CB37}" name="TablaDinámica7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="57">
-  <location ref="AI107:AJ122" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
+  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -42223,10 +42444,10 @@
         <item x="8"/>
         <item x="9"/>
         <item x="10"/>
-        <item h="1" x="11"/>
-        <item h="1" x="12"/>
-        <item h="1" x="13"/>
-        <item h="1" x="14"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -42259,12 +42480,21 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" m="1" x="4"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -42287,7 +42517,7 @@
   <rowFields count="1">
     <field x="6"/>
   </rowFields>
-  <rowItems count="15">
+  <rowItems count="14">
     <i>
       <x/>
     </i>
@@ -42325,24 +42555,29 @@
       <x v="11"/>
     </i>
     <i>
-      <x v="12"/>
-    </i>
-    <i>
       <x v="13"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colItems count="1">
-    <i/>
+  <colFields count="1">
+    <field x="13"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
   </colItems>
   <pageFields count="2">
     <pageField fld="3" hier="-1"/>
     <pageField fld="4" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Cuenta de Turno" fld="8" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="10">
     <format dxfId="38">
@@ -42413,38 +42648,50 @@
     </format>
   </formats>
   <chartFormats count="4">
-    <chartFormat chart="48" format="8" series="1">
+    <chartFormat chart="34" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
+        <references count="2">
           <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="39" format="8" series="1">
+    <chartFormat chart="34" format="1" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
+        <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="53" format="0" series="1">
+    <chartFormat chart="34" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
+        <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="56" format="2" series="1">
+    <chartFormat chart="34" format="3" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
+        <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="3"/>
           </reference>
         </references>
       </pivotArea>
@@ -42463,8 +42710,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{07721E28-36B5-4676-BFC5-097A3B63190A}" name="Tabla1" displayName="Tabla1" ref="A1:AF1048571" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71">
-  <autoFilter ref="A1:AF1048571" xr:uid="{07721E28-36B5-4676-BFC5-097A3B63190A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{07721E28-36B5-4676-BFC5-097A3B63190A}" name="Tabla1" displayName="Tabla1" ref="A1:AF1048569" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71">
+  <autoFilter ref="A1:AF1048569" xr:uid="{07721E28-36B5-4676-BFC5-097A3B63190A}"/>
   <tableColumns count="32">
     <tableColumn id="1" xr3:uid="{BFACFB74-E6A6-4648-B0DA-7D6E1FC88A79}" name="ID" dataDxfId="70"/>
     <tableColumn id="2" xr3:uid="{B67B24E0-3585-47FC-A130-8F37C8640BC4}" name="Archivo" dataDxfId="69"/>
@@ -44302,7 +44549,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BB328"/>
+  <dimension ref="A1:BB326"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" style="9" customWidth="1"/>
@@ -44316,7 +44563,9 @@
     <col min="10" max="10" width="15.140625" style="9" customWidth="1"/>
     <col min="11" max="11" width="24.85546875" style="9" customWidth="1"/>
     <col min="12" max="12" width="21.5703125" style="9" customWidth="1"/>
-    <col min="13" max="32" width="24.85546875" style="9" customWidth="1"/>
+    <col min="13" max="16" width="24.85546875" style="9" customWidth="1"/>
+    <col min="17" max="17" width="24.85546875" style="10" customWidth="1"/>
+    <col min="18" max="32" width="24.85546875" style="9" customWidth="1"/>
     <col min="33" max="34" width="24.85546875" style="14" customWidth="1"/>
     <col min="35" max="37" width="24.85546875" style="9" customWidth="1"/>
     <col min="38" max="38" width="24.85546875" style="19" customWidth="1"/>
@@ -68004,7 +68253,7 @@
         <v>-75.546586000000005</v>
       </c>
       <c r="AM195" s="26">
-        <f t="shared" ref="AM195:AM226" si="3">IF(N195="INICIO TARDÍO",M195,0)+IF(R195="TERMINÓ ANTES",Q195,0)</f>
+        <f t="shared" ref="AM195:AM236" si="3">IF(N195="INICIO TARDÍO",M195,0)+IF(R195="TERMINÓ ANTES",Q195,0)</f>
         <v>0</v>
       </c>
       <c r="AN195" s="9"/>
@@ -71760,34 +72009,1209 @@
       </c>
       <c r="AN226" s="9"/>
     </row>
-    <row r="227" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A227" s="9" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B227" s="9" t="s">
+        <v>1947</v>
+      </c>
+      <c r="C227" s="9" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D227" s="9" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E227" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F227" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G227" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H227" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I227" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J227" s="9">
+        <v>5959</v>
+      </c>
+      <c r="K227" s="9" t="s">
+        <v>1950</v>
+      </c>
+      <c r="L227" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M227" s="10">
+        <v>3.2673252314814813E-2</v>
+      </c>
+      <c r="N227" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O227" s="9" t="s">
+        <v>1951</v>
+      </c>
+      <c r="P227" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q227" s="10">
+        <v>2.7579675925925931E-2</v>
+      </c>
+      <c r="R227" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="S227" s="10">
+        <v>0.32823975694444452</v>
+      </c>
+      <c r="T227" s="9">
+        <v>33.295999999999999</v>
+      </c>
+      <c r="U227" s="9">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="V227" s="10">
+        <v>0.14539078703703681</v>
+      </c>
+      <c r="W227" s="10">
+        <v>0.1105644560185185</v>
+      </c>
+      <c r="X227" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y227" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z227" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA227" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB227" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC227" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD227" s="9">
+        <v>4</v>
+      </c>
+      <c r="AE227" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF227" s="9" t="s">
+        <v>1952</v>
+      </c>
+      <c r="AG227" s="9" t="s">
+        <v>1953</v>
+      </c>
+      <c r="AH227" s="9">
+        <v>6.203335</v>
+      </c>
+      <c r="AI227" s="9">
+        <v>-75.600755000000007</v>
+      </c>
+      <c r="AJ227" s="9" t="s">
+        <v>1954</v>
+      </c>
+      <c r="AK227" s="9">
+        <v>6.2333160000000003</v>
+      </c>
+      <c r="AL227" s="9">
+        <v>-75.603454999999997</v>
+      </c>
+      <c r="AM227" s="26">
+        <f t="shared" si="3"/>
+        <v>3.2673252314814813E-2</v>
+      </c>
       <c r="AN227" s="9"/>
     </row>
-    <row r="228" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A228" s="9" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B228" s="9" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C228" s="9" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D228" s="9" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E228" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F228" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G228" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H228" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I228" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J228" s="9">
+        <v>1868</v>
+      </c>
+      <c r="K228" s="9" t="s">
+        <v>1958</v>
+      </c>
+      <c r="L228" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M228" s="10">
+        <v>9.5370370370370366E-3</v>
+      </c>
+      <c r="N228" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O228" s="9" t="s">
+        <v>1959</v>
+      </c>
+      <c r="P228" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q228" s="10">
+        <v>1.306712962962963E-2</v>
+      </c>
+      <c r="R228" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S228" s="10">
+        <v>0.32980324074074069</v>
+      </c>
+      <c r="T228" s="9">
+        <v>22.170999999999999</v>
+      </c>
+      <c r="U228" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="V228" s="10">
+        <v>0.205162037037037</v>
+      </c>
+      <c r="W228" s="10">
+        <v>0.1571990740740741</v>
+      </c>
+      <c r="X228" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y228" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z228" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA228" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB228" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC228" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD228" s="9">
+        <v>2</v>
+      </c>
+      <c r="AE228" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF228" s="9" t="s">
+        <v>1960</v>
+      </c>
+      <c r="AG228" s="9" t="s">
+        <v>1961</v>
+      </c>
+      <c r="AH228" s="9">
+        <v>6.2257470000000001</v>
+      </c>
+      <c r="AI228" s="9">
+        <v>-75.599410000000006</v>
+      </c>
+      <c r="AJ228" s="9" t="s">
+        <v>1962</v>
+      </c>
+      <c r="AK228" s="9">
+        <v>6.2559570000000004</v>
+      </c>
+      <c r="AL228" s="9">
+        <v>-75.616417999999996</v>
+      </c>
+      <c r="AM228" s="26">
+        <f t="shared" si="3"/>
+        <v>1.306712962962963E-2</v>
+      </c>
       <c r="AN228" s="9"/>
     </row>
-    <row r="229" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A229" s="9" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B229" s="9" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C229" s="9" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D229" s="9" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E229" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F229" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G229" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="H229" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I229" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J229" s="9">
+        <v>2244</v>
+      </c>
+      <c r="K229" s="9" t="s">
+        <v>1966</v>
+      </c>
+      <c r="L229" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M229" s="10">
+        <v>1.518518518518519E-2</v>
+      </c>
+      <c r="N229" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O229" s="9" t="s">
+        <v>1967</v>
+      </c>
+      <c r="P229" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q229" s="10">
+        <v>8.0092592592592594E-3</v>
+      </c>
+      <c r="R229" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S229" s="10">
+        <v>0.3261574074074074</v>
+      </c>
+      <c r="T229" s="9">
+        <v>27.957000000000001</v>
+      </c>
+      <c r="U229" s="9">
+        <v>5.12</v>
+      </c>
+      <c r="V229" s="10">
+        <v>0.22765046296296301</v>
+      </c>
+      <c r="W229" s="10">
+        <v>0.17216435185185189</v>
+      </c>
+      <c r="X229" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y229" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z229" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA229" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB229" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC229" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD229" s="9">
+        <v>3</v>
+      </c>
+      <c r="AE229" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF229" s="9" t="s">
+        <v>1968</v>
+      </c>
+      <c r="AG229" s="9" t="s">
+        <v>1969</v>
+      </c>
+      <c r="AH229" s="9">
+        <v>6.2329119999999998</v>
+      </c>
+      <c r="AI229" s="9">
+        <v>-75.602197000000004</v>
+      </c>
+      <c r="AJ229" s="9" t="s">
+        <v>1970</v>
+      </c>
+      <c r="AK229" s="9">
+        <v>6.2508840000000001</v>
+      </c>
+      <c r="AL229" s="9">
+        <v>-75.621311000000006</v>
+      </c>
+      <c r="AM229" s="26">
+        <f t="shared" si="3"/>
+        <v>1.518518518518519E-2</v>
+      </c>
       <c r="AN229" s="9"/>
     </row>
-    <row r="230" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A230" s="9" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B230" s="9" t="s">
+        <v>1972</v>
+      </c>
+      <c r="C230" s="9" t="s">
+        <v>1973</v>
+      </c>
+      <c r="D230" s="9" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E230" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F230" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G230" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H230" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I230" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J230" s="9">
+        <v>4411</v>
+      </c>
+      <c r="K230" s="9" t="s">
+        <v>1974</v>
+      </c>
+      <c r="L230" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M230" s="10">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="N230" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O230" s="9" t="s">
+        <v>1975</v>
+      </c>
+      <c r="P230" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q230" s="10">
+        <v>9.178240740740741E-2</v>
+      </c>
+      <c r="R230" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S230" s="10">
+        <v>0.24849537037037039</v>
+      </c>
+      <c r="T230" s="9">
+        <v>57.37</v>
+      </c>
+      <c r="U230" s="9">
+        <v>13.72</v>
+      </c>
+      <c r="V230" s="10">
+        <v>0.17427083333333329</v>
+      </c>
+      <c r="W230" s="10">
+        <v>6.6747685185185188E-2</v>
+      </c>
+      <c r="X230" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y230" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z230" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA230" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB230" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC230" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD230" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE230" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF230" s="9" t="s">
+        <v>1976</v>
+      </c>
+      <c r="AG230" s="9" t="s">
+        <v>1977</v>
+      </c>
+      <c r="AH230" s="9">
+        <v>6.2256619999999998</v>
+      </c>
+      <c r="AI230" s="9">
+        <v>-75.599078000000006</v>
+      </c>
+      <c r="AJ230" s="9" t="s">
+        <v>1978</v>
+      </c>
+      <c r="AK230" s="9">
+        <v>6.271636</v>
+      </c>
+      <c r="AL230" s="9">
+        <v>-75.597142000000005</v>
+      </c>
+      <c r="AM230" s="26">
+        <f t="shared" si="3"/>
+        <v>9.178240740740741E-2</v>
+      </c>
       <c r="AN230" s="9"/>
     </row>
-    <row r="231" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A231" s="9" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B231" s="9" t="s">
+        <v>1991</v>
+      </c>
+      <c r="C231" s="9" t="s">
+        <v>1992</v>
+      </c>
+      <c r="D231" s="9" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E231" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F231" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G231" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H231" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I231" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J231" s="9">
+        <v>5246</v>
+      </c>
+      <c r="K231" s="9" t="s">
+        <v>1993</v>
+      </c>
+      <c r="L231" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M231" s="10">
+        <v>1.0986909722222221E-2</v>
+      </c>
+      <c r="N231" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O231" s="9" t="s">
+        <v>1994</v>
+      </c>
+      <c r="P231" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q231" s="10">
+        <v>1.054550925925926E-2</v>
+      </c>
+      <c r="R231" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="S231" s="10">
+        <v>0.33289193287037039</v>
+      </c>
+      <c r="T231" s="9">
+        <v>27.216000000000001</v>
+      </c>
+      <c r="U231" s="9">
+        <v>33.270000000000003</v>
+      </c>
+      <c r="V231" s="10">
+        <v>3.4082523148148157E-2</v>
+      </c>
+      <c r="W231" s="10">
+        <v>1.6476238425925931E-2</v>
+      </c>
+      <c r="X231" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y231" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z231" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA231" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB231" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC231" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD231" s="9">
+        <v>10</v>
+      </c>
+      <c r="AE231" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF231" s="9" t="s">
+        <v>1995</v>
+      </c>
+      <c r="AG231" s="9" t="s">
+        <v>1996</v>
+      </c>
+      <c r="AH231" s="9">
+        <v>6.225619</v>
+      </c>
+      <c r="AI231" s="9">
+        <v>-75.599349000000004</v>
+      </c>
+      <c r="AJ231" s="9" t="s">
+        <v>1997</v>
+      </c>
+      <c r="AK231" s="9">
+        <v>6.2460630000000004</v>
+      </c>
+      <c r="AL231" s="9">
+        <v>-75.561329999999998</v>
+      </c>
+      <c r="AM231" s="26">
+        <f t="shared" si="3"/>
+        <v>1.0986909722222221E-2</v>
+      </c>
       <c r="AN231" s="9"/>
     </row>
-    <row r="232" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A232" s="9" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B232" s="9" t="s">
+        <v>1999</v>
+      </c>
+      <c r="C232" s="9" t="s">
+        <v>2000</v>
+      </c>
+      <c r="D232" s="9" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E232" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F232" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G232" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H232" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I232" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J232" s="9">
+        <v>5580</v>
+      </c>
+      <c r="K232" s="9" t="s">
+        <v>2001</v>
+      </c>
+      <c r="L232" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M232" s="10">
+        <v>1.773148148148148E-2</v>
+      </c>
+      <c r="N232" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O232" s="9" t="s">
+        <v>2002</v>
+      </c>
+      <c r="P232" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q232" s="10">
+        <v>3.1944444444444451E-3</v>
+      </c>
+      <c r="R232" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S232" s="10">
+        <v>0.35425925925925927</v>
+      </c>
+      <c r="T232" s="9">
+        <v>75.423000000000002</v>
+      </c>
+      <c r="U232" s="9">
+        <v>10.25</v>
+      </c>
+      <c r="V232" s="10">
+        <v>0.30664351851851851</v>
+      </c>
+      <c r="W232" s="10">
+        <v>0.1716435185185185</v>
+      </c>
+      <c r="X232" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y232" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z232" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA232" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB232" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC232" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD232" s="9">
+        <v>3</v>
+      </c>
+      <c r="AE232" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF232" s="9" t="s">
+        <v>2003</v>
+      </c>
+      <c r="AG232" s="9" t="s">
+        <v>2004</v>
+      </c>
+      <c r="AH232" s="9">
+        <v>6.2265730000000001</v>
+      </c>
+      <c r="AI232" s="9">
+        <v>-75.599305000000001</v>
+      </c>
+      <c r="AJ232" s="9" t="s">
+        <v>2005</v>
+      </c>
+      <c r="AK232" s="9">
+        <v>6.2794549999999996</v>
+      </c>
+      <c r="AL232" s="9">
+        <v>-75.570395000000005</v>
+      </c>
+      <c r="AM232" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN232" s="9"/>
     </row>
-    <row r="233" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A233" s="9" t="s">
+        <v>2006</v>
+      </c>
+      <c r="B233" s="9" t="s">
+        <v>2007</v>
+      </c>
+      <c r="C233" s="9" t="s">
+        <v>2008</v>
+      </c>
+      <c r="D233" s="9" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E233" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F233" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G233" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H233" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="I233" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J233" s="9">
+        <v>2385</v>
+      </c>
+      <c r="K233" s="9" t="s">
+        <v>2009</v>
+      </c>
+      <c r="L233" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M233" s="10">
+        <v>6.2962962962962964E-3</v>
+      </c>
+      <c r="N233" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O233" s="9" t="s">
+        <v>2010</v>
+      </c>
+      <c r="P233" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q233" s="10">
+        <v>1.755787037037037E-2</v>
+      </c>
+      <c r="R233" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S233" s="10">
+        <v>0.30947916666666669</v>
+      </c>
+      <c r="T233" s="9">
+        <v>30.879000000000001</v>
+      </c>
+      <c r="U233" s="9">
+        <v>7.36</v>
+      </c>
+      <c r="V233" s="10">
+        <v>0.17486111111111111</v>
+      </c>
+      <c r="W233" s="10">
+        <v>0.12642361111111111</v>
+      </c>
+      <c r="X233" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y233" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z233" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA233" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB233" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC233" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD233" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE233" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF233" s="9" t="s">
+        <v>2011</v>
+      </c>
+      <c r="AG233" s="9" t="s">
+        <v>2012</v>
+      </c>
+      <c r="AH233" s="9">
+        <v>6.2256629999999999</v>
+      </c>
+      <c r="AI233" s="9">
+        <v>-75.599389000000002</v>
+      </c>
+      <c r="AJ233" s="9" t="s">
+        <v>2013</v>
+      </c>
+      <c r="AK233" s="9">
+        <v>6.3079999999999998</v>
+      </c>
+      <c r="AL233" s="9">
+        <v>-75.581952000000001</v>
+      </c>
+      <c r="AM233" s="26">
+        <f t="shared" si="3"/>
+        <v>1.755787037037037E-2</v>
+      </c>
       <c r="AN233" s="9"/>
     </row>
-    <row r="234" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A234" s="9" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B234" s="9" t="s">
+        <v>2015</v>
+      </c>
+      <c r="C234" s="9" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D234" s="9" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E234" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F234" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G234" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H234" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I234" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J234" s="9">
+        <v>4294</v>
+      </c>
+      <c r="K234" s="9" t="s">
+        <v>2017</v>
+      </c>
+      <c r="L234" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M234" s="10">
+        <v>1.34375E-2</v>
+      </c>
+      <c r="N234" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O234" s="9" t="s">
+        <v>2018</v>
+      </c>
+      <c r="P234" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q234" s="10">
+        <v>1.041666666666667E-2</v>
+      </c>
+      <c r="R234" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S234" s="10">
+        <v>0.33031250000000001</v>
+      </c>
+      <c r="T234" s="9">
+        <v>57.81</v>
+      </c>
+      <c r="U234" s="9">
+        <v>13.04</v>
+      </c>
+      <c r="V234" s="10">
+        <v>0.18466435185185179</v>
+      </c>
+      <c r="W234" s="10">
+        <v>0.1046643518518519</v>
+      </c>
+      <c r="X234" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y234" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z234" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA234" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB234" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC234" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD234" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE234" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF234" s="9" t="s">
+        <v>2019</v>
+      </c>
+      <c r="AG234" s="9" t="s">
+        <v>2020</v>
+      </c>
+      <c r="AH234" s="9">
+        <v>6.2255799999999999</v>
+      </c>
+      <c r="AI234" s="9">
+        <v>-75.599298000000005</v>
+      </c>
+      <c r="AJ234" s="9" t="s">
+        <v>2021</v>
+      </c>
+      <c r="AK234" s="9">
+        <v>6.258559</v>
+      </c>
+      <c r="AL234" s="9">
+        <v>-75.616271999999995</v>
+      </c>
+      <c r="AM234" s="26">
+        <f t="shared" si="3"/>
+        <v>1.34375E-2</v>
+      </c>
       <c r="AN234" s="9"/>
     </row>
-    <row r="235" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A235" s="9" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B235" s="9" t="s">
+        <v>1980</v>
+      </c>
+      <c r="C235" s="9" t="s">
+        <v>1987</v>
+      </c>
+      <c r="D235" s="9" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E235" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F235" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G235" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H235" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I235" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J235" s="9">
+        <v>1382</v>
+      </c>
+      <c r="K235" s="9" t="s">
+        <v>1988</v>
+      </c>
+      <c r="L235" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M235" s="10">
+        <v>1.4548611111111109E-2</v>
+      </c>
+      <c r="N235" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O235" s="9" t="s">
+        <v>1989</v>
+      </c>
+      <c r="P235" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q235" s="9"/>
+      <c r="R235" s="9" t="s">
+        <v>1984</v>
+      </c>
+      <c r="S235" s="10">
+        <v>0.36158564814814809</v>
+      </c>
+      <c r="T235" s="9">
+        <v>17.55</v>
+      </c>
+      <c r="U235" s="9">
+        <v>7.15</v>
+      </c>
+      <c r="V235" s="10">
+        <v>0.10223379629629629</v>
+      </c>
+      <c r="W235" s="10">
+        <v>7.1469907407407413E-2</v>
+      </c>
+      <c r="X235" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y235" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z235" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA235" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB235" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC235" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD235" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE235" s="9" t="s">
+        <v>1984</v>
+      </c>
+      <c r="AF235" s="9" t="s">
+        <v>2022</v>
+      </c>
+      <c r="AG235" s="9" t="s">
+        <v>2023</v>
+      </c>
+      <c r="AH235" s="9">
+        <v>6.2257340000000001</v>
+      </c>
+      <c r="AI235" s="9">
+        <v>-75.599446999999998</v>
+      </c>
+      <c r="AJ235" s="9" t="s">
+        <v>2024</v>
+      </c>
+      <c r="AK235" s="9">
+        <v>6.2358130000000003</v>
+      </c>
+      <c r="AL235" s="9">
+        <v>-75.555079000000006</v>
+      </c>
+      <c r="AM235" s="26">
+        <f t="shared" si="3"/>
+        <v>1.4548611111111109E-2</v>
+      </c>
       <c r="AN235" s="9"/>
     </row>
-    <row r="236" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A236" s="9" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B236" s="9" t="s">
+        <v>1986</v>
+      </c>
+      <c r="C236" s="9" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D236" s="9" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E236" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F236" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G236" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H236" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I236" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J236" s="9">
+        <v>336</v>
+      </c>
+      <c r="K236" s="9" t="s">
+        <v>1982</v>
+      </c>
+      <c r="L236" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="N236" s="9" t="s">
+        <v>1984</v>
+      </c>
+      <c r="O236" s="9" t="s">
+        <v>1983</v>
+      </c>
+      <c r="P236" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q236" s="10">
+        <v>4.2800925925925923E-2</v>
+      </c>
+      <c r="R236" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="S236" s="10">
+        <v>0.36158564814814809</v>
+      </c>
+      <c r="T236" s="9">
+        <v>3.5720000000000001</v>
+      </c>
+      <c r="U236" s="9">
+        <v>3.31</v>
+      </c>
+      <c r="V236" s="10">
+        <v>4.4965277777777778E-2</v>
+      </c>
+      <c r="W236" s="10">
+        <v>3.7164351851851851E-2</v>
+      </c>
+      <c r="X236" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y236" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z236" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA236" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB236" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC236" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD236" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE236" s="9" t="s">
+        <v>1984</v>
+      </c>
+      <c r="AF236" s="9" t="s">
+        <v>2025</v>
+      </c>
+      <c r="AG236" s="9" t="s">
+        <v>2026</v>
+      </c>
+      <c r="AH236" s="9">
+        <v>6.236402</v>
+      </c>
+      <c r="AI236" s="9">
+        <v>-75.560053999999994</v>
+      </c>
+      <c r="AJ236" s="9" t="s">
+        <v>2027</v>
+      </c>
+      <c r="AK236" s="9">
+        <v>6.2370260000000002</v>
+      </c>
+      <c r="AL236" s="9">
+        <v>-75.558757</v>
+      </c>
+      <c r="AM236" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN236" s="9"/>
     </row>
     <row r="237" spans="1:40" x14ac:dyDescent="0.25">
@@ -72060,12 +73484,6 @@
     <row r="326" spans="40:40" x14ac:dyDescent="0.25">
       <c r="AN326" s="9"/>
     </row>
-    <row r="327" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN327" s="9"/>
-    </row>
-    <row r="328" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN328" s="9"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="N1:N1048576">
@@ -72079,7 +73497,7 @@
       <formula>"INICIO TARDÍO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R1048571">
+  <conditionalFormatting sqref="R1:R1048569">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"TERMINÓ DESPUÉS"</formula>
     </cfRule>

--- a/BASE_RECORRIDOS_PRO_JCA.xlsx
+++ b/BASE_RECORRIDOS_PRO_JCA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\INTERVENTORIA VELNEC\Recorridos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B38211-433F-4341-93F3-4A430725F856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC09BD5-1AF5-44C9-910A-3593317AB8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="24240" windowHeight="13020" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,8 +30,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId8"/>
-    <pivotCache cacheId="3" r:id="rId9"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5433" uniqueCount="2028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5509" uniqueCount="2060">
   <si>
     <t>ID</t>
   </si>
@@ -6134,6 +6134,102 @@
   </si>
   <si>
     <t>6.237026, -75.558757</t>
+  </si>
+  <si>
+    <t>c7bcdda3448eca70</t>
+  </si>
+  <si>
+    <t>23_09_2026_DV_Noct.gpx</t>
+  </si>
+  <si>
+    <t>c7bcdda3448eca7014a76963f98c28a7628c901ad953ed367050d466f0da05ff</t>
+  </si>
+  <si>
+    <t>23/09/2026 17:50:48</t>
+  </si>
+  <si>
+    <t>24/09/2026 00:23:26</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS posterior: 00:23:26 después de las 00:00.</t>
+  </si>
+  <si>
+    <t>6.226789, -75.599344</t>
+  </si>
+  <si>
+    <t>6.272684, -75.602048</t>
+  </si>
+  <si>
+    <t>854b85750ca295ba</t>
+  </si>
+  <si>
+    <t>23_09_2026_IQ_Noct.gpx</t>
+  </si>
+  <si>
+    <t>854b85750ca295bab2dbaff996de56ef78092891b34f495b545a89ffb99f5af8</t>
+  </si>
+  <si>
+    <t>23/09/2026 17:35:20</t>
+  </si>
+  <si>
+    <t>23/09/2026 23:57:48</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 00:24:40 antes de las 18:00.; Fin GPS dentro de la tolerancia del horario programado.; 6 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.213995, -75.596642</t>
+  </si>
+  <si>
+    <t>6.270932, -75.554243</t>
+  </si>
+  <si>
+    <t>1524ebf6e64c53aa</t>
+  </si>
+  <si>
+    <t>23_09_2026_JP_Noct.gpx</t>
+  </si>
+  <si>
+    <t>1524ebf6e64c53aa5e6027a2d921e2541675d5de5bc7ab5d37d972940274a473</t>
+  </si>
+  <si>
+    <t>23/09/2026 17:30:41</t>
+  </si>
+  <si>
+    <t>23/09/2026 21:41:04</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 00:29:19 antes de las 18:00.; Fin GPS anticipado: 02:18:56 antes de las 00:00.</t>
+  </si>
+  <si>
+    <t>6.226977, -75.599622</t>
+  </si>
+  <si>
+    <t>6.251832, -75.551835</t>
+  </si>
+  <si>
+    <t>c28c6adae2a52086</t>
+  </si>
+  <si>
+    <t>23_09_2026_LA_Noct.gpx</t>
+  </si>
+  <si>
+    <t>c28c6adae2a52086a5b43f8adf2f7efb0ab6d21e943556b357652747d7f1966b</t>
+  </si>
+  <si>
+    <t>23/09/2026 17:41:21</t>
+  </si>
+  <si>
+    <t>24/09/2026 00:07:53</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 00:18:39 antes de las 18:00.; Fin GPS dentro de la tolerancia del horario programado.; 2 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.226768, -75.599312</t>
+  </si>
+  <si>
+    <t>6.268597, -75.599288</t>
   </si>
 </sst>
 </file>
@@ -6501,14 +6597,6 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
       <font>
         <sz val="14"/>
       </font>
@@ -6564,9 +6652,11 @@
       </font>
     </dxf>
     <dxf>
+      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
+    </dxf>
+    <dxf>
       <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
+        <sz val="14"/>
       </font>
     </dxf>
     <dxf>
@@ -6592,6 +6682,12 @@
     <dxf>
       <font>
         <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -40218,7 +40314,283 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0966AFF-8B15-4A0E-BE48-1F64EB76CB37}" name="TablaDinámica7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="57">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E67C1C-2F15-4D2B-A97A-A1B46B6F5B69}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
+  <location ref="A57:E73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item m="1" x="4"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="17"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="8">
+    <chartFormat chart="24" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="15" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="16" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="21" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="22" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="23" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="24" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0966AFF-8B15-4A0E-BE48-1F64EB76CB37}" name="TablaDinámica7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="57">
   <location ref="AI107:AJ122" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
     <pivotField showAll="0"/>
@@ -40478,8 +40850,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D330A9A-54B8-43DD-8D11-CC5633B99CDA}" name="TablaDinámica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D330A9A-54B8-43DD-8D11-CC5633B99CDA}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A6:E22" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
     <pivotField showAll="0"/>
@@ -40766,8 +41138,295 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
+  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" m="1" x="4"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="13"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="25">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="22">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="19">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="17">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="34" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
   <location ref="A107:D123" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
     <pivotField showAll="0"/>
@@ -41019,8 +41678,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{238AB259-E577-48AC-B3A0-09F752F5685D}" name="TablaDinámica6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{238AB259-E577-48AC-B3A0-09F752F5685D}" name="TablaDinámica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A169:B185" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="43">
     <pivotField showAll="0"/>
@@ -41818,7 +42477,7 @@
     <dataField name="Suma de Sumatoria de tiempo total sin recorrido" fld="38" baseField="6" baseItem="0" numFmtId="21"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="16">
+    <format dxfId="26">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -41845,8 +42504,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B44BF58-179E-4C57-BD89-E6E3367D37B9}" name="TablaDinámica4" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B44BF58-179E-4C57-BD89-E6E3367D37B9}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
   <location ref="K107:M122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
     <pivotField showAll="0"/>
@@ -42003,13 +42662,13 @@
     <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="28">
+    <format dxfId="38">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="37">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="13">
@@ -42030,26 +42689,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="35">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="33">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="32">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="31">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="13">
@@ -42070,17 +42729,17 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="28">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -42128,569 +42787,6 @@
             <x v="0"/>
           </reference>
           <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E67C1C-2F15-4D2B-A97A-A1B46B6F5B69}" name="TablaDinámica2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
-  <location ref="A57:E73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item m="1" x="4"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="17"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="8">
-    <chartFormat chart="24" format="13" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="14" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="15" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="16" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="21" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="22" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="23" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="24" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
-  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item h="1" m="1" x="4"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="13"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="10">
-    <format dxfId="38">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="37">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="36">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="35">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="34">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="33">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="32">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="31">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="30">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="29">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="34" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
             <x v="3"/>
           </reference>
         </references>
@@ -68253,7 +68349,7 @@
         <v>-75.546586000000005</v>
       </c>
       <c r="AM195" s="26">
-        <f t="shared" ref="AM195:AM236" si="3">IF(N195="INICIO TARDÍO",M195,0)+IF(R195="TERMINÓ ANTES",Q195,0)</f>
+        <f t="shared" ref="AM195:AM240" si="3">IF(N195="INICIO TARDÍO",M195,0)+IF(R195="TERMINÓ ANTES",Q195,0)</f>
         <v>0</v>
       </c>
       <c r="AN195" s="9"/>
@@ -73214,16 +73310,488 @@
       </c>
       <c r="AN236" s="9"/>
     </row>
-    <row r="237" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A237" s="9" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B237" s="9" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C237" s="9" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D237" s="9" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E237" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F237" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G237" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H237" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I237" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J237" s="9">
+        <v>5086</v>
+      </c>
+      <c r="K237" s="9" t="s">
+        <v>2031</v>
+      </c>
+      <c r="L237" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M237" s="10">
+        <v>6.3888888888888893E-3</v>
+      </c>
+      <c r="N237" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O237" s="9" t="s">
+        <v>2032</v>
+      </c>
+      <c r="P237" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q237" s="10">
+        <v>1.6273148148148151E-2</v>
+      </c>
+      <c r="R237" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="S237" s="10">
+        <v>0.27266203703703712</v>
+      </c>
+      <c r="T237" s="9">
+        <v>64.069000000000003</v>
+      </c>
+      <c r="U237" s="9">
+        <v>13.78</v>
+      </c>
+      <c r="V237" s="10">
+        <v>0.19375000000000001</v>
+      </c>
+      <c r="W237" s="10">
+        <v>4.5520833333333337E-2</v>
+      </c>
+      <c r="X237" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y237" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z237" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA237" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB237" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC237" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD237" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE237" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF237" s="9" t="s">
+        <v>2033</v>
+      </c>
+      <c r="AG237" s="9" t="s">
+        <v>2034</v>
+      </c>
+      <c r="AH237" s="9">
+        <v>6.2267890000000001</v>
+      </c>
+      <c r="AI237" s="9">
+        <v>-75.599344000000002</v>
+      </c>
+      <c r="AJ237" s="9" t="s">
+        <v>2035</v>
+      </c>
+      <c r="AK237" s="9">
+        <v>6.2726839999999999</v>
+      </c>
+      <c r="AL237" s="9">
+        <v>-75.602047999999996</v>
+      </c>
+      <c r="AM237" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN237" s="9"/>
     </row>
-    <row r="238" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A238" s="9" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B238" s="9" t="s">
+        <v>2037</v>
+      </c>
+      <c r="C238" s="9" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D238" s="9" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E238" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F238" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G238" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="H238" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="I238" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J238" s="9">
+        <v>2052</v>
+      </c>
+      <c r="K238" s="9" t="s">
+        <v>2039</v>
+      </c>
+      <c r="L238" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M238" s="10">
+        <v>1.712962962962963E-2</v>
+      </c>
+      <c r="N238" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O238" s="9" t="s">
+        <v>2040</v>
+      </c>
+      <c r="P238" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q238" s="10">
+        <v>1.5277777777777781E-3</v>
+      </c>
+      <c r="R238" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S238" s="10">
+        <v>0.26560185185185192</v>
+      </c>
+      <c r="T238" s="9">
+        <v>35.808999999999997</v>
+      </c>
+      <c r="U238" s="9">
+        <v>14.06</v>
+      </c>
+      <c r="V238" s="10">
+        <v>0.1061458333333333</v>
+      </c>
+      <c r="W238" s="10">
+        <v>6.5925925925925929E-2</v>
+      </c>
+      <c r="X238" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y238" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z238" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA238" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB238" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC238" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD238" s="9">
+        <v>6</v>
+      </c>
+      <c r="AE238" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF238" s="9" t="s">
+        <v>2041</v>
+      </c>
+      <c r="AG238" s="9" t="s">
+        <v>2042</v>
+      </c>
+      <c r="AH238" s="9">
+        <v>6.2139949999999997</v>
+      </c>
+      <c r="AI238" s="9">
+        <v>-75.596642000000003</v>
+      </c>
+      <c r="AJ238" s="9" t="s">
+        <v>2043</v>
+      </c>
+      <c r="AK238" s="9">
+        <v>6.2709320000000002</v>
+      </c>
+      <c r="AL238" s="9">
+        <v>-75.554243</v>
+      </c>
+      <c r="AM238" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN238" s="9"/>
     </row>
-    <row r="239" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A239" s="9" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B239" s="9" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C239" s="9" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D239" s="9" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E239" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F239" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G239" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H239" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="I239" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J239" s="9">
+        <v>3372</v>
+      </c>
+      <c r="K239" s="9" t="s">
+        <v>2047</v>
+      </c>
+      <c r="L239" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M239" s="10">
+        <v>2.0358796296296292E-2</v>
+      </c>
+      <c r="N239" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O239" s="9" t="s">
+        <v>2048</v>
+      </c>
+      <c r="P239" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q239" s="10">
+        <v>9.6481481481481488E-2</v>
+      </c>
+      <c r="R239" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S239" s="10">
+        <v>0.1738773148148148</v>
+      </c>
+      <c r="T239" s="9">
+        <v>46.061</v>
+      </c>
+      <c r="U239" s="9">
+        <v>13.42</v>
+      </c>
+      <c r="V239" s="10">
+        <v>0.14305555555555549</v>
+      </c>
+      <c r="W239" s="10">
+        <v>7.694444444444444E-2</v>
+      </c>
+      <c r="X239" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y239" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z239" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA239" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB239" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC239" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD239" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE239" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF239" s="9" t="s">
+        <v>2049</v>
+      </c>
+      <c r="AG239" s="9" t="s">
+        <v>2050</v>
+      </c>
+      <c r="AH239" s="9">
+        <v>6.2269769999999998</v>
+      </c>
+      <c r="AI239" s="9">
+        <v>-75.599621999999997</v>
+      </c>
+      <c r="AJ239" s="9" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AK239" s="9">
+        <v>6.2518320000000003</v>
+      </c>
+      <c r="AL239" s="9">
+        <v>-75.551834999999997</v>
+      </c>
+      <c r="AM239" s="26">
+        <f t="shared" si="3"/>
+        <v>9.6481481481481488E-2</v>
+      </c>
       <c r="AN239" s="9"/>
     </row>
-    <row r="240" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A240" s="9" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B240" s="9" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C240" s="9" t="s">
+        <v>2054</v>
+      </c>
+      <c r="D240" s="9" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E240" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F240" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G240" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="H240" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="I240" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J240" s="9">
+        <v>7287</v>
+      </c>
+      <c r="K240" s="9" t="s">
+        <v>2055</v>
+      </c>
+      <c r="L240" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M240" s="10">
+        <v>1.295013888888889E-2</v>
+      </c>
+      <c r="N240" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O240" s="9" t="s">
+        <v>2056</v>
+      </c>
+      <c r="P240" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q240" s="10">
+        <v>5.4758101851851851E-3</v>
+      </c>
+      <c r="R240" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S240" s="10">
+        <v>0.26842594907407408</v>
+      </c>
+      <c r="T240" s="9">
+        <v>45.036999999999999</v>
+      </c>
+      <c r="U240" s="9">
+        <v>10.41</v>
+      </c>
+      <c r="V240" s="10">
+        <v>0.18027780092592591</v>
+      </c>
+      <c r="W240" s="10">
+        <v>0.1340850810185184</v>
+      </c>
+      <c r="X240" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y240" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z240" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA240" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB240" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC240" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD240" s="9">
+        <v>2</v>
+      </c>
+      <c r="AE240" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF240" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="AG240" s="9" t="s">
+        <v>2058</v>
+      </c>
+      <c r="AH240" s="9">
+        <v>6.2267679999999999</v>
+      </c>
+      <c r="AI240" s="9">
+        <v>-75.599311999999998</v>
+      </c>
+      <c r="AJ240" s="9" t="s">
+        <v>2059</v>
+      </c>
+      <c r="AK240" s="9">
+        <v>6.2685969999999998</v>
+      </c>
+      <c r="AL240" s="9">
+        <v>-75.599288000000001</v>
+      </c>
+      <c r="AM240" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN240" s="9"/>
     </row>
     <row r="241" spans="40:40" x14ac:dyDescent="0.25">

--- a/BASE_RECORRIDOS_PRO_JCA.xlsx
+++ b/BASE_RECORRIDOS_PRO_JCA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\INTERVENTORIA VELNEC\Recorridos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC09BD5-1AF5-44C9-910A-3593317AB8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA67C3B-6617-46B5-BCE1-F913C0695ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="24240" windowHeight="13020" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5509" uniqueCount="2060">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5680" uniqueCount="2131">
   <si>
     <t>ID</t>
   </si>
@@ -6230,6 +6230,219 @@
   </si>
   <si>
     <t>6.268597, -75.599288</t>
+  </si>
+  <si>
+    <t>d8610283ab31c17b</t>
+  </si>
+  <si>
+    <t>24_09_2026_AO_Diur.gpx</t>
+  </si>
+  <si>
+    <t>d8610283ab31c17b60cf55c57f3fef35c24792cb35cd6303472074d6dc57a9e2</t>
+  </si>
+  <si>
+    <t>24/09/2026</t>
+  </si>
+  <si>
+    <t>24/09/2026 09:11:42</t>
+  </si>
+  <si>
+    <t>24/09/2026 15:36:24</t>
+  </si>
+  <si>
+    <t>Inicio GPS tardío: 00:41:43 después de las 08:30.; Fin GPS anticipado: 00:53:36 antes de las 16:30.; 4 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.216154, -75.597554</t>
+  </si>
+  <si>
+    <t>6.222023, -75.593338</t>
+  </si>
+  <si>
+    <t>80b1d8418c2b1eaa</t>
+  </si>
+  <si>
+    <t>24_09_2026_AR_Diur.gpx</t>
+  </si>
+  <si>
+    <t>80b1d8418c2b1eaab60e02e6a877ea0131fa1acbbaf1244fd97677a34ac1ea83</t>
+  </si>
+  <si>
+    <t>24/09/2026 08:14:20</t>
+  </si>
+  <si>
+    <t>24/09/2026 16:32:03</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 00:15:40 antes de las 08:30.; Fin GPS dentro de la tolerancia del horario programado.; 4 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.225782, -75.599368</t>
+  </si>
+  <si>
+    <t>6.247414, -75.615005</t>
+  </si>
+  <si>
+    <t>26d8bdaf1d13469e</t>
+  </si>
+  <si>
+    <t>24_09_2026_DR_Diur.gpx</t>
+  </si>
+  <si>
+    <t>26d8bdaf1d13469ee33712c9bfcbfe9c5901905e2a80baf0fe4c1f50012cf2f3</t>
+  </si>
+  <si>
+    <t>24/09/2026 08:27:18</t>
+  </si>
+  <si>
+    <t>24/09/2026 15:51:15</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS anticipado: 00:38:45 antes de las 16:30.; 2 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.238194, -75.603010</t>
+  </si>
+  <si>
+    <t>6.248174, -75.605002</t>
+  </si>
+  <si>
+    <t>92b923405ece402b</t>
+  </si>
+  <si>
+    <t>24_09_2026_HC_Diur.gpx</t>
+  </si>
+  <si>
+    <t>92b923405ece402b75cd59de5c90e486ec87dfad75c78c4f899255e5739248da</t>
+  </si>
+  <si>
+    <t>24/09/2026 09:16:50</t>
+  </si>
+  <si>
+    <t>24/09/2026 13:34:41</t>
+  </si>
+  <si>
+    <t>Inicio GPS tardío: 00:46:50 después de las 08:30.; Fin GPS anticipado: 02:55:19 antes de las 16:30.; 1 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.225663, -75.599553</t>
+  </si>
+  <si>
+    <t>6.261435, -75.603897</t>
+  </si>
+  <si>
+    <t>676d50fbccc03774</t>
+  </si>
+  <si>
+    <t>24_09_2026_JA_Diur.gpx</t>
+  </si>
+  <si>
+    <t>676d50fbccc0377475a506b4c473ea57a7024889c5da3b94f8b6202fc5952dfe</t>
+  </si>
+  <si>
+    <t>24/09/2026 08:52:25</t>
+  </si>
+  <si>
+    <t>24/09/2026 12:37:22</t>
+  </si>
+  <si>
+    <t>Inicio GPS tardío: 00:22:25 después de las 08:30.; Fin GPS anticipado: 03:52:38 antes de las 16:30.</t>
+  </si>
+  <si>
+    <t>6.225514, -75.599447</t>
+  </si>
+  <si>
+    <t>6.236992, -75.558877</t>
+  </si>
+  <si>
+    <t>b4281bc6eb1402cd</t>
+  </si>
+  <si>
+    <t>24_09_2026_JO_Diur.gpx</t>
+  </si>
+  <si>
+    <t>b4281bc6eb1402cd6b1c175a0e75d9bca1eb794b273c036c77cd612468789d15</t>
+  </si>
+  <si>
+    <t>24/09/2026 08:53:59</t>
+  </si>
+  <si>
+    <t>24/09/2026 16:24:23</t>
+  </si>
+  <si>
+    <t>Inicio GPS tardío: 00:23:59 después de las 08:30.; Fin GPS dentro de la tolerancia del horario programado.; 14 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.225613, -75.599412</t>
+  </si>
+  <si>
+    <t>6.246439, -75.552709</t>
+  </si>
+  <si>
+    <t>9f4f0535ce907d5c</t>
+  </si>
+  <si>
+    <t>24_09_2026_JZ_Diur.gpx</t>
+  </si>
+  <si>
+    <t>9f4f0535ce907d5c87d52ce754bb4b9539a103e71e85d5792a13d7c8617a20d6</t>
+  </si>
+  <si>
+    <t>24/09/2026 08:33:45</t>
+  </si>
+  <si>
+    <t>24/09/2026 16:40:46</t>
+  </si>
+  <si>
+    <t>6.226663, -75.599202</t>
+  </si>
+  <si>
+    <t>6.279131, -75.569137</t>
+  </si>
+  <si>
+    <t>6c891630b524a9ff</t>
+  </si>
+  <si>
+    <t>24_09_2026_SJ_Diur.gpx</t>
+  </si>
+  <si>
+    <t>6c891630b524a9ffafdb948e9cbc7937f36d22b6ca2cbcba2289b40b905b476d</t>
+  </si>
+  <si>
+    <t>24/09/2026 08:53:57</t>
+  </si>
+  <si>
+    <t>24/09/2026 15:52:13</t>
+  </si>
+  <si>
+    <t>Inicio GPS tardío: 00:23:57 después de las 08:30.; Fin GPS anticipado: 00:37:47 antes de las 16:30.; 1 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.225561, -75.599342</t>
+  </si>
+  <si>
+    <t>6.311430, -75.558457</t>
+  </si>
+  <si>
+    <t>564426f7571d7fb3</t>
+  </si>
+  <si>
+    <t>24_09_2026_YL_Diur.gpx</t>
+  </si>
+  <si>
+    <t>564426f7571d7fb39bec01e73fe74859f78006eae2f3d66e604884dc4b8f07a3</t>
+  </si>
+  <si>
+    <t>24/09/2026 08:29:19</t>
+  </si>
+  <si>
+    <t>24/09/2026 16:35:40</t>
+  </si>
+  <si>
+    <t>6.225586, -75.599145</t>
+  </si>
+  <si>
+    <t>6.258532, -75.615984</t>
   </si>
 </sst>
 </file>
@@ -6239,7 +6452,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[hh]:mm:ss"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6307,6 +6520,12 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -6406,7 +6625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6494,6 +6713,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6540,6 +6765,9 @@
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
     </dxf>
     <dxf>
       <font>
@@ -6623,6 +6851,11 @@
     </dxf>
     <dxf>
       <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
@@ -6652,11 +6885,9 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
-    </dxf>
-    <dxf>
       <font>
-        <sz val="14"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -6682,12 +6913,6 @@
     <dxf>
       <font>
         <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -40314,1371 +40539,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E67C1C-2F15-4D2B-A97A-A1B46B6F5B69}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
-  <location ref="A57:E73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item m="1" x="4"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="17"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="8">
-    <chartFormat chart="24" format="13" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="14" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="15" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="16" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="21" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="22" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="23" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="24" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0966AFF-8B15-4A0E-BE48-1F64EB76CB37}" name="TablaDinámica7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="57">
-  <location ref="AI107:AJ122" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item h="1" x="11"/>
-        <item h="1" x="12"/>
-        <item h="1" x="13"/>
-        <item h="1" x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Turno" fld="8" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="10">
-    <format dxfId="15">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="14">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="13">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="12">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="11">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="10">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="9">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="8">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="7">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="6">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="48" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="53" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="56" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D330A9A-54B8-43DD-8D11-CC5633B99CDA}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
-  <location ref="A6:E22" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item m="1" x="4"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="13"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="6" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="9">
-    <chartFormat chart="5" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="10" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="11" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="12" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
-  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item h="1" m="1" x="4"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="13"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="10">
-    <format dxfId="25">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="24">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="23">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="22">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="21">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="20">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="19">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="18">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="17">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="16">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="34" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
-  <location ref="A107:D123" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="8"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Suma de Kilómetros" fld="19" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="6">
-    <chartFormat chart="16" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="12"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="12"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{238AB259-E577-48AC-B3A0-09F752F5685D}" name="TablaDinámica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A169:B185" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="43">
@@ -42477,7 +41337,7 @@
     <dataField name="Suma de Sumatoria de tiempo total sin recorrido" fld="38" baseField="6" baseItem="0" numFmtId="21"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="26">
+    <format dxfId="6">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -42504,7 +41364,544 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E67C1C-2F15-4D2B-A97A-A1B46B6F5B69}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
+  <location ref="A57:E73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item m="1" x="4"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="17"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="8">
+    <chartFormat chart="24" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="15" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="16" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="21" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="22" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="23" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="24" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0966AFF-8B15-4A0E-BE48-1F64EB76CB37}" name="TablaDinámica7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="57">
+  <location ref="AI107:AJ122" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="13"/>
+        <item h="1" x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Turno" fld="8" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="16">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="48" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="53" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="56" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B44BF58-179E-4C57-BD89-E6E3367D37B9}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
   <location ref="K107:M122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
@@ -42662,13 +42059,13 @@
     <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="38">
+    <format dxfId="28">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="37">
+    <format dxfId="27">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="36">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="13">
@@ -42689,26 +42086,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="35">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="33">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="22">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="21">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="13">
@@ -42729,17 +42126,17 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="29">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="27">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -42788,6 +42185,834 @@
           </reference>
           <reference field="17" count="1" selected="0">
             <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D330A9A-54B8-43DD-8D11-CC5633B99CDA}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+  <location ref="A6:E22" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item m="1" x="4"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="13"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="6" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="9">
+    <chartFormat chart="5" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
+  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" m="1" x="4"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="13"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="38">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="37">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="35">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="33">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="32">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="31">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="34" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
+  <location ref="A107:D123" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="8"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Suma de Kilómetros" fld="19" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="16" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
@@ -68349,7 +68574,7 @@
         <v>-75.546586000000005</v>
       </c>
       <c r="AM195" s="26">
-        <f t="shared" ref="AM195:AM240" si="3">IF(N195="INICIO TARDÍO",M195,0)+IF(R195="TERMINÓ ANTES",Q195,0)</f>
+        <f t="shared" ref="AM195:AM249" si="3">IF(N195="INICIO TARDÍO",M195,0)+IF(R195="TERMINÓ ANTES",Q195,0)</f>
         <v>0</v>
       </c>
       <c r="AN195" s="9"/>
@@ -73794,52 +74019,1114 @@
       </c>
       <c r="AN240" s="9"/>
     </row>
-    <row r="241" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A241" s="35" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B241" s="35" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C241" s="35" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D241" s="35" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E241" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="F241" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="G241" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="H241" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="I241" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="J241" s="35">
+        <v>3430</v>
+      </c>
+      <c r="K241" s="35" t="s">
+        <v>2064</v>
+      </c>
+      <c r="L241" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="M241" s="36">
+        <v>2.8965428240740741E-2</v>
+      </c>
+      <c r="N241" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="O241" s="35" t="s">
+        <v>2065</v>
+      </c>
+      <c r="P241" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q241" s="36">
+        <v>3.7219456018518518E-2</v>
+      </c>
+      <c r="R241" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="S241" s="36">
+        <v>0.26714844907407409</v>
+      </c>
+      <c r="T241" s="35">
+        <v>19.553999999999998</v>
+      </c>
+      <c r="U241" s="35">
+        <v>18.96</v>
+      </c>
+      <c r="V241" s="36">
+        <v>4.2980486111111098E-2</v>
+      </c>
+      <c r="W241" s="36">
+        <v>2.4208506944444451E-2</v>
+      </c>
+      <c r="X241" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y241" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z241" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA241" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB241" s="35">
+        <v>0</v>
+      </c>
+      <c r="AC241" s="35">
+        <v>0</v>
+      </c>
+      <c r="AD241" s="35">
+        <v>4</v>
+      </c>
+      <c r="AE241" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF241" s="35" t="s">
+        <v>2066</v>
+      </c>
+      <c r="AG241" s="35" t="s">
+        <v>2067</v>
+      </c>
+      <c r="AH241" s="35">
+        <v>6.2161540000000004</v>
+      </c>
+      <c r="AI241" s="35">
+        <v>-75.597554000000002</v>
+      </c>
+      <c r="AJ241" s="35" t="s">
+        <v>2068</v>
+      </c>
+      <c r="AK241" s="35">
+        <v>6.2220230000000001</v>
+      </c>
+      <c r="AL241" s="35">
+        <v>-75.593338000000003</v>
+      </c>
+      <c r="AM241" s="26">
+        <f t="shared" si="3"/>
+        <v>6.6184884259259252E-2</v>
+      </c>
       <c r="AN241" s="9"/>
     </row>
-    <row r="242" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A242" s="35" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B242" s="35" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C242" s="35" t="s">
+        <v>2071</v>
+      </c>
+      <c r="D242" s="35" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E242" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="F242" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="G242" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="H242" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="I242" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="J242" s="35">
+        <v>1795</v>
+      </c>
+      <c r="K242" s="35" t="s">
+        <v>2072</v>
+      </c>
+      <c r="L242" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="M242" s="36">
+        <v>1.087962962962963E-2</v>
+      </c>
+      <c r="N242" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="O242" s="35" t="s">
+        <v>2073</v>
+      </c>
+      <c r="P242" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q242" s="36">
+        <v>1.423611111111111E-3</v>
+      </c>
+      <c r="R242" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="S242" s="36">
+        <v>0.34563657407407411</v>
+      </c>
+      <c r="T242" s="35">
+        <v>29.731000000000002</v>
+      </c>
+      <c r="U242" s="35">
+        <v>4.18</v>
+      </c>
+      <c r="V242" s="36">
+        <v>0.29662037037037042</v>
+      </c>
+      <c r="W242" s="36">
+        <v>0.2630439814814815</v>
+      </c>
+      <c r="X242" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y242" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z242" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA242" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB242" s="35">
+        <v>0</v>
+      </c>
+      <c r="AC242" s="35">
+        <v>0</v>
+      </c>
+      <c r="AD242" s="35">
+        <v>4</v>
+      </c>
+      <c r="AE242" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF242" s="35" t="s">
+        <v>2074</v>
+      </c>
+      <c r="AG242" s="35" t="s">
+        <v>2075</v>
+      </c>
+      <c r="AH242" s="35">
+        <v>6.2257819999999997</v>
+      </c>
+      <c r="AI242" s="35">
+        <v>-75.599367999999998</v>
+      </c>
+      <c r="AJ242" s="35" t="s">
+        <v>2076</v>
+      </c>
+      <c r="AK242" s="35">
+        <v>6.247414</v>
+      </c>
+      <c r="AL242" s="35">
+        <v>-75.615004999999996</v>
+      </c>
+      <c r="AM242" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN242" s="9"/>
     </row>
-    <row r="243" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A243" s="35" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B243" s="35" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C243" s="35" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D243" s="35" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E243" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="F243" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="G243" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="H243" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="I243" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="J243" s="35">
+        <v>2721</v>
+      </c>
+      <c r="K243" s="35" t="s">
+        <v>2080</v>
+      </c>
+      <c r="L243" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="M243" s="36">
+        <v>1.8749999999999999E-3</v>
+      </c>
+      <c r="N243" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="O243" s="35" t="s">
+        <v>2081</v>
+      </c>
+      <c r="P243" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q243" s="36">
+        <v>2.690972222222222E-2</v>
+      </c>
+      <c r="R243" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="S243" s="36">
+        <v>0.30829861111111112</v>
+      </c>
+      <c r="T243" s="35">
+        <v>35.728999999999999</v>
+      </c>
+      <c r="U243" s="35">
+        <v>5.9</v>
+      </c>
+      <c r="V243" s="36">
+        <v>0.2522800925925926</v>
+      </c>
+      <c r="W243" s="36">
+        <v>0.1942939814814815</v>
+      </c>
+      <c r="X243" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y243" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z243" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA243" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB243" s="35">
+        <v>0</v>
+      </c>
+      <c r="AC243" s="35">
+        <v>0</v>
+      </c>
+      <c r="AD243" s="35">
+        <v>2</v>
+      </c>
+      <c r="AE243" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF243" s="35" t="s">
+        <v>2082</v>
+      </c>
+      <c r="AG243" s="35" t="s">
+        <v>2083</v>
+      </c>
+      <c r="AH243" s="35">
+        <v>6.238194</v>
+      </c>
+      <c r="AI243" s="35">
+        <v>-75.603009999999998</v>
+      </c>
+      <c r="AJ243" s="35" t="s">
+        <v>2084</v>
+      </c>
+      <c r="AK243" s="35">
+        <v>6.2481739999999997</v>
+      </c>
+      <c r="AL243" s="35">
+        <v>-75.605001999999999</v>
+      </c>
+      <c r="AM243" s="26">
+        <f t="shared" si="3"/>
+        <v>2.690972222222222E-2</v>
+      </c>
       <c r="AN243" s="9"/>
     </row>
-    <row r="244" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A244" s="35" t="s">
+        <v>2085</v>
+      </c>
+      <c r="B244" s="35" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C244" s="35" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D244" s="35" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E244" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="F244" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="G244" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="H244" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="I244" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="J244" s="35">
+        <v>2783</v>
+      </c>
+      <c r="K244" s="35" t="s">
+        <v>2088</v>
+      </c>
+      <c r="L244" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="M244" s="36">
+        <v>3.2523148148148148E-2</v>
+      </c>
+      <c r="N244" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="O244" s="35" t="s">
+        <v>2089</v>
+      </c>
+      <c r="P244" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q244" s="36">
+        <v>0.12174768518518519</v>
+      </c>
+      <c r="R244" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="S244" s="36">
+        <v>0.17906250000000001</v>
+      </c>
+      <c r="T244" s="35">
+        <v>36.811</v>
+      </c>
+      <c r="U244" s="35">
+        <v>11.08</v>
+      </c>
+      <c r="V244" s="36">
+        <v>0.13844907407407411</v>
+      </c>
+      <c r="W244" s="36">
+        <v>7.7569444444444441E-2</v>
+      </c>
+      <c r="X244" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y244" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z244" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA244" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB244" s="35">
+        <v>0</v>
+      </c>
+      <c r="AC244" s="35">
+        <v>0</v>
+      </c>
+      <c r="AD244" s="35">
+        <v>1</v>
+      </c>
+      <c r="AE244" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF244" s="35" t="s">
+        <v>2090</v>
+      </c>
+      <c r="AG244" s="35" t="s">
+        <v>2091</v>
+      </c>
+      <c r="AH244" s="35">
+        <v>6.2256629999999999</v>
+      </c>
+      <c r="AI244" s="35">
+        <v>-75.599553</v>
+      </c>
+      <c r="AJ244" s="35" t="s">
+        <v>2092</v>
+      </c>
+      <c r="AK244" s="35">
+        <v>6.2614349999999996</v>
+      </c>
+      <c r="AL244" s="35">
+        <v>-75.603897000000003</v>
+      </c>
+      <c r="AM244" s="26">
+        <f t="shared" si="3"/>
+        <v>0.15427083333333336</v>
+      </c>
       <c r="AN244" s="9"/>
     </row>
-    <row r="245" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A245" s="35" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B245" s="35" t="s">
+        <v>2094</v>
+      </c>
+      <c r="C245" s="35" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D245" s="35" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E245" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="F245" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="G245" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="H245" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="I245" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="J245" s="35">
+        <v>1079</v>
+      </c>
+      <c r="K245" s="35" t="s">
+        <v>2096</v>
+      </c>
+      <c r="L245" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="M245" s="36">
+        <v>1.556712962962963E-2</v>
+      </c>
+      <c r="N245" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="O245" s="35" t="s">
+        <v>2097</v>
+      </c>
+      <c r="P245" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q245" s="36">
+        <v>0.1615509259259259</v>
+      </c>
+      <c r="R245" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="S245" s="36">
+        <v>0.1562152777777778</v>
+      </c>
+      <c r="T245" s="35">
+        <v>14.132</v>
+      </c>
+      <c r="U245" s="35">
+        <v>5.49</v>
+      </c>
+      <c r="V245" s="36">
+        <v>0.1071990740740741</v>
+      </c>
+      <c r="W245" s="36">
+        <v>8.802083333333334E-2</v>
+      </c>
+      <c r="X245" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y245" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z245" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA245" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB245" s="35">
+        <v>0</v>
+      </c>
+      <c r="AC245" s="35">
+        <v>0</v>
+      </c>
+      <c r="AD245" s="35">
+        <v>0</v>
+      </c>
+      <c r="AE245" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF245" s="35" t="s">
+        <v>2098</v>
+      </c>
+      <c r="AG245" s="35" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AH245" s="35">
+        <v>6.2255140000000004</v>
+      </c>
+      <c r="AI245" s="35">
+        <v>-75.599446999999998</v>
+      </c>
+      <c r="AJ245" s="35" t="s">
+        <v>2100</v>
+      </c>
+      <c r="AK245" s="35">
+        <v>6.2369919999999999</v>
+      </c>
+      <c r="AL245" s="35">
+        <v>-75.558876999999995</v>
+      </c>
+      <c r="AM245" s="26">
+        <f t="shared" si="3"/>
+        <v>0.17711805555555554</v>
+      </c>
       <c r="AN245" s="9"/>
     </row>
-    <row r="246" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A246" s="35" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B246" s="35" t="s">
+        <v>2102</v>
+      </c>
+      <c r="C246" s="35" t="s">
+        <v>2103</v>
+      </c>
+      <c r="D246" s="35" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E246" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="F246" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="G246" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="H246" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="I246" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="J246" s="35">
+        <v>4391</v>
+      </c>
+      <c r="K246" s="35" t="s">
+        <v>2104</v>
+      </c>
+      <c r="L246" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="M246" s="36">
+        <v>1.6657268518518519E-2</v>
+      </c>
+      <c r="N246" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="O246" s="35" t="s">
+        <v>2105</v>
+      </c>
+      <c r="P246" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q246" s="36">
+        <v>3.900231481481482E-3</v>
+      </c>
+      <c r="R246" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="S246" s="36">
+        <v>0.31277583333333331</v>
+      </c>
+      <c r="T246" s="35">
+        <v>28.091000000000001</v>
+      </c>
+      <c r="U246" s="35">
+        <v>8.52</v>
+      </c>
+      <c r="V246" s="36">
+        <v>0.13743112268518529</v>
+      </c>
+      <c r="W246" s="36">
+        <v>0.1038293287037037</v>
+      </c>
+      <c r="X246" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y246" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z246" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA246" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB246" s="35">
+        <v>0</v>
+      </c>
+      <c r="AC246" s="35">
+        <v>0</v>
+      </c>
+      <c r="AD246" s="35">
+        <v>14</v>
+      </c>
+      <c r="AE246" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF246" s="35" t="s">
+        <v>2106</v>
+      </c>
+      <c r="AG246" s="35" t="s">
+        <v>2107</v>
+      </c>
+      <c r="AH246" s="35">
+        <v>6.2256130000000001</v>
+      </c>
+      <c r="AI246" s="35">
+        <v>-75.599412000000001</v>
+      </c>
+      <c r="AJ246" s="35" t="s">
+        <v>2108</v>
+      </c>
+      <c r="AK246" s="35">
+        <v>6.2464389999999996</v>
+      </c>
+      <c r="AL246" s="35">
+        <v>-75.552708999999993</v>
+      </c>
+      <c r="AM246" s="26">
+        <f t="shared" si="3"/>
+        <v>1.6657268518518519E-2</v>
+      </c>
       <c r="AN246" s="9"/>
     </row>
-    <row r="247" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A247" s="35" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B247" s="35" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C247" s="35" t="s">
+        <v>2111</v>
+      </c>
+      <c r="D247" s="35" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E247" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="F247" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="G247" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="H247" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="I247" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="J247" s="35">
+        <v>4312</v>
+      </c>
+      <c r="K247" s="35" t="s">
+        <v>2112</v>
+      </c>
+      <c r="L247" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="M247" s="36">
+        <v>2.604166666666667E-3</v>
+      </c>
+      <c r="N247" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="O247" s="35" t="s">
+        <v>2113</v>
+      </c>
+      <c r="P247" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q247" s="36">
+        <v>7.4768518518518517E-3</v>
+      </c>
+      <c r="R247" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="S247" s="36">
+        <v>0.3382060185185185</v>
+      </c>
+      <c r="T247" s="35">
+        <v>53.088999999999999</v>
+      </c>
+      <c r="U247" s="35">
+        <v>9</v>
+      </c>
+      <c r="V247" s="36">
+        <v>0.24577546296296299</v>
+      </c>
+      <c r="W247" s="36">
+        <v>0.1365625</v>
+      </c>
+      <c r="X247" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y247" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z247" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA247" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB247" s="35">
+        <v>0</v>
+      </c>
+      <c r="AC247" s="35">
+        <v>0</v>
+      </c>
+      <c r="AD247" s="35">
+        <v>1</v>
+      </c>
+      <c r="AE247" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF247" s="35" t="s">
+        <v>324</v>
+      </c>
+      <c r="AG247" s="35" t="s">
+        <v>2114</v>
+      </c>
+      <c r="AH247" s="35">
+        <v>6.2266630000000003</v>
+      </c>
+      <c r="AI247" s="35">
+        <v>-75.599202000000005</v>
+      </c>
+      <c r="AJ247" s="35" t="s">
+        <v>2115</v>
+      </c>
+      <c r="AK247" s="35">
+        <v>6.2791309999999996</v>
+      </c>
+      <c r="AL247" s="35">
+        <v>-75.569136999999998</v>
+      </c>
+      <c r="AM247" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN247" s="9"/>
     </row>
-    <row r="248" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A248" s="35" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B248" s="35" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C248" s="35" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D248" s="35" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E248" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="F248" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="G248" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="H248" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="I248" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="J248" s="35">
+        <v>3465</v>
+      </c>
+      <c r="K248" s="35" t="s">
+        <v>2119</v>
+      </c>
+      <c r="L248" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="M248" s="36">
+        <v>1.6631944444444449E-2</v>
+      </c>
+      <c r="N248" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="O248" s="35" t="s">
+        <v>2120</v>
+      </c>
+      <c r="P248" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q248" s="36">
+        <v>2.6238425925925929E-2</v>
+      </c>
+      <c r="R248" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="S248" s="36">
+        <v>0.29046296296296298</v>
+      </c>
+      <c r="T248" s="35">
+        <v>45.395000000000003</v>
+      </c>
+      <c r="U248" s="35">
+        <v>10.93</v>
+      </c>
+      <c r="V248" s="36">
+        <v>0.17298611111111109</v>
+      </c>
+      <c r="W248" s="36">
+        <v>0.1090856481481482</v>
+      </c>
+      <c r="X248" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y248" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z248" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA248" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB248" s="35">
+        <v>0</v>
+      </c>
+      <c r="AC248" s="35">
+        <v>0</v>
+      </c>
+      <c r="AD248" s="35">
+        <v>1</v>
+      </c>
+      <c r="AE248" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF248" s="35" t="s">
+        <v>2121</v>
+      </c>
+      <c r="AG248" s="35" t="s">
+        <v>2122</v>
+      </c>
+      <c r="AH248" s="35">
+        <v>6.2255609999999999</v>
+      </c>
+      <c r="AI248" s="35">
+        <v>-75.599341999999993</v>
+      </c>
+      <c r="AJ248" s="35" t="s">
+        <v>2123</v>
+      </c>
+      <c r="AK248" s="35">
+        <v>6.3114299999999997</v>
+      </c>
+      <c r="AL248" s="35">
+        <v>-75.558457000000004</v>
+      </c>
+      <c r="AM248" s="26">
+        <f t="shared" si="3"/>
+        <v>4.2870370370370378E-2</v>
+      </c>
       <c r="AN248" s="9"/>
     </row>
-    <row r="249" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A249" s="35" t="s">
+        <v>2124</v>
+      </c>
+      <c r="B249" s="35" t="s">
+        <v>2125</v>
+      </c>
+      <c r="C249" s="35" t="s">
+        <v>2126</v>
+      </c>
+      <c r="D249" s="35" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E249" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="F249" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="G249" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="H249" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="I249" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="J249" s="35">
+        <v>679</v>
+      </c>
+      <c r="K249" s="35" t="s">
+        <v>2127</v>
+      </c>
+      <c r="L249" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="M249" s="36">
+        <v>4.7453703703703698E-4</v>
+      </c>
+      <c r="N249" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="O249" s="35" t="s">
+        <v>2128</v>
+      </c>
+      <c r="P249" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q249" s="36">
+        <v>3.9351851851851848E-3</v>
+      </c>
+      <c r="R249" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="S249" s="36">
+        <v>0.33774305555555562</v>
+      </c>
+      <c r="T249" s="35">
+        <v>13.8</v>
+      </c>
+      <c r="U249" s="35">
+        <v>1.9</v>
+      </c>
+      <c r="V249" s="36">
+        <v>0.3027199074074074</v>
+      </c>
+      <c r="W249" s="36">
+        <v>0.29311342592592587</v>
+      </c>
+      <c r="X249" s="36">
+        <v>0</v>
+      </c>
+      <c r="Y249" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z249" s="35">
+        <v>0</v>
+      </c>
+      <c r="AA249" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB249" s="35">
+        <v>0</v>
+      </c>
+      <c r="AC249" s="35">
+        <v>0</v>
+      </c>
+      <c r="AD249" s="35">
+        <v>1</v>
+      </c>
+      <c r="AE249" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF249" s="35" t="s">
+        <v>324</v>
+      </c>
+      <c r="AG249" s="35" t="s">
+        <v>2129</v>
+      </c>
+      <c r="AH249" s="35">
+        <v>6.2255859999999998</v>
+      </c>
+      <c r="AI249" s="35">
+        <v>-75.599144999999993</v>
+      </c>
+      <c r="AJ249" s="35" t="s">
+        <v>2130</v>
+      </c>
+      <c r="AK249" s="35">
+        <v>6.2585319999999998</v>
+      </c>
+      <c r="AL249" s="35">
+        <v>-75.615983999999997</v>
+      </c>
+      <c r="AM249" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN249" s="9"/>
     </row>
-    <row r="250" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN250" s="9"/>
     </row>
-    <row r="251" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN251" s="9"/>
     </row>
-    <row r="252" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN252" s="9"/>
     </row>
-    <row r="253" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN253" s="9"/>
     </row>
-    <row r="254" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN254" s="9"/>
     </row>
-    <row r="255" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN255" s="9"/>
     </row>
-    <row r="256" spans="40:40" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:40" x14ac:dyDescent="0.25">
       <c r="AN256" s="9"/>
     </row>
     <row r="257" spans="40:40" x14ac:dyDescent="0.25">

--- a/BASE_RECORRIDOS_PRO_JCA.xlsx
+++ b/BASE_RECORRIDOS_PRO_JCA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\INTERVENTORIA VELNEC\Recorridos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA67C3B-6617-46B5-BCE1-F913C0695ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC924BD7-EF00-4DB5-9489-44CD1E509925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="24240" windowHeight="13020" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5680" uniqueCount="2131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5756" uniqueCount="2163">
   <si>
     <t>ID</t>
   </si>
@@ -6443,6 +6443,102 @@
   </si>
   <si>
     <t>6.258532, -75.615984</t>
+  </si>
+  <si>
+    <t>bab305730ba056d1</t>
+  </si>
+  <si>
+    <t>24_09_2026_DV_Noct.gpx</t>
+  </si>
+  <si>
+    <t>bab305730ba056d176d0642f5f7797bef81782d99654b9a7d153eca74bc51454</t>
+  </si>
+  <si>
+    <t>24/09/2026 17:45:06</t>
+  </si>
+  <si>
+    <t>25/09/2026 00:20:21</t>
+  </si>
+  <si>
+    <t>Inicio GPS dentro de la tolerancia del horario programado.; Fin GPS posterior: 00:20:21 después de las 00:00.</t>
+  </si>
+  <si>
+    <t>6.226775, -75.599357</t>
+  </si>
+  <si>
+    <t>6.272680, -75.601973</t>
+  </si>
+  <si>
+    <t>517e09ca382f2401</t>
+  </si>
+  <si>
+    <t>24_09_2026_IQ_Noct.gpx</t>
+  </si>
+  <si>
+    <t>517e09ca382f240146f4d160e91a2e77611b8b3c7b2749178d70cd88ebdba105</t>
+  </si>
+  <si>
+    <t>24/09/2026 16:44:27</t>
+  </si>
+  <si>
+    <t>24/09/2026 23:53:58</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 01:15:33 antes de las 18:00.; Fin GPS dentro de la tolerancia del horario programado.; 2 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.228867, -75.596225</t>
+  </si>
+  <si>
+    <t>6.294895, -75.543944</t>
+  </si>
+  <si>
+    <t>c91268ef9d9bb5cd</t>
+  </si>
+  <si>
+    <t>24_09_2026_JP_Noct.gpx</t>
+  </si>
+  <si>
+    <t>c91268ef9d9bb5cde23a9219657fe3b734c5e105bab9c46f195b8e269fa1ffd3</t>
+  </si>
+  <si>
+    <t>24/09/2026 17:43:58</t>
+  </si>
+  <si>
+    <t>24/09/2026 22:51:32</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 00:16:02 antes de las 18:00.; Fin GPS anticipado: 01:08:28 antes de las 00:00.</t>
+  </si>
+  <si>
+    <t>6.226888, -75.599710</t>
+  </si>
+  <si>
+    <t>6.251725, -75.551782</t>
+  </si>
+  <si>
+    <t>7bc001476223be32</t>
+  </si>
+  <si>
+    <t>24_09_2026_LA_Noct.gpx</t>
+  </si>
+  <si>
+    <t>7bc001476223be32ca2e18bfca848d78c20a463a1f334d53d5ae105117f98a46</t>
+  </si>
+  <si>
+    <t>24/09/2026 17:26:54</t>
+  </si>
+  <si>
+    <t>25/09/2026 00:05:11</t>
+  </si>
+  <si>
+    <t>Inicio GPS anterior al horario: 00:33:06 antes de las 18:00.; Fin GPS dentro de la tolerancia del horario programado.; 3 hueco(s) GPS &gt;= 10 min.</t>
+  </si>
+  <si>
+    <t>6.226773, -75.599313</t>
+  </si>
+  <si>
+    <t>6.263545, -75.596572</t>
   </si>
 </sst>
 </file>
@@ -6767,64 +6863,6 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
       <font>
         <sz val="14"/>
       </font>
@@ -6889,6 +6927,64 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
     </dxf>
     <dxf>
       <font>
@@ -40539,6 +40635,594 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B44BF58-179E-4C57-BD89-E6E3367D37B9}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
+  <location ref="K107:M122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item h="1" x="0"/>
+        <item h="1" m="1" x="4"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="17"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="12">
+    <format dxfId="17">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="17" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="17" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="28" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="28" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="28" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="28" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
+  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" m="1" x="4"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="13"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="27">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="25">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="34" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{238AB259-E577-48AC-B3A0-09F752F5685D}" name="TablaDinámica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A169:B185" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="43">
@@ -41337,7 +42021,7 @@
     <dataField name="Suma de Sumatoria de tiempo total sin recorrido" fld="38" baseField="6" baseItem="0" numFmtId="21"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="6">
+    <format dxfId="28">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -41364,845 +42048,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E67C1C-2F15-4D2B-A97A-A1B46B6F5B69}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
-  <location ref="A57:E73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item m="1" x="4"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="17"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="8">
-    <chartFormat chart="24" format="13" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="14" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="15" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="16" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="21" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="22" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="23" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="24" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0966AFF-8B15-4A0E-BE48-1F64EB76CB37}" name="TablaDinámica7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="57">
-  <location ref="AI107:AJ122" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item h="1" x="11"/>
-        <item h="1" x="12"/>
-        <item h="1" x="13"/>
-        <item h="1" x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="15">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Turno" fld="8" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="10">
-    <format dxfId="16">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="15">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="14">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="13">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="12">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="11">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="10">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="9">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="8">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="7">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="48" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="53" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="56" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B44BF58-179E-4C57-BD89-E6E3367D37B9}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
-  <location ref="K107:M122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="18">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="15"/>
-        <item x="2"/>
-        <item h="1" m="1" x="16"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="1"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="7"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item h="1" x="0"/>
-        <item h="1" m="1" x="4"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="17"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="12">
-    <format dxfId="28">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="27">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="26">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="25">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="24">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="17" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="23">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="22">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="21">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="20">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="19">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="18">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="17" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="17">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="28" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="28" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="28" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="28" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="17" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D330A9A-54B8-43DD-8D11-CC5633B99CDA}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A6:E22" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
@@ -42490,9 +42336,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28E38F05-C705-4B63-8427-947953AE6907}" name="TablaDinámica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
-  <location ref="W107:Y122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47E67C1C-2F15-4D2B-A97A-A1B46B6F5B69}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
+  <location ref="A57:E73" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -42553,20 +42399,20 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item h="1" m="1" x="4"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item m="1" x="4"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -42585,7 +42431,7 @@
   <rowFields count="1">
     <field x="6"/>
   </rowFields>
-  <rowItems count="14">
+  <rowItems count="15">
     <i>
       <x/>
     </i>
@@ -42623,6 +42469,9 @@
       <x v="11"/>
     </i>
     <i>
+      <x v="12"/>
+    </i>
+    <i>
       <x v="13"/>
     </i>
     <i t="grand">
@@ -42630,11 +42479,17 @@
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="13"/>
+    <field x="17"/>
   </colFields>
-  <colItems count="2">
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
     <i>
       <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -42645,120 +42500,100 @@
     <pageField fld="4" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Cuenta de Estado inicio" fld="13" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Cuenta de Estado fin" fld="17" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="10">
-    <format dxfId="38">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="37">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="36">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="35">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="34">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="33">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="32">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="31">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="13">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="30">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="29">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="34" format="0" series="1">
+  <chartFormats count="8">
+    <chartFormat chart="24" format="13" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="13" count="1" selected="0">
+          <reference field="17" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="34" format="1" series="1">
+    <chartFormat chart="24" format="14" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="13" count="1" selected="0">
+          <reference field="17" count="1" selected="0">
             <x v="1"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="34" format="2" series="1">
+    <chartFormat chart="24" format="15" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="13" count="1" selected="0">
+          <reference field="17" count="1" selected="0">
             <x v="2"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="34" format="3" series="1">
+    <chartFormat chart="24" format="16" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="13" count="1" selected="0">
+          <reference field="17" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="21" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="22" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="23" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="24" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="17" count="1" selected="0">
             <x v="3"/>
           </reference>
         </references>
@@ -42777,7 +42612,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EF99BAB-2468-4B54-BA40-E9C7DB4614DE}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
   <location ref="A107:D123" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="32">
@@ -43013,6 +42848,267 @@
           </reference>
           <reference field="8" count="1" selected="0">
             <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0966AFF-8B15-4A0E-BE48-1F64EB76CB37}" name="TablaDinámica7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="57">
+  <location ref="AI107:AJ122" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="18">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="15"/>
+        <item x="2"/>
+        <item h="1" m="1" x="16"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="13"/>
+        <item h="1" x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="1"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Turno" fld="8" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="38">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="37">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="35">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="33">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="32">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="31">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="13">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="48" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="53" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="56" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -68574,7 +68670,7 @@
         <v>-75.546586000000005</v>
       </c>
       <c r="AM195" s="26">
-        <f t="shared" ref="AM195:AM249" si="3">IF(N195="INICIO TARDÍO",M195,0)+IF(R195="TERMINÓ ANTES",Q195,0)</f>
+        <f t="shared" ref="AM195:AM253" si="3">IF(N195="INICIO TARDÍO",M195,0)+IF(R195="TERMINÓ ANTES",Q195,0)</f>
         <v>0</v>
       </c>
       <c r="AN195" s="9"/>
@@ -75108,16 +75204,488 @@
       </c>
       <c r="AN249" s="9"/>
     </row>
-    <row r="250" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A250" s="9" t="s">
+        <v>2131</v>
+      </c>
+      <c r="B250" s="9" t="s">
+        <v>2132</v>
+      </c>
+      <c r="C250" s="9" t="s">
+        <v>2133</v>
+      </c>
+      <c r="D250" s="9" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E250" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F250" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="G250" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H250" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I250" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J250" s="9">
+        <v>3161</v>
+      </c>
+      <c r="K250" s="9" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L250" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M250" s="10">
+        <v>1.0347222222222219E-2</v>
+      </c>
+      <c r="N250" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O250" s="9" t="s">
+        <v>2135</v>
+      </c>
+      <c r="P250" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q250" s="10">
+        <v>1.413194444444445E-2</v>
+      </c>
+      <c r="R250" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="S250" s="10">
+        <v>0.27447916666666672</v>
+      </c>
+      <c r="T250" s="9">
+        <v>63.529000000000003</v>
+      </c>
+      <c r="U250" s="9">
+        <v>14.36</v>
+      </c>
+      <c r="V250" s="10">
+        <v>0.18431712962962959</v>
+      </c>
+      <c r="W250" s="10">
+        <v>7.6909722222222227E-2</v>
+      </c>
+      <c r="X250" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y250" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z250" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA250" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB250" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC250" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD250" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE250" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF250" s="9" t="s">
+        <v>2136</v>
+      </c>
+      <c r="AG250" s="9" t="s">
+        <v>2137</v>
+      </c>
+      <c r="AH250" s="9">
+        <v>6.2267749999999999</v>
+      </c>
+      <c r="AI250" s="9">
+        <v>-75.599356999999998</v>
+      </c>
+      <c r="AJ250" s="9" t="s">
+        <v>2138</v>
+      </c>
+      <c r="AK250" s="9">
+        <v>6.2726800000000003</v>
+      </c>
+      <c r="AL250" s="9">
+        <v>-75.601973000000001</v>
+      </c>
+      <c r="AM250" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN250" s="9"/>
     </row>
-    <row r="251" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A251" s="9" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B251" s="9" t="s">
+        <v>2140</v>
+      </c>
+      <c r="C251" s="9" t="s">
+        <v>2141</v>
+      </c>
+      <c r="D251" s="9" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E251" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F251" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="G251" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="H251" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="I251" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J251" s="9">
+        <v>1719</v>
+      </c>
+      <c r="K251" s="9" t="s">
+        <v>2142</v>
+      </c>
+      <c r="L251" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M251" s="10">
+        <v>5.2465277777777777E-2</v>
+      </c>
+      <c r="N251" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O251" s="9" t="s">
+        <v>2143</v>
+      </c>
+      <c r="P251" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q251" s="10">
+        <v>4.1898148148148146E-3</v>
+      </c>
+      <c r="R251" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S251" s="10">
+        <v>0.29827546296296298</v>
+      </c>
+      <c r="T251" s="9">
+        <v>29.850999999999999</v>
+      </c>
+      <c r="U251" s="9">
+        <v>10.64</v>
+      </c>
+      <c r="V251" s="10">
+        <v>0.1168634259259259</v>
+      </c>
+      <c r="W251" s="10">
+        <v>7.8483796296296301E-2</v>
+      </c>
+      <c r="X251" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y251" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z251" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA251" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB251" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC251" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD251" s="9">
+        <v>2</v>
+      </c>
+      <c r="AE251" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF251" s="9" t="s">
+        <v>2144</v>
+      </c>
+      <c r="AG251" s="9" t="s">
+        <v>2145</v>
+      </c>
+      <c r="AH251" s="9">
+        <v>6.2288670000000002</v>
+      </c>
+      <c r="AI251" s="9">
+        <v>-75.596225000000004</v>
+      </c>
+      <c r="AJ251" s="9" t="s">
+        <v>2146</v>
+      </c>
+      <c r="AK251" s="9">
+        <v>6.2948950000000004</v>
+      </c>
+      <c r="AL251" s="9">
+        <v>-75.543943999999996</v>
+      </c>
+      <c r="AM251" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN251" s="9"/>
     </row>
-    <row r="252" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A252" s="9" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B252" s="9" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C252" s="9" t="s">
+        <v>2149</v>
+      </c>
+      <c r="D252" s="9" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E252" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F252" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="G252" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H252" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="I252" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J252" s="9">
+        <v>2463</v>
+      </c>
+      <c r="K252" s="9" t="s">
+        <v>2150</v>
+      </c>
+      <c r="L252" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M252" s="10">
+        <v>1.113425925925926E-2</v>
+      </c>
+      <c r="N252" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O252" s="9" t="s">
+        <v>2151</v>
+      </c>
+      <c r="P252" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q252" s="10">
+        <v>4.7546296296296288E-2</v>
+      </c>
+      <c r="R252" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S252" s="10">
+        <v>0.21358796296296301</v>
+      </c>
+      <c r="T252" s="9">
+        <v>32.11</v>
+      </c>
+      <c r="U252" s="9">
+        <v>9.9</v>
+      </c>
+      <c r="V252" s="10">
+        <v>0.135162037037037</v>
+      </c>
+      <c r="W252" s="10">
+        <v>8.1377314814814819E-2</v>
+      </c>
+      <c r="X252" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y252" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z252" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA252" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB252" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC252" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD252" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE252" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF252" s="9" t="s">
+        <v>2152</v>
+      </c>
+      <c r="AG252" s="9" t="s">
+        <v>2153</v>
+      </c>
+      <c r="AH252" s="9">
+        <v>6.2268879999999998</v>
+      </c>
+      <c r="AI252" s="9">
+        <v>-75.599710000000002</v>
+      </c>
+      <c r="AJ252" s="9" t="s">
+        <v>2154</v>
+      </c>
+      <c r="AK252" s="9">
+        <v>6.2517250000000004</v>
+      </c>
+      <c r="AL252" s="9">
+        <v>-75.551782000000003</v>
+      </c>
+      <c r="AM252" s="26">
+        <f t="shared" si="3"/>
+        <v>4.7546296296296288E-2</v>
+      </c>
       <c r="AN252" s="9"/>
     </row>
-    <row r="253" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A253" s="9" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B253" s="9" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C253" s="9" t="s">
+        <v>2157</v>
+      </c>
+      <c r="D253" s="9" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E253" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F253" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="G253" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="H253" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="I253" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J253" s="9">
+        <v>4867</v>
+      </c>
+      <c r="K253" s="9" t="s">
+        <v>2158</v>
+      </c>
+      <c r="L253" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M253" s="10">
+        <v>2.298483796296296E-2</v>
+      </c>
+      <c r="N253" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O253" s="9" t="s">
+        <v>2159</v>
+      </c>
+      <c r="P253" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q253" s="10">
+        <v>3.6007870370370369E-3</v>
+      </c>
+      <c r="R253" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S253" s="10">
+        <v>0.276585625</v>
+      </c>
+      <c r="T253" s="9">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="U253" s="9">
+        <v>6.81</v>
+      </c>
+      <c r="V253" s="10">
+        <v>0.1976852662037038</v>
+      </c>
+      <c r="W253" s="10">
+        <v>0.16368065972222229</v>
+      </c>
+      <c r="X253" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y253" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z253" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA253" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB253" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC253" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD253" s="9">
+        <v>3</v>
+      </c>
+      <c r="AE253" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF253" s="9" t="s">
+        <v>2160</v>
+      </c>
+      <c r="AG253" s="9" t="s">
+        <v>2161</v>
+      </c>
+      <c r="AH253" s="9">
+        <v>6.2267729999999997</v>
+      </c>
+      <c r="AI253" s="9">
+        <v>-75.599312999999995</v>
+      </c>
+      <c r="AJ253" s="9" t="s">
+        <v>2162</v>
+      </c>
+      <c r="AK253" s="9">
+        <v>6.2635449999999997</v>
+      </c>
+      <c r="AL253" s="9">
+        <v>-75.596571999999995</v>
+      </c>
+      <c r="AM253" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AN253" s="9"/>
     </row>
     <row r="254" spans="1:40" x14ac:dyDescent="0.25">
